--- a/results/02_taxa_assemblage/WardsClustering/tables/coassignment_matrix.xlsx
+++ b/results/02_taxa_assemblage/WardsClustering/tables/coassignment_matrix.xlsx
@@ -698,10 +698,10 @@
         <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>0.9135802469135802</v>
+        <v>0.9891975308641975</v>
       </c>
       <c r="E2" t="n">
-        <v>0.3245341614906832</v>
+        <v>1</v>
       </c>
       <c r="F2" t="n">
         <v>0</v>
@@ -710,13 +710,13 @@
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>0.5707898658718331</v>
+        <v>0.5588673621460507</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>1</v>
+        <v>0.540625</v>
       </c>
       <c r="K2" t="n">
         <v>0</v>
@@ -725,118 +725,118 @@
         <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>1</v>
+        <v>0.8996865203761756</v>
       </c>
       <c r="N2" t="n">
-        <v>1</v>
+        <v>0.9392523364485982</v>
       </c>
       <c r="O2" t="n">
-        <v>0.9829457364341085</v>
+        <v>0.5395348837209303</v>
       </c>
       <c r="P2" t="n">
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>0.4204018547140649</v>
       </c>
       <c r="R2" t="n">
         <v>0</v>
       </c>
       <c r="S2" t="n">
-        <v>0.4003189792663477</v>
+        <v>0.5869218500797448</v>
       </c>
       <c r="T2" t="n">
-        <v>0.5890625</v>
+        <v>0.984375</v>
       </c>
       <c r="U2" t="n">
-        <v>0.5313935681470138</v>
+        <v>0.9846860643185299</v>
       </c>
       <c r="V2" t="n">
         <v>0</v>
       </c>
       <c r="W2" t="n">
-        <v>0.2782071097372488</v>
+        <v>0.5023183925811437</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>0.5796875</v>
       </c>
       <c r="Y2" t="n">
-        <v>1</v>
+        <v>0.6835637480798771</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.4155038759689922</v>
+        <v>0.8790697674418605</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.08333333333333333</v>
+        <v>0.5496794871794872</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.08571428571428572</v>
+        <v>0.5507936507936508</v>
       </c>
       <c r="AC2" t="n">
-        <v>0</v>
+        <v>0.4621578099838969</v>
       </c>
       <c r="AD2" t="n">
-        <v>0.9891640866873065</v>
+        <v>0.5541795665634675</v>
       </c>
       <c r="AE2" t="n">
-        <v>0.06220839813374806</v>
+        <v>0.5536547433903577</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.07894736842105263</v>
+        <v>0.5634674922600619</v>
       </c>
       <c r="AG2" t="n">
-        <v>0</v>
+        <v>0.546969696969697</v>
       </c>
       <c r="AH2" t="n">
-        <v>0.001555209953343701</v>
+        <v>0.1959564541213064</v>
       </c>
       <c r="AI2" t="n">
-        <v>1</v>
+        <v>0.5461658841940532</v>
       </c>
       <c r="AJ2" t="n">
-        <v>1</v>
+        <v>0.5632911392405063</v>
       </c>
       <c r="AK2" t="n">
-        <v>0.9734789391575663</v>
+        <v>0.5273010920436817</v>
       </c>
       <c r="AL2" t="n">
-        <v>0.9862174578866769</v>
+        <v>0.8208269525267994</v>
       </c>
       <c r="AM2" t="n">
-        <v>1</v>
+        <v>0.5799701046337817</v>
       </c>
       <c r="AN2" t="n">
-        <v>0.1037151702786378</v>
+        <v>0.9721362229102167</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.003021148036253776</v>
+        <v>0.1812688821752266</v>
       </c>
       <c r="AP2" t="n">
-        <v>0.0015600624024961</v>
+        <v>0.4024960998439938</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0</v>
+        <v>0.05405405405405406</v>
       </c>
       <c r="AR2" t="n">
-        <v>0</v>
+        <v>0.5276073619631901</v>
       </c>
       <c r="AS2" t="n">
-        <v>0.0577223088923557</v>
+        <v>0.6037441497659907</v>
       </c>
       <c r="AT2" t="n">
-        <v>1</v>
+        <v>0.6213292117465224</v>
       </c>
       <c r="AU2" t="n">
-        <v>0</v>
+        <v>0.2339089481946625</v>
       </c>
       <c r="AV2" t="n">
-        <v>0.4094368340943683</v>
+        <v>0.512937595129376</v>
       </c>
       <c r="AW2" t="n">
-        <v>0.9984076433121019</v>
+        <v>1</v>
       </c>
       <c r="AX2" t="n">
-        <v>0</v>
+        <v>0.5300632911392406</v>
       </c>
       <c r="AY2" t="n">
         <v>1</v>
@@ -861,7 +861,7 @@
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>1</v>
+        <v>0.9444444444444444</v>
       </c>
       <c r="G3" t="n">
         <v>1</v>
@@ -891,16 +891,16 @@
         <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>1</v>
+        <v>0.984</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>0.007874015748031496</v>
       </c>
       <c r="R3" t="n">
         <v>1</v>
       </c>
       <c r="S3" t="n">
-        <v>0.004862236628849271</v>
+        <v>0</v>
       </c>
       <c r="T3" t="n">
         <v>0</v>
@@ -912,7 +912,7 @@
         <v>1</v>
       </c>
       <c r="W3" t="n">
-        <v>0.1650793650793651</v>
+        <v>0.003174603174603175</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
@@ -945,7 +945,7 @@
         <v>0</v>
       </c>
       <c r="AH3" t="n">
-        <v>0.9825949367088608</v>
+        <v>0.2088607594936709</v>
       </c>
       <c r="AI3" t="n">
         <v>0</v>
@@ -966,13 +966,13 @@
         <v>0</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.9831546707503829</v>
+        <v>0.2419601837672282</v>
       </c>
       <c r="AP3" t="n">
-        <v>0</v>
+        <v>0.009433962264150943</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0.9953198127925117</v>
+        <v>0.4040561622464899</v>
       </c>
       <c r="AR3" t="n">
         <v>0</v>
@@ -984,10 +984,10 @@
         <v>0</v>
       </c>
       <c r="AU3" t="n">
-        <v>0.9919614147909968</v>
+        <v>0.2057877813504823</v>
       </c>
       <c r="AV3" t="n">
-        <v>0</v>
+        <v>0.003144654088050315</v>
       </c>
       <c r="AW3" t="n">
         <v>0</v>
@@ -1006,7 +1006,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.9135802469135802</v>
+        <v>0.9891975308641975</v>
       </c>
       <c r="C4" t="n">
         <v>0</v>
@@ -1015,7 +1015,7 @@
         <v>1</v>
       </c>
       <c r="E4" t="n">
-        <v>0.5465838509316771</v>
+        <v>0.9984472049689441</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
@@ -1024,13 +1024,13 @@
         <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>0.661608497723824</v>
+        <v>0.4946889226100152</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>0.916403785488959</v>
+        <v>0.4826498422712934</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
@@ -1039,121 +1039,121 @@
         <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>0.8998435054773083</v>
+        <v>0.9061032863849765</v>
       </c>
       <c r="N4" t="n">
-        <v>0.9111111111111111</v>
+        <v>0.9587301587301588</v>
       </c>
       <c r="O4" t="n">
-        <v>0.8996913580246914</v>
+        <v>0.4737654320987654</v>
       </c>
       <c r="P4" t="n">
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.0600924499229584</v>
+        <v>0.3697996918335901</v>
       </c>
       <c r="R4" t="n">
         <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>0.6028938906752411</v>
+        <v>0.6463022508038585</v>
       </c>
       <c r="T4" t="n">
-        <v>0.7464788732394366</v>
+        <v>1</v>
       </c>
       <c r="U4" t="n">
-        <v>0.6953846153846154</v>
+        <v>1</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>0.4427001569858713</v>
+        <v>0.554160125588697</v>
       </c>
       <c r="X4" t="n">
-        <v>0.07740916271721959</v>
+        <v>0.5165876777251185</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.9183673469387755</v>
+        <v>0.7268445839874411</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.5031446540880503</v>
+        <v>0.8522012578616353</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.1645367412140575</v>
+        <v>0.4840255591054313</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.1777777777777778</v>
+        <v>0.5</v>
       </c>
       <c r="AC4" t="n">
-        <v>0.06677265500794913</v>
+        <v>0.4085850556438791</v>
       </c>
       <c r="AD4" t="n">
-        <v>0.9088098918083463</v>
+        <v>0.4930448222565688</v>
       </c>
       <c r="AE4" t="n">
-        <v>0.1269592476489028</v>
+        <v>0.4921630094043887</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.15600624024961</v>
+        <v>0.5101404056162246</v>
       </c>
       <c r="AG4" t="n">
-        <v>0.07272727272727272</v>
+        <v>0.4818181818181818</v>
       </c>
       <c r="AH4" t="n">
-        <v>0.00310077519379845</v>
+        <v>0.2294573643410853</v>
       </c>
       <c r="AI4" t="n">
-        <v>0.9022082018927445</v>
+        <v>0.4889589905362776</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0.9079365079365079</v>
+        <v>0.4952380952380953</v>
       </c>
       <c r="AK4" t="n">
-        <v>0.8961832061068702</v>
+        <v>0.482442748091603</v>
       </c>
       <c r="AL4" t="n">
-        <v>0.9015625</v>
+        <v>0.7921875</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.911144578313253</v>
+        <v>0.5030120481927711</v>
       </c>
       <c r="AN4" t="n">
-        <v>0.2390625</v>
+        <v>0.9875</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.006163328197226503</v>
+        <v>0.2187981510015408</v>
       </c>
       <c r="AP4" t="n">
-        <v>0.07740916271721959</v>
+        <v>0.344391785150079</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0</v>
+        <v>0.07121212121212121</v>
       </c>
       <c r="AR4" t="n">
-        <v>0.07339449541284404</v>
+        <v>0.463302752293578</v>
       </c>
       <c r="AS4" t="n">
-        <v>0.1605723370429253</v>
+        <v>0.6565977742448331</v>
       </c>
       <c r="AT4" t="n">
-        <v>0.9254658385093167</v>
+        <v>0.6537267080745341</v>
       </c>
       <c r="AU4" t="n">
-        <v>0.003194888178913738</v>
+        <v>0.2795527156549521</v>
       </c>
       <c r="AV4" t="n">
-        <v>0.6172839506172839</v>
+        <v>0.5632716049382716</v>
       </c>
       <c r="AW4" t="n">
-        <v>0.9149606299212598</v>
+        <v>0.9779527559055118</v>
       </c>
       <c r="AX4" t="n">
-        <v>0.06698564593301436</v>
+        <v>0.4673046251993621</v>
       </c>
       <c r="AY4" t="n">
-        <v>0.9231950844854071</v>
+        <v>0.9907834101382489</v>
       </c>
     </row>
     <row r="5">
@@ -1163,13 +1163,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.3245341614906832</v>
+        <v>1</v>
       </c>
       <c r="C5" t="n">
         <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>0.5465838509316771</v>
+        <v>0.9984472049689441</v>
       </c>
       <c r="E5" t="n">
         <v>1</v>
@@ -1181,13 +1181,13 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>0.4923312883435583</v>
+        <v>0.5199386503067485</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>0.3591772151898734</v>
+        <v>0.5063291139240507</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
@@ -1196,121 +1196,121 @@
         <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>0.408</v>
+        <v>0.8992</v>
       </c>
       <c r="N5" t="n">
-        <v>0.3444444444444444</v>
+        <v>0.946031746031746</v>
       </c>
       <c r="O5" t="n">
-        <v>0.3847352024922118</v>
+        <v>0.5093457943925234</v>
       </c>
       <c r="P5" t="n">
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.598116169544741</v>
+        <v>0.3830455259026688</v>
       </c>
       <c r="R5" t="n">
         <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>0.9459901800327333</v>
+        <v>0.6284779050736498</v>
       </c>
       <c r="T5" t="n">
-        <v>0.8164556962025317</v>
+        <v>0.9968354430379747</v>
       </c>
       <c r="U5" t="n">
-        <v>0.8271604938271605</v>
+        <v>0.9953703703703703</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>0.8411949685534591</v>
+        <v>0.539308176100629</v>
       </c>
       <c r="X5" t="n">
-        <v>0.6130573248407644</v>
+        <v>0.5445859872611465</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.3694968553459119</v>
+        <v>0.7169811320754716</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.5102040816326531</v>
+        <v>0.8665620094191523</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.6937086092715232</v>
+        <v>0.5149006622516556</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.6954397394136808</v>
+        <v>0.5211726384364821</v>
       </c>
       <c r="AC5" t="n">
-        <v>0.5928338762214984</v>
+        <v>0.4267100977198697</v>
       </c>
       <c r="AD5" t="n">
-        <v>0.3886255924170616</v>
+        <v>0.5197472353870458</v>
       </c>
       <c r="AE5" t="n">
-        <v>0.7018927444794952</v>
+        <v>0.5173501577287066</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.6769706336939721</v>
+        <v>0.5347758887171561</v>
       </c>
       <c r="AG5" t="n">
-        <v>0.6018662519440124</v>
+        <v>0.5054432348367029</v>
       </c>
       <c r="AH5" t="n">
-        <v>0.007874015748031496</v>
+        <v>0.2110236220472441</v>
       </c>
       <c r="AI5" t="n">
-        <v>0.3591772151898734</v>
+        <v>0.5205696202531646</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0.3745980707395498</v>
+        <v>0.522508038585209</v>
       </c>
       <c r="AK5" t="n">
-        <v>0.3913713405238829</v>
+        <v>0.5038520801232665</v>
       </c>
       <c r="AL5" t="n">
-        <v>0.3713405238828968</v>
+        <v>0.785824345146379</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.362406015037594</v>
+        <v>0.5398496240601504</v>
       </c>
       <c r="AN5" t="n">
-        <v>0.7429906542056075</v>
+        <v>0.9813084112149533</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.01080246913580247</v>
+        <v>0.2067901234567901</v>
       </c>
       <c r="AP5" t="n">
-        <v>0.6156299840510366</v>
+        <v>0.3700159489633174</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0.001529051987767584</v>
+        <v>0.06727828746177369</v>
       </c>
       <c r="AR5" t="n">
-        <v>0.6213740458015267</v>
+        <v>0.4916030534351145</v>
       </c>
       <c r="AS5" t="n">
-        <v>0.7435483870967742</v>
+        <v>0.6483870967741936</v>
       </c>
       <c r="AT5" t="n">
-        <v>0.3528481012658228</v>
+        <v>0.6392405063291139</v>
       </c>
       <c r="AU5" t="n">
-        <v>0.00644122383252818</v>
+        <v>0.2576489533011272</v>
       </c>
       <c r="AV5" t="n">
-        <v>1</v>
+        <v>0.5383411580594679</v>
       </c>
       <c r="AW5" t="n">
-        <v>0.3695299837925446</v>
+        <v>1</v>
       </c>
       <c r="AX5" t="n">
-        <v>0.6075353218210361</v>
+        <v>0.5007849293563579</v>
       </c>
       <c r="AY5" t="n">
-        <v>0.3674418604651163</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -1323,7 +1323,7 @@
         <v>0</v>
       </c>
       <c r="C6" t="n">
-        <v>1</v>
+        <v>0.9444444444444444</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
@@ -1335,43 +1335,43 @@
         <v>1</v>
       </c>
       <c r="G6" t="n">
-        <v>1</v>
+        <v>0.9412698412698413</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>1</v>
+        <v>0.98145285935085</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>1</v>
+        <v>0.9414556962025317</v>
       </c>
       <c r="L6" t="n">
-        <v>1</v>
+        <v>0.955177743431221</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>0.004702194357366771</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>1</v>
+        <v>0.9508716323296355</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>0.0108359133126935</v>
       </c>
       <c r="R6" t="n">
-        <v>1</v>
+        <v>0.9319620253164557</v>
       </c>
       <c r="S6" t="n">
-        <v>0.003184713375796179</v>
+        <v>0.03662420382165605</v>
       </c>
       <c r="T6" t="n">
         <v>0</v>
@@ -1380,16 +1380,16 @@
         <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>1</v>
+        <v>0.9355828220858896</v>
       </c>
       <c r="W6" t="n">
-        <v>0.1546875</v>
+        <v>0.0515625</v>
       </c>
       <c r="X6" t="n">
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>0.01713395638629283</v>
       </c>
       <c r="Z6" t="n">
         <v>0</v>
@@ -1401,7 +1401,7 @@
         <v>0</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>0.001592356687898089</v>
       </c>
       <c r="AD6" t="n">
         <v>0</v>
@@ -1416,7 +1416,7 @@
         <v>0</v>
       </c>
       <c r="AH6" t="n">
-        <v>0.9843014128728415</v>
+        <v>0.3092621664050236</v>
       </c>
       <c r="AI6" t="n">
         <v>0</v>
@@ -1437,28 +1437,28 @@
         <v>0</v>
       </c>
       <c r="AO6" t="n">
-        <v>0.9892966360856269</v>
+        <v>0.3440366972477064</v>
       </c>
       <c r="AP6" t="n">
-        <v>0</v>
+        <v>0.01095461658841941</v>
       </c>
       <c r="AQ6" t="n">
-        <v>0.9954819277108434</v>
+        <v>0.5225903614457831</v>
       </c>
       <c r="AR6" t="n">
         <v>0</v>
       </c>
       <c r="AS6" t="n">
-        <v>0</v>
+        <v>0.04081632653061224</v>
       </c>
       <c r="AT6" t="n">
-        <v>0</v>
+        <v>0.02773497688751926</v>
       </c>
       <c r="AU6" t="n">
-        <v>0.9921259842519685</v>
+        <v>0.3023622047244094</v>
       </c>
       <c r="AV6" t="n">
-        <v>0</v>
+        <v>0.04923076923076923</v>
       </c>
       <c r="AW6" t="n">
         <v>0</v>
@@ -1489,7 +1489,7 @@
         <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>1</v>
+        <v>0.9412698412698413</v>
       </c>
       <c r="G7" t="n">
         <v>1</v>
@@ -1519,16 +1519,16 @@
         <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>1</v>
+        <v>0.9902597402597403</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>0.004754358161648178</v>
       </c>
       <c r="R7" t="n">
         <v>1</v>
       </c>
       <c r="S7" t="n">
-        <v>0.00487012987012987</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
         <v>0</v>
@@ -1540,7 +1540,7 @@
         <v>1</v>
       </c>
       <c r="W7" t="n">
-        <v>0.1576433121019108</v>
+        <v>0.003184713375796179</v>
       </c>
       <c r="X7" t="n">
         <v>0</v>
@@ -1573,7 +1573,7 @@
         <v>0</v>
       </c>
       <c r="AH7" t="n">
-        <v>0.9838187702265372</v>
+        <v>0.226537216828479</v>
       </c>
       <c r="AI7" t="n">
         <v>0</v>
@@ -1594,13 +1594,13 @@
         <v>0</v>
       </c>
       <c r="AO7" t="n">
-        <v>0.984375</v>
+        <v>0.271875</v>
       </c>
       <c r="AP7" t="n">
-        <v>0</v>
+        <v>0.0046875</v>
       </c>
       <c r="AQ7" t="n">
-        <v>0.9938176197836167</v>
+        <v>0.4234930448222566</v>
       </c>
       <c r="AR7" t="n">
         <v>0</v>
@@ -1612,10 +1612,10 @@
         <v>0</v>
       </c>
       <c r="AU7" t="n">
-        <v>0.9903999999999999</v>
+        <v>0.2256</v>
       </c>
       <c r="AV7" t="n">
-        <v>0</v>
+        <v>0.0032</v>
       </c>
       <c r="AW7" t="n">
         <v>0</v>
@@ -1634,16 +1634,16 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.5707898658718331</v>
+        <v>0.5588673621460507</v>
       </c>
       <c r="C8" t="n">
         <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>0.661608497723824</v>
+        <v>0.4946889226100152</v>
       </c>
       <c r="E8" t="n">
-        <v>0.4923312883435583</v>
+        <v>0.5199386503067485</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
@@ -1658,7 +1658,7 @@
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>0.5553846153846154</v>
+        <v>1</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
@@ -1667,121 +1667,121 @@
         <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>0.5729646697388633</v>
+        <v>0.5898617511520737</v>
       </c>
       <c r="N8" t="n">
-        <v>0.5729483282674772</v>
+        <v>0.5030395136778115</v>
       </c>
       <c r="O8" t="n">
-        <v>0.6066066066066066</v>
+        <v>1</v>
       </c>
       <c r="P8" t="n">
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.4181547619047619</v>
+        <v>0.8839285714285714</v>
       </c>
       <c r="R8" t="n">
         <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>0.4617784711388456</v>
+        <v>0.1326053042121685</v>
       </c>
       <c r="T8" t="n">
-        <v>0.482442748091603</v>
+        <v>0.4809160305343512</v>
       </c>
       <c r="U8" t="n">
-        <v>0.4887218045112782</v>
+        <v>0.4556390977443609</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>0.4</v>
+        <v>0.1181818181818182</v>
       </c>
       <c r="X8" t="n">
-        <v>0.4226006191950464</v>
+        <v>0.9891640866873065</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.5630630630630631</v>
+        <v>0.2597597597597597</v>
       </c>
       <c r="Z8" t="n">
-        <v>1</v>
+        <v>0.7331288343558282</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.5581395348837209</v>
+        <v>1</v>
       </c>
       <c r="AC8" t="n">
-        <v>0.419811320754717</v>
+        <v>0.9229559748427673</v>
       </c>
       <c r="AD8" t="n">
-        <v>0.5960365853658537</v>
+        <v>1</v>
       </c>
       <c r="AE8" t="n">
-        <v>0.4349157733537519</v>
+        <v>1</v>
       </c>
       <c r="AF8" t="n">
-        <v>0.4977307110438729</v>
+        <v>1</v>
       </c>
       <c r="AG8" t="n">
-        <v>0.4152923538230884</v>
+        <v>1</v>
       </c>
       <c r="AH8" t="n">
         <v>0.0060790273556231</v>
       </c>
       <c r="AI8" t="n">
-        <v>0.5390505359877489</v>
+        <v>1</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0.5801526717557252</v>
+        <v>1</v>
       </c>
       <c r="AK8" t="n">
-        <v>0.687218045112782</v>
+        <v>1</v>
       </c>
       <c r="AL8" t="n">
-        <v>0.600896860986547</v>
+        <v>0.7937219730941704</v>
       </c>
       <c r="AM8" t="n">
-        <v>0.5647058823529412</v>
+        <v>0.9779411764705882</v>
       </c>
       <c r="AN8" t="n">
-        <v>0.4486404833836858</v>
+        <v>0.5468277945619335</v>
       </c>
       <c r="AO8" t="n">
-        <v>0.01037037037037037</v>
+        <v>0.002962962962962963</v>
       </c>
       <c r="AP8" t="n">
-        <v>0.4224924012158054</v>
+        <v>0.8495440729483282</v>
       </c>
       <c r="AQ8" t="n">
-        <v>0.001464128843338214</v>
+        <v>0.002928257686676428</v>
       </c>
       <c r="AR8" t="n">
-        <v>0.4296407185628742</v>
+        <v>1</v>
       </c>
       <c r="AS8" t="n">
-        <v>0.503125</v>
+        <v>0.1640625</v>
       </c>
       <c r="AT8" t="n">
-        <v>0.6198473282442748</v>
+        <v>0.1603053435114504</v>
       </c>
       <c r="AU8" t="n">
         <v>0.003076923076923077</v>
       </c>
       <c r="AV8" t="n">
-        <v>0.5639097744360902</v>
+        <v>0.081203007518797</v>
       </c>
       <c r="AW8" t="n">
-        <v>0.5754276827371695</v>
+        <v>0.5987558320373251</v>
       </c>
       <c r="AX8" t="n">
-        <v>0.4230769230769231</v>
+        <v>1</v>
       </c>
       <c r="AY8" t="n">
-        <v>0.5969696969696969</v>
+        <v>0.546969696969697</v>
       </c>
     </row>
     <row r="9">
@@ -1803,7 +1803,7 @@
         <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>1</v>
+        <v>0.98145285935085</v>
       </c>
       <c r="G9" t="n">
         <v>1</v>
@@ -1833,16 +1833,16 @@
         <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>1</v>
+        <v>0.985981308411215</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>0.006269592476489028</v>
       </c>
       <c r="R9" t="n">
         <v>1</v>
       </c>
       <c r="S9" t="n">
-        <v>0.00482315112540193</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
         <v>0</v>
@@ -1854,7 +1854,7 @@
         <v>1</v>
       </c>
       <c r="W9" t="n">
-        <v>0.1658914728682171</v>
+        <v>0.00310077519379845</v>
       </c>
       <c r="X9" t="n">
         <v>0</v>
@@ -1887,7 +1887,7 @@
         <v>0</v>
       </c>
       <c r="AH9" t="n">
-        <v>0.984251968503937</v>
+        <v>0.2062992125984252</v>
       </c>
       <c r="AI9" t="n">
         <v>0</v>
@@ -1908,13 +1908,13 @@
         <v>0</v>
       </c>
       <c r="AO9" t="n">
-        <v>0.9847560975609756</v>
+        <v>0.2469512195121951</v>
       </c>
       <c r="AP9" t="n">
-        <v>0</v>
+        <v>0.004724409448818898</v>
       </c>
       <c r="AQ9" t="n">
-        <v>0.9939024390243902</v>
+        <v>0.4009146341463415</v>
       </c>
       <c r="AR9" t="n">
         <v>0</v>
@@ -1926,10 +1926,10 @@
         <v>0</v>
       </c>
       <c r="AU9" t="n">
-        <v>0.9905808477237049</v>
+        <v>0.2135007849293564</v>
       </c>
       <c r="AV9" t="n">
-        <v>0</v>
+        <v>0.003091190108191654</v>
       </c>
       <c r="AW9" t="n">
         <v>0</v>
@@ -1948,16 +1948,16 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1</v>
+        <v>0.540625</v>
       </c>
       <c r="C10" t="n">
         <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>0.916403785488959</v>
+        <v>0.4826498422712934</v>
       </c>
       <c r="E10" t="n">
-        <v>0.3591772151898734</v>
+        <v>0.5063291139240507</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
@@ -1966,7 +1966,7 @@
         <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>0.5553846153846154</v>
+        <v>1</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
@@ -1981,70 +1981,70 @@
         <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>1</v>
+        <v>0.5814696485623003</v>
       </c>
       <c r="N10" t="n">
-        <v>1</v>
+        <v>0.4976</v>
       </c>
       <c r="O10" t="n">
-        <v>0.9827044025157232</v>
+        <v>1</v>
       </c>
       <c r="P10" t="n">
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>0.8880248833592534</v>
       </c>
       <c r="R10" t="n">
         <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>0.434640522875817</v>
+        <v>0.1176470588235294</v>
       </c>
       <c r="T10" t="n">
-        <v>0.6075949367088608</v>
+        <v>0.4651898734177215</v>
       </c>
       <c r="U10" t="n">
-        <v>0.5694006309148265</v>
+        <v>0.4400630914826498</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>0.3004694835680751</v>
+        <v>0.107981220657277</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>0.9855769230769231</v>
       </c>
       <c r="Y10" t="n">
-        <v>1</v>
+        <v>0.2413793103448276</v>
       </c>
       <c r="Z10" t="n">
-        <v>0.3949843260188088</v>
+        <v>0.7241379310344828</v>
       </c>
       <c r="AA10" t="n">
-        <v>0.07479674796747968</v>
+        <v>1</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.07592891760904685</v>
+        <v>1</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>0.9189627228525121</v>
       </c>
       <c r="AD10" t="n">
-        <v>0.9889415481832543</v>
+        <v>1</v>
       </c>
       <c r="AE10" t="n">
-        <v>0.05727554179566564</v>
+        <v>1</v>
       </c>
       <c r="AF10" t="n">
-        <v>0.07210031347962383</v>
+        <v>1</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH10" t="n">
-        <v>0.001579778830963665</v>
+        <v>0.007898894154818325</v>
       </c>
       <c r="AI10" t="n">
         <v>1</v>
@@ -2053,49 +2053,49 @@
         <v>1</v>
       </c>
       <c r="AK10" t="n">
-        <v>0.9728</v>
+        <v>1</v>
       </c>
       <c r="AL10" t="n">
-        <v>0.9859375</v>
+        <v>0.7515625</v>
       </c>
       <c r="AM10" t="n">
-        <v>1</v>
+        <v>0.9758308157099698</v>
       </c>
       <c r="AN10" t="n">
-        <v>0.1316614420062696</v>
+        <v>0.5203761755485894</v>
       </c>
       <c r="AO10" t="n">
-        <v>0.001555209953343701</v>
+        <v>0.003110419906687403</v>
       </c>
       <c r="AP10" t="n">
-        <v>0.001610305958132045</v>
+        <v>0.8486312399355878</v>
       </c>
       <c r="AQ10" t="n">
-        <v>0</v>
+        <v>0.0045662100456621</v>
       </c>
       <c r="AR10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AS10" t="n">
-        <v>0.04830917874396135</v>
+        <v>0.14170692431562</v>
       </c>
       <c r="AT10" t="n">
-        <v>1</v>
+        <v>0.1403508771929824</v>
       </c>
       <c r="AU10" t="n">
-        <v>0</v>
+        <v>0.003225806451612903</v>
       </c>
       <c r="AV10" t="n">
-        <v>0.4430379746835443</v>
+        <v>0.06487341772151899</v>
       </c>
       <c r="AW10" t="n">
-        <v>0.9983948635634029</v>
+        <v>0.579454253611557</v>
       </c>
       <c r="AX10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AY10" t="n">
-        <v>1</v>
+        <v>0.5337519623233909</v>
       </c>
     </row>
     <row r="11">
@@ -2117,7 +2117,7 @@
         <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>1</v>
+        <v>0.9414556962025317</v>
       </c>
       <c r="G11" t="n">
         <v>1</v>
@@ -2147,16 +2147,16 @@
         <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>1</v>
+        <v>0.9935064935064936</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>0.001607717041800643</v>
       </c>
       <c r="R11" t="n">
         <v>1</v>
       </c>
       <c r="S11" t="n">
-        <v>0.004918032786885246</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
         <v>0</v>
@@ -2168,7 +2168,7 @@
         <v>1</v>
       </c>
       <c r="W11" t="n">
-        <v>0.1624203821656051</v>
+        <v>0.003184713375796179</v>
       </c>
       <c r="X11" t="n">
         <v>0</v>
@@ -2201,7 +2201,7 @@
         <v>0</v>
       </c>
       <c r="AH11" t="n">
-        <v>0.9853896103896104</v>
+        <v>0.2256493506493507</v>
       </c>
       <c r="AI11" t="n">
         <v>0</v>
@@ -2222,13 +2222,13 @@
         <v>0</v>
       </c>
       <c r="AO11" t="n">
-        <v>0.9829192546583851</v>
+        <v>0.2531055900621118</v>
       </c>
       <c r="AP11" t="n">
-        <v>0</v>
+        <v>0.008</v>
       </c>
       <c r="AQ11" t="n">
-        <v>0.9937694704049844</v>
+        <v>0.3800623052959501</v>
       </c>
       <c r="AR11" t="n">
         <v>0</v>
@@ -2240,10 +2240,10 @@
         <v>0</v>
       </c>
       <c r="AU11" t="n">
-        <v>0.9901315789473685</v>
+        <v>0.2171052631578947</v>
       </c>
       <c r="AV11" t="n">
-        <v>0</v>
+        <v>0.004777070063694267</v>
       </c>
       <c r="AW11" t="n">
         <v>0</v>
@@ -2274,7 +2274,7 @@
         <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>1</v>
+        <v>0.955177743431221</v>
       </c>
       <c r="G12" t="n">
         <v>1</v>
@@ -2307,13 +2307,13 @@
         <v>1</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>0.001567398119122257</v>
       </c>
       <c r="R12" t="n">
         <v>1</v>
       </c>
       <c r="S12" t="n">
-        <v>0.003252032520325203</v>
+        <v>0</v>
       </c>
       <c r="T12" t="n">
         <v>0</v>
@@ -2325,7 +2325,7 @@
         <v>1</v>
       </c>
       <c r="W12" t="n">
-        <v>0.1578125</v>
+        <v>0.003125</v>
       </c>
       <c r="X12" t="n">
         <v>0</v>
@@ -2358,7 +2358,7 @@
         <v>0</v>
       </c>
       <c r="AH12" t="n">
-        <v>0.9826771653543307</v>
+        <v>0.1984251968503937</v>
       </c>
       <c r="AI12" t="n">
         <v>0</v>
@@ -2379,13 +2379,13 @@
         <v>0</v>
       </c>
       <c r="AO12" t="n">
-        <v>0.9848024316109423</v>
+        <v>0.2386018237082067</v>
       </c>
       <c r="AP12" t="n">
-        <v>0</v>
+        <v>0.00782472613458529</v>
       </c>
       <c r="AQ12" t="n">
-        <v>0.9938931297709923</v>
+        <v>0.3816793893129771</v>
       </c>
       <c r="AR12" t="n">
         <v>0</v>
@@ -2397,10 +2397,10 @@
         <v>0</v>
       </c>
       <c r="AU12" t="n">
-        <v>0.9904761904761905</v>
+        <v>0.2</v>
       </c>
       <c r="AV12" t="n">
-        <v>0</v>
+        <v>0.001524390243902439</v>
       </c>
       <c r="AW12" t="n">
         <v>0</v>
@@ -2419,16 +2419,16 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1</v>
+        <v>0.8996865203761756</v>
       </c>
       <c r="C13" t="n">
         <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>0.8998435054773083</v>
+        <v>0.9061032863849765</v>
       </c>
       <c r="E13" t="n">
-        <v>0.408</v>
+        <v>0.8992</v>
       </c>
       <c r="F13" t="n">
         <v>0</v>
@@ -2437,13 +2437,13 @@
         <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>0.5729646697388633</v>
+        <v>0.5898617511520737</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>1</v>
+        <v>0.5814696485623003</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
@@ -2458,115 +2458,115 @@
         <v>1</v>
       </c>
       <c r="O13" t="n">
-        <v>0.984472049689441</v>
+        <v>0.562111801242236</v>
       </c>
       <c r="P13" t="n">
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>0.4339035769828927</v>
       </c>
       <c r="R13" t="n">
         <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>0.4626623376623377</v>
+        <v>0.560064935064935</v>
       </c>
       <c r="T13" t="n">
-        <v>0.6238244514106583</v>
+        <v>0.9137931034482759</v>
       </c>
       <c r="U13" t="n">
-        <v>0.5856697819314641</v>
+        <v>0.9221183800623053</v>
       </c>
       <c r="V13" t="n">
         <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>0.321259842519685</v>
+        <v>0.4992125984251968</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>0.6129541864139021</v>
       </c>
       <c r="Y13" t="n">
-        <v>1</v>
+        <v>0.7126984126984127</v>
       </c>
       <c r="Z13" t="n">
-        <v>0.4048</v>
+        <v>0.8</v>
       </c>
       <c r="AA13" t="n">
-        <v>0.08852459016393442</v>
+        <v>0.5737704918032787</v>
       </c>
       <c r="AB13" t="n">
-        <v>0.08412698412698413</v>
+        <v>0.5888888888888889</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>0.4838709677419355</v>
       </c>
       <c r="AD13" t="n">
-        <v>0.9889937106918238</v>
+        <v>0.5849056603773585</v>
       </c>
       <c r="AE13" t="n">
-        <v>0.06190476190476191</v>
+        <v>0.5841269841269842</v>
       </c>
       <c r="AF13" t="n">
-        <v>0.0828125</v>
+        <v>0.5984375</v>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>0.577639751552795</v>
       </c>
       <c r="AH13" t="n">
-        <v>0.001607717041800643</v>
+        <v>0.1752411575562701</v>
       </c>
       <c r="AI13" t="n">
-        <v>1</v>
+        <v>0.5945945945945946</v>
       </c>
       <c r="AJ13" t="n">
-        <v>1</v>
+        <v>0.593192868719611</v>
       </c>
       <c r="AK13" t="n">
-        <v>0.9745627980922098</v>
+        <v>0.5739268680445151</v>
       </c>
       <c r="AL13" t="n">
-        <v>0.9874411302982732</v>
+        <v>0.7456828885400314</v>
       </c>
       <c r="AM13" t="n">
-        <v>1</v>
+        <v>0.6018376722817764</v>
       </c>
       <c r="AN13" t="n">
-        <v>0.1293375394321767</v>
+        <v>0.8785488958990536</v>
       </c>
       <c r="AO13" t="n">
-        <v>0.001540832049306626</v>
+        <v>0.1679506933744222</v>
       </c>
       <c r="AP13" t="n">
-        <v>0.001587301587301587</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="AQ13" t="n">
-        <v>0</v>
+        <v>0.05513016845329249</v>
       </c>
       <c r="AR13" t="n">
-        <v>0</v>
+        <v>0.5595054095826894</v>
       </c>
       <c r="AS13" t="n">
-        <v>0.06180665610142631</v>
+        <v>0.5784469096671949</v>
       </c>
       <c r="AT13" t="n">
-        <v>1</v>
+        <v>0.5921259842519685</v>
       </c>
       <c r="AU13" t="n">
-        <v>0</v>
+        <v>0.2188498402555911</v>
       </c>
       <c r="AV13" t="n">
-        <v>0.4836702954898912</v>
+        <v>0.4758942457231726</v>
       </c>
       <c r="AW13" t="n">
-        <v>0.9983766233766234</v>
+        <v>0.8944805194805194</v>
       </c>
       <c r="AX13" t="n">
-        <v>0</v>
+        <v>0.5629032258064516</v>
       </c>
       <c r="AY13" t="n">
-        <v>1</v>
+        <v>0.8918495297805643</v>
       </c>
     </row>
     <row r="14">
@@ -2576,31 +2576,31 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1</v>
+        <v>0.9392523364485982</v>
       </c>
       <c r="C14" t="n">
         <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>0.9111111111111111</v>
+        <v>0.9587301587301588</v>
       </c>
       <c r="E14" t="n">
-        <v>0.3444444444444444</v>
+        <v>0.946031746031746</v>
       </c>
       <c r="F14" t="n">
-        <v>0</v>
+        <v>0.004702194357366771</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>0.5729483282674772</v>
+        <v>0.5030395136778115</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>1</v>
+        <v>0.4976</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
@@ -2615,115 +2615,115 @@
         <v>1</v>
       </c>
       <c r="O14" t="n">
-        <v>0.9843014128728415</v>
+        <v>0.4866562009419153</v>
       </c>
       <c r="P14" t="n">
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>0.3543307086614173</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>0.4019292604501608</v>
+        <v>0.6479099678456591</v>
       </c>
       <c r="T14" t="n">
-        <v>0.5736925515055468</v>
+        <v>0.9619651347068146</v>
       </c>
       <c r="U14" t="n">
-        <v>0.5366242038216561</v>
+        <v>0.9856687898089171</v>
       </c>
       <c r="V14" t="n">
         <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>0.286833855799373</v>
+        <v>0.5658307210031348</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>0.5208333333333334</v>
       </c>
       <c r="Y14" t="n">
-        <v>1</v>
+        <v>0.7507936507936508</v>
       </c>
       <c r="Z14" t="n">
-        <v>0.4124203821656051</v>
+        <v>0.7914012738853503</v>
       </c>
       <c r="AA14" t="n">
-        <v>0.07843137254901961</v>
+        <v>0.4901960784313725</v>
       </c>
       <c r="AB14" t="n">
-        <v>0.07928802588996764</v>
+        <v>0.5048543689320388</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>0.4059900166389351</v>
       </c>
       <c r="AD14" t="n">
-        <v>0.9905511811023622</v>
+        <v>0.5023622047244094</v>
       </c>
       <c r="AE14" t="n">
-        <v>0.06151419558359621</v>
+        <v>0.5047318611987381</v>
       </c>
       <c r="AF14" t="n">
-        <v>0.07355242566510173</v>
+        <v>0.5164319248826291</v>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>0.4984177215189873</v>
       </c>
       <c r="AH14" t="n">
-        <v>0</v>
+        <v>0.22508038585209</v>
       </c>
       <c r="AI14" t="n">
-        <v>1</v>
+        <v>0.5087719298245614</v>
       </c>
       <c r="AJ14" t="n">
-        <v>1</v>
+        <v>0.5111464968152867</v>
       </c>
       <c r="AK14" t="n">
-        <v>0.9750390015600624</v>
+        <v>0.4960998439937597</v>
       </c>
       <c r="AL14" t="n">
-        <v>0.9875968992248062</v>
+        <v>0.7364341085271318</v>
       </c>
       <c r="AM14" t="n">
-        <v>1</v>
+        <v>0.5251141552511416</v>
       </c>
       <c r="AN14" t="n">
-        <v>0.1271860095389507</v>
+        <v>0.931637519872814</v>
       </c>
       <c r="AO14" t="n">
-        <v>0</v>
+        <v>0.2186046511627907</v>
       </c>
       <c r="AP14" t="n">
-        <v>0.001574803149606299</v>
+        <v>0.3574803149606299</v>
       </c>
       <c r="AQ14" t="n">
-        <v>0</v>
+        <v>0.06955177743431221</v>
       </c>
       <c r="AR14" t="n">
-        <v>0</v>
+        <v>0.4721362229102167</v>
       </c>
       <c r="AS14" t="n">
-        <v>0.05144694533762058</v>
+        <v>0.6495176848874598</v>
       </c>
       <c r="AT14" t="n">
-        <v>1</v>
+        <v>0.6687797147385103</v>
       </c>
       <c r="AU14" t="n">
-        <v>0</v>
+        <v>0.2688</v>
       </c>
       <c r="AV14" t="n">
-        <v>0.4314641744548287</v>
+        <v>0.5467289719626168</v>
       </c>
       <c r="AW14" t="n">
-        <v>0.99836867862969</v>
+        <v>0.9216965742251223</v>
       </c>
       <c r="AX14" t="n">
-        <v>0</v>
+        <v>0.4719101123595505</v>
       </c>
       <c r="AY14" t="n">
-        <v>1</v>
+        <v>0.9365079365079365</v>
       </c>
     </row>
     <row r="15">
@@ -2733,16 +2733,16 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.9829457364341085</v>
+        <v>0.5395348837209303</v>
       </c>
       <c r="C15" t="n">
         <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>0.8996913580246914</v>
+        <v>0.4737654320987654</v>
       </c>
       <c r="E15" t="n">
-        <v>0.3847352024922118</v>
+        <v>0.5093457943925234</v>
       </c>
       <c r="F15" t="n">
         <v>0</v>
@@ -2751,13 +2751,13 @@
         <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>0.6066066066066066</v>
+        <v>1</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>0.9827044025157232</v>
+        <v>1</v>
       </c>
       <c r="K15" t="n">
         <v>0</v>
@@ -2766,10 +2766,10 @@
         <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>0.984472049689441</v>
+        <v>0.562111801242236</v>
       </c>
       <c r="N15" t="n">
-        <v>0.9843014128728415</v>
+        <v>0.4866562009419153</v>
       </c>
       <c r="O15" t="n">
         <v>1</v>
@@ -2778,109 +2778,109 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.01540832049306626</v>
+        <v>0.8921417565485362</v>
       </c>
       <c r="R15" t="n">
         <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>0.4276629570747218</v>
+        <v>0.1255961844197138</v>
       </c>
       <c r="T15" t="n">
-        <v>0.5903426791277259</v>
+        <v>0.456386292834891</v>
       </c>
       <c r="U15" t="n">
-        <v>0.5517774343122102</v>
+        <v>0.4327666151468315</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>0.3054263565891473</v>
+        <v>0.1069767441860465</v>
       </c>
       <c r="X15" t="n">
-        <v>0.0126984126984127</v>
+        <v>0.9857142857142858</v>
       </c>
       <c r="Y15" t="n">
-        <v>0.9875776397515528</v>
+        <v>0.2453416149068323</v>
       </c>
       <c r="Z15" t="n">
-        <v>0.434375</v>
+        <v>0.7203125</v>
       </c>
       <c r="AA15" t="n">
-        <v>0.1021069692058347</v>
+        <v>1</v>
       </c>
       <c r="AB15" t="n">
-        <v>0.09651898734177215</v>
+        <v>1</v>
       </c>
       <c r="AC15" t="n">
-        <v>0.0127591706539075</v>
+        <v>0.9234449760765551</v>
       </c>
       <c r="AD15" t="n">
         <v>1</v>
       </c>
       <c r="AE15" t="n">
-        <v>0.07266982622432859</v>
+        <v>1</v>
       </c>
       <c r="AF15" t="n">
-        <v>0.09782608695652174</v>
+        <v>1</v>
       </c>
       <c r="AG15" t="n">
-        <v>0.01057401812688822</v>
+        <v>1</v>
       </c>
       <c r="AH15" t="n">
-        <v>0.003129890453834116</v>
+        <v>0.004694835680751174</v>
       </c>
       <c r="AI15" t="n">
         <v>1</v>
       </c>
       <c r="AJ15" t="n">
-        <v>0.9841269841269841</v>
+        <v>1</v>
       </c>
       <c r="AK15" t="n">
         <v>1</v>
       </c>
       <c r="AL15" t="n">
-        <v>1</v>
+        <v>0.7538940809968847</v>
       </c>
       <c r="AM15" t="n">
-        <v>0.9834586466165414</v>
+        <v>0.9759398496240601</v>
       </c>
       <c r="AN15" t="n">
-        <v>0.125193199381762</v>
+        <v>0.5162287480680062</v>
       </c>
       <c r="AO15" t="n">
         <v>0.00303030303030303</v>
       </c>
       <c r="AP15" t="n">
-        <v>0.00778816199376947</v>
+        <v>0.8520249221183801</v>
       </c>
       <c r="AQ15" t="n">
-        <v>0</v>
+        <v>0.004497751124437781</v>
       </c>
       <c r="AR15" t="n">
-        <v>0.01536098310291859</v>
+        <v>1</v>
       </c>
       <c r="AS15" t="n">
-        <v>0.07606973058637084</v>
+        <v>0.1489698890649762</v>
       </c>
       <c r="AT15" t="n">
-        <v>0.984399375975039</v>
+        <v>0.1419656786271451</v>
       </c>
       <c r="AU15" t="n">
-        <v>0</v>
+        <v>0.001584786053882726</v>
       </c>
       <c r="AV15" t="n">
-        <v>0.4608294930875576</v>
+        <v>0.07526881720430108</v>
       </c>
       <c r="AW15" t="n">
-        <v>0.9889937106918238</v>
+        <v>0.5707547169811321</v>
       </c>
       <c r="AX15" t="n">
-        <v>0.01572327044025157</v>
+        <v>1</v>
       </c>
       <c r="AY15" t="n">
-        <v>0.9891135303265941</v>
+        <v>0.5349922239502333</v>
       </c>
     </row>
     <row r="16">
@@ -2893,7 +2893,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>1</v>
+        <v>0.984</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
@@ -2902,22 +2902,22 @@
         <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>1</v>
+        <v>0.9508716323296355</v>
       </c>
       <c r="G16" t="n">
-        <v>1</v>
+        <v>0.9902597402597403</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
       </c>
       <c r="I16" t="n">
-        <v>1</v>
+        <v>0.985981308411215</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>1</v>
+        <v>0.9935064935064936</v>
       </c>
       <c r="L16" t="n">
         <v>1</v>
@@ -2935,13 +2935,13 @@
         <v>1</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>0.0192</v>
       </c>
       <c r="R16" t="n">
-        <v>1</v>
+        <v>0.982200647249191</v>
       </c>
       <c r="S16" t="n">
-        <v>0.003246753246753247</v>
+        <v>0.00487012987012987</v>
       </c>
       <c r="T16" t="n">
         <v>0</v>
@@ -2950,10 +2950,10 @@
         <v>0</v>
       </c>
       <c r="V16" t="n">
-        <v>1</v>
+        <v>0.9828926905132193</v>
       </c>
       <c r="W16" t="n">
-        <v>0.1637519872813991</v>
+        <v>0.004769475357710651</v>
       </c>
       <c r="X16" t="n">
         <v>0</v>
@@ -2971,7 +2971,7 @@
         <v>0</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>0.003294892915980231</v>
       </c>
       <c r="AD16" t="n">
         <v>0</v>
@@ -2986,7 +2986,7 @@
         <v>0</v>
       </c>
       <c r="AH16" t="n">
-        <v>0.9890453834115805</v>
+        <v>0.2676056338028169</v>
       </c>
       <c r="AI16" t="n">
         <v>0</v>
@@ -3007,28 +3007,28 @@
         <v>0</v>
       </c>
       <c r="AO16" t="n">
-        <v>0.9891975308641975</v>
+        <v>0.2993827160493827</v>
       </c>
       <c r="AP16" t="n">
-        <v>0</v>
+        <v>0.0208</v>
       </c>
       <c r="AQ16" t="n">
-        <v>0.9953488372093023</v>
+        <v>0.4837209302325581</v>
       </c>
       <c r="AR16" t="n">
         <v>0</v>
       </c>
       <c r="AS16" t="n">
-        <v>0</v>
+        <v>0.001610305958132045</v>
       </c>
       <c r="AT16" t="n">
-        <v>0</v>
+        <v>0.0016</v>
       </c>
       <c r="AU16" t="n">
-        <v>0.9936204146730463</v>
+        <v>0.2599681020733652</v>
       </c>
       <c r="AV16" t="n">
-        <v>0</v>
+        <v>0.01257861635220126</v>
       </c>
       <c r="AW16" t="n">
         <v>0</v>
@@ -3047,154 +3047,154 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0</v>
+        <v>0.4204018547140649</v>
       </c>
       <c r="C17" t="n">
-        <v>0</v>
+        <v>0.007874015748031496</v>
       </c>
       <c r="D17" t="n">
-        <v>0.0600924499229584</v>
+        <v>0.3697996918335901</v>
       </c>
       <c r="E17" t="n">
-        <v>0.598116169544741</v>
+        <v>0.3830455259026688</v>
       </c>
       <c r="F17" t="n">
-        <v>0</v>
+        <v>0.0108359133126935</v>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>0.004754358161648178</v>
       </c>
       <c r="H17" t="n">
-        <v>0.4181547619047619</v>
+        <v>0.8839285714285714</v>
       </c>
       <c r="I17" t="n">
-        <v>0</v>
+        <v>0.006269592476489028</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>0.8880248833592534</v>
       </c>
       <c r="K17" t="n">
-        <v>0</v>
+        <v>0.001607717041800643</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>0.001567398119122257</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>0.4339035769828927</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>0.3543307086614173</v>
       </c>
       <c r="O17" t="n">
-        <v>0.01540832049306626</v>
+        <v>0.8921417565485362</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>0.0192</v>
       </c>
       <c r="Q17" t="n">
         <v>1</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>0.00782472613458529</v>
       </c>
       <c r="S17" t="n">
-        <v>0.5191693290734825</v>
+        <v>0.04952076677316294</v>
       </c>
       <c r="T17" t="n">
-        <v>0.357032457496136</v>
+        <v>0.3369397217928903</v>
       </c>
       <c r="U17" t="n">
-        <v>0.3931357254290171</v>
+        <v>0.3260530421216848</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>0.007633587786259542</v>
       </c>
       <c r="W17" t="n">
-        <v>0.4968944099378882</v>
+        <v>0.04813664596273292</v>
       </c>
       <c r="X17" t="n">
-        <v>1</v>
+        <v>0.875</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>0.1411042944785276</v>
       </c>
       <c r="Z17" t="n">
-        <v>0.5780525502318392</v>
+        <v>0.5935085007727975</v>
       </c>
       <c r="AA17" t="n">
-        <v>0.9012738853503185</v>
+        <v>0.89171974522293</v>
       </c>
       <c r="AB17" t="n">
-        <v>0.9017713365539453</v>
+        <v>0.8808373590982287</v>
       </c>
       <c r="AC17" t="n">
-        <v>1</v>
+        <v>0.9278846153846154</v>
       </c>
       <c r="AD17" t="n">
-        <v>0.009216589861751152</v>
+        <v>0.8755760368663594</v>
       </c>
       <c r="AE17" t="n">
-        <v>0.9287925696594427</v>
+        <v>0.8761609907120743</v>
       </c>
       <c r="AF17" t="n">
-        <v>0.9069767441860465</v>
+        <v>0.8728682170542635</v>
       </c>
       <c r="AG17" t="n">
-        <v>1</v>
+        <v>0.8931297709923665</v>
       </c>
       <c r="AH17" t="n">
-        <v>0.01417322834645669</v>
+        <v>0.1133858267716535</v>
       </c>
       <c r="AI17" t="n">
-        <v>0</v>
+        <v>0.8757861635220126</v>
       </c>
       <c r="AJ17" t="n">
-        <v>0</v>
+        <v>0.8770226537216829</v>
       </c>
       <c r="AK17" t="n">
-        <v>0.02180685358255452</v>
+        <v>0.9003115264797508</v>
       </c>
       <c r="AL17" t="n">
-        <v>0.0108359133126935</v>
+        <v>0.6191950464396285</v>
       </c>
       <c r="AM17" t="n">
-        <v>0</v>
+        <v>0.8649468892261002</v>
       </c>
       <c r="AN17" t="n">
-        <v>0.8627145085803433</v>
+        <v>0.3946957878315133</v>
       </c>
       <c r="AO17" t="n">
-        <v>0.01070336391437309</v>
+        <v>0.09021406727828746</v>
       </c>
       <c r="AP17" t="n">
-        <v>0.9984375</v>
+        <v>1</v>
       </c>
       <c r="AQ17" t="n">
-        <v>0.0060790273556231</v>
+        <v>0.1291793313069909</v>
       </c>
       <c r="AR17" t="n">
-        <v>1</v>
+        <v>0.9041731066460588</v>
       </c>
       <c r="AS17" t="n">
-        <v>0.9300476947535771</v>
+        <v>0.05405405405405406</v>
       </c>
       <c r="AT17" t="n">
-        <v>0</v>
+        <v>0.05817610062893082</v>
       </c>
       <c r="AU17" t="n">
-        <v>0.007961783439490446</v>
+        <v>0.06847133757961783</v>
       </c>
       <c r="AV17" t="n">
-        <v>0.5301391035548686</v>
+        <v>0.04482225656877898</v>
       </c>
       <c r="AW17" t="n">
-        <v>0.0016</v>
+        <v>0.4528</v>
       </c>
       <c r="AX17" t="n">
-        <v>1</v>
+        <v>0.903125</v>
       </c>
       <c r="AY17" t="n">
-        <v>0</v>
+        <v>0.4101382488479263</v>
       </c>
     </row>
     <row r="18">
@@ -3216,7 +3216,7 @@
         <v>0</v>
       </c>
       <c r="F18" t="n">
-        <v>1</v>
+        <v>0.9319620253164557</v>
       </c>
       <c r="G18" t="n">
         <v>1</v>
@@ -3246,16 +3246,16 @@
         <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>1</v>
+        <v>0.982200647249191</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>0.00782472613458529</v>
       </c>
       <c r="R18" t="n">
         <v>1</v>
       </c>
       <c r="S18" t="n">
-        <v>0.005008347245409015</v>
+        <v>0</v>
       </c>
       <c r="T18" t="n">
         <v>0</v>
@@ -3267,7 +3267,7 @@
         <v>1</v>
       </c>
       <c r="W18" t="n">
-        <v>0.1669316375198728</v>
+        <v>0.003179650238473768</v>
       </c>
       <c r="X18" t="n">
         <v>0</v>
@@ -3300,7 +3300,7 @@
         <v>0</v>
       </c>
       <c r="AH18" t="n">
-        <v>0.9823151125401929</v>
+        <v>0.2122186495176849</v>
       </c>
       <c r="AI18" t="n">
         <v>0</v>
@@ -3321,13 +3321,13 @@
         <v>0</v>
       </c>
       <c r="AO18" t="n">
-        <v>0.984472049689441</v>
+        <v>0.2453416149068323</v>
       </c>
       <c r="AP18" t="n">
-        <v>0</v>
+        <v>0.003231017770597738</v>
       </c>
       <c r="AQ18" t="n">
-        <v>0.9938271604938271</v>
+        <v>0.4104938271604938</v>
       </c>
       <c r="AR18" t="n">
         <v>0</v>
@@ -3339,10 +3339,10 @@
         <v>0</v>
       </c>
       <c r="AU18" t="n">
-        <v>0.9902120717781403</v>
+        <v>0.2088091353996737</v>
       </c>
       <c r="AV18" t="n">
-        <v>0</v>
+        <v>0.003149606299212598</v>
       </c>
       <c r="AW18" t="n">
         <v>0</v>
@@ -3361,154 +3361,154 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.4003189792663477</v>
+        <v>0.5869218500797448</v>
       </c>
       <c r="C19" t="n">
-        <v>0.004862236628849271</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>0.6028938906752411</v>
+        <v>0.6463022508038585</v>
       </c>
       <c r="E19" t="n">
-        <v>0.9459901800327333</v>
+        <v>0.6284779050736498</v>
       </c>
       <c r="F19" t="n">
-        <v>0.003184713375796179</v>
+        <v>0.03662420382165605</v>
       </c>
       <c r="G19" t="n">
+        <v>0</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0.1326053042121685</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0.1176470588235294</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0.560064935064935</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0.6479099678456591</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0.1255961844197138</v>
+      </c>
+      <c r="P19" t="n">
         <v>0.00487012987012987</v>
       </c>
-      <c r="H19" t="n">
-        <v>0.4617784711388456</v>
-      </c>
-      <c r="I19" t="n">
-        <v>0.00482315112540193</v>
-      </c>
-      <c r="J19" t="n">
-        <v>0.434640522875817</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0.004918032786885246</v>
-      </c>
-      <c r="L19" t="n">
-        <v>0.003252032520325203</v>
-      </c>
-      <c r="M19" t="n">
-        <v>0.4626623376623377</v>
-      </c>
-      <c r="N19" t="n">
-        <v>0.4019292604501608</v>
-      </c>
-      <c r="O19" t="n">
-        <v>0.4276629570747218</v>
-      </c>
-      <c r="P19" t="n">
-        <v>0.003246753246753247</v>
-      </c>
       <c r="Q19" t="n">
-        <v>0.5191693290734825</v>
+        <v>0.04952076677316294</v>
       </c>
       <c r="R19" t="n">
-        <v>0.005008347245409015</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
         <v>1</v>
       </c>
       <c r="T19" t="n">
-        <v>0.9758842443729904</v>
+        <v>0.6672025723472669</v>
       </c>
       <c r="U19" t="n">
-        <v>0.9760383386581469</v>
+        <v>0.6869009584664537</v>
       </c>
       <c r="V19" t="n">
-        <v>0.004784688995215311</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>0.9427168576104746</v>
+        <v>1</v>
       </c>
       <c r="X19" t="n">
-        <v>0.5264</v>
+        <v>0.1456</v>
       </c>
       <c r="Y19" t="n">
-        <v>0.4374009508716323</v>
+        <v>0.9318541996830428</v>
       </c>
       <c r="Z19" t="n">
-        <v>0.4429967426710097</v>
+        <v>0.4283387622149837</v>
       </c>
       <c r="AA19" t="n">
-        <v>0.5779967159277504</v>
+        <v>0.1247947454844007</v>
       </c>
       <c r="AB19" t="n">
-        <v>0.5721311475409836</v>
+        <v>0.140983606557377</v>
       </c>
       <c r="AC19" t="n">
-        <v>0.5091819699499165</v>
+        <v>0.1185308848080134</v>
       </c>
       <c r="AD19" t="n">
-        <v>0.4465709728867623</v>
+        <v>0.1291866028708134</v>
       </c>
       <c r="AE19" t="n">
-        <v>0.5702746365105008</v>
+        <v>0.1405492730210016</v>
       </c>
       <c r="AF19" t="n">
-        <v>0.5696</v>
+        <v>0.1376</v>
       </c>
       <c r="AG19" t="n">
-        <v>0.5285714285714286</v>
+        <v>0.126984126984127</v>
       </c>
       <c r="AH19" t="n">
-        <v>0.01623376623376623</v>
+        <v>0.5957792207792207</v>
       </c>
       <c r="AI19" t="n">
-        <v>0.4204545454545455</v>
+        <v>0.1314935064935065</v>
       </c>
       <c r="AJ19" t="n">
-        <v>0.4223300970873786</v>
+        <v>0.1407766990291262</v>
       </c>
       <c r="AK19" t="n">
-        <v>0.4317817014446228</v>
+        <v>0.1171749598715891</v>
       </c>
       <c r="AL19" t="n">
-        <v>0.4281098546042003</v>
+        <v>0.3909531502423264</v>
       </c>
       <c r="AM19" t="n">
-        <v>0.4134165366614664</v>
+        <v>0.15600624024961</v>
       </c>
       <c r="AN19" t="n">
-        <v>0.717741935483871</v>
+        <v>0.617741935483871</v>
       </c>
       <c r="AO19" t="n">
-        <v>0.01901743264659271</v>
+        <v>0.5625990491283677</v>
       </c>
       <c r="AP19" t="n">
-        <v>0.5418006430868167</v>
+        <v>0.0707395498392283</v>
       </c>
       <c r="AQ19" t="n">
-        <v>0.006211180124223602</v>
+        <v>0.391304347826087</v>
       </c>
       <c r="AR19" t="n">
-        <v>0.534621578099839</v>
+        <v>0.1175523349436393</v>
       </c>
       <c r="AS19" t="n">
-        <v>0.6183574879227053</v>
+        <v>1</v>
       </c>
       <c r="AT19" t="n">
-        <v>0.417741935483871</v>
+        <v>0.9983870967741936</v>
       </c>
       <c r="AU19" t="n">
-        <v>0.01140065146579805</v>
+        <v>0.6351791530944625</v>
       </c>
       <c r="AV19" t="n">
-        <v>0.8763693270735524</v>
+        <v>0.9765258215962441</v>
       </c>
       <c r="AW19" t="n">
-        <v>0.4444444444444444</v>
+        <v>0.5555555555555556</v>
       </c>
       <c r="AX19" t="n">
-        <v>0.532051282051282</v>
+        <v>0.1201923076923077</v>
       </c>
       <c r="AY19" t="n">
-        <v>0.4391025641025641</v>
+        <v>0.592948717948718</v>
       </c>
     </row>
     <row r="20">
@@ -3518,16 +3518,16 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.5890625</v>
+        <v>0.984375</v>
       </c>
       <c r="C20" t="n">
         <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>0.7464788732394366</v>
+        <v>1</v>
       </c>
       <c r="E20" t="n">
-        <v>0.8164556962025317</v>
+        <v>0.9968354430379747</v>
       </c>
       <c r="F20" t="n">
         <v>0</v>
@@ -3536,13 +3536,13 @@
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>0.482442748091603</v>
+        <v>0.4809160305343512</v>
       </c>
       <c r="I20" t="n">
         <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>0.6075949367088608</v>
+        <v>0.4651898734177215</v>
       </c>
       <c r="K20" t="n">
         <v>0</v>
@@ -3551,25 +3551,25 @@
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>0.6238244514106583</v>
+        <v>0.9137931034482759</v>
       </c>
       <c r="N20" t="n">
-        <v>0.5736925515055468</v>
+        <v>0.9619651347068146</v>
       </c>
       <c r="O20" t="n">
-        <v>0.5903426791277259</v>
+        <v>0.456386292834891</v>
       </c>
       <c r="P20" t="n">
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.357032457496136</v>
+        <v>0.3369397217928903</v>
       </c>
       <c r="R20" t="n">
         <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>0.9758842443729904</v>
+        <v>0.6672025723472669</v>
       </c>
       <c r="T20" t="n">
         <v>1</v>
@@ -3581,91 +3581,91 @@
         <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>0.7279874213836478</v>
+        <v>0.5833333333333334</v>
       </c>
       <c r="X20" t="n">
-        <v>0.3513513513513514</v>
+        <v>0.4992050874403816</v>
       </c>
       <c r="Y20" t="n">
-        <v>0.6118935837245696</v>
+        <v>0.7543035993740219</v>
       </c>
       <c r="Z20" t="n">
-        <v>0.4094488188976378</v>
+        <v>0.8362204724409449</v>
       </c>
       <c r="AA20" t="n">
-        <v>0.4498381877022654</v>
+        <v>0.4724919093851133</v>
       </c>
       <c r="AB20" t="n">
-        <v>0.4315286624203822</v>
+        <v>0.4856687898089172</v>
       </c>
       <c r="AC20" t="n">
-        <v>0.3440514469453376</v>
+        <v>0.3938906752411576</v>
       </c>
       <c r="AD20" t="n">
-        <v>0.6105100463678517</v>
+        <v>0.4744976816074188</v>
       </c>
       <c r="AE20" t="n">
-        <v>0.4207221350078493</v>
+        <v>0.478806907378336</v>
       </c>
       <c r="AF20" t="n">
-        <v>0.425</v>
+        <v>0.490625</v>
       </c>
       <c r="AG20" t="n">
-        <v>0.3543913713405239</v>
+        <v>0.4668721109399075</v>
       </c>
       <c r="AH20" t="n">
-        <v>0.01114649681528662</v>
+        <v>0.2340764331210191</v>
       </c>
       <c r="AI20" t="n">
-        <v>0.5921259842519685</v>
+        <v>0.4755905511811024</v>
       </c>
       <c r="AJ20" t="n">
-        <v>0.5906902086677368</v>
+        <v>0.4895666131621188</v>
       </c>
       <c r="AK20" t="n">
-        <v>0.5863708399366085</v>
+        <v>0.4564183835182251</v>
       </c>
       <c r="AL20" t="n">
-        <v>0.5987460815047022</v>
+        <v>0.7695924764890282</v>
       </c>
       <c r="AM20" t="n">
-        <v>0.5987933634992458</v>
+        <v>0.5037707390648567</v>
       </c>
       <c r="AN20" t="n">
-        <v>0.5458860759493671</v>
+        <v>0.9857594936708861</v>
       </c>
       <c r="AO20" t="n">
-        <v>0.01393188854489164</v>
+        <v>0.2321981424148607</v>
       </c>
       <c r="AP20" t="n">
-        <v>0.3789308176100629</v>
+        <v>0.3191823899371069</v>
       </c>
       <c r="AQ20" t="n">
-        <v>0.0045662100456621</v>
+        <v>0.0776255707762557</v>
       </c>
       <c r="AR20" t="n">
-        <v>0.3580246913580247</v>
+        <v>0.4567901234567901</v>
       </c>
       <c r="AS20" t="n">
-        <v>0.4647435897435898</v>
+        <v>0.6714743589743589</v>
       </c>
       <c r="AT20" t="n">
-        <v>0.5915492957746479</v>
+        <v>0.6807511737089202</v>
       </c>
       <c r="AU20" t="n">
-        <v>0.008025682182985553</v>
+        <v>0.2921348314606741</v>
       </c>
       <c r="AV20" t="n">
-        <v>0.7897196261682243</v>
+        <v>0.5887850467289719</v>
       </c>
       <c r="AW20" t="n">
-        <v>0.6236044657097288</v>
+        <v>0.9712918660287081</v>
       </c>
       <c r="AX20" t="n">
-        <v>0.3672496025437202</v>
+        <v>0.4578696343402226</v>
       </c>
       <c r="AY20" t="n">
-        <v>0.6111111111111112</v>
+        <v>0.9861111111111112</v>
       </c>
     </row>
     <row r="21">
@@ -3675,16 +3675,16 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.5313935681470138</v>
+        <v>0.9846860643185299</v>
       </c>
       <c r="C21" t="n">
         <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>0.6953846153846154</v>
+        <v>1</v>
       </c>
       <c r="E21" t="n">
-        <v>0.8271604938271605</v>
+        <v>0.9953703703703703</v>
       </c>
       <c r="F21" t="n">
         <v>0</v>
@@ -3693,13 +3693,13 @@
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>0.4887218045112782</v>
+        <v>0.4556390977443609</v>
       </c>
       <c r="I21" t="n">
         <v>0</v>
       </c>
       <c r="J21" t="n">
-        <v>0.5694006309148265</v>
+        <v>0.4400630914826498</v>
       </c>
       <c r="K21" t="n">
         <v>0</v>
@@ -3708,25 +3708,25 @@
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>0.5856697819314641</v>
+        <v>0.9221183800623053</v>
       </c>
       <c r="N21" t="n">
-        <v>0.5366242038216561</v>
+        <v>0.9856687898089171</v>
       </c>
       <c r="O21" t="n">
-        <v>0.5517774343122102</v>
+        <v>0.4327666151468315</v>
       </c>
       <c r="P21" t="n">
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.3931357254290171</v>
+        <v>0.3260530421216848</v>
       </c>
       <c r="R21" t="n">
         <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>0.9760383386581469</v>
+        <v>0.6869009584664537</v>
       </c>
       <c r="T21" t="n">
         <v>1</v>
@@ -3738,91 +3738,91 @@
         <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>0.7546875</v>
+        <v>0.5953125</v>
       </c>
       <c r="X21" t="n">
-        <v>0.4065934065934066</v>
+        <v>0.478806907378336</v>
       </c>
       <c r="Y21" t="n">
-        <v>0.5683229813664596</v>
+        <v>0.7608695652173914</v>
       </c>
       <c r="Z21" t="n">
-        <v>0.4335443037974683</v>
+        <v>0.8306962025316456</v>
       </c>
       <c r="AA21" t="n">
-        <v>0.4855305466237942</v>
+        <v>0.4453376205787781</v>
       </c>
       <c r="AB21" t="n">
-        <v>0.4729299363057325</v>
+        <v>0.4601910828025478</v>
       </c>
       <c r="AC21" t="n">
-        <v>0.3754045307443366</v>
+        <v>0.3608414239482201</v>
       </c>
       <c r="AD21" t="n">
-        <v>0.576271186440678</v>
+        <v>0.4468412942989214</v>
       </c>
       <c r="AE21" t="n">
-        <v>0.4758942457231726</v>
+        <v>0.4494556765163297</v>
       </c>
       <c r="AF21" t="n">
-        <v>0.4738461538461539</v>
+        <v>0.4661538461538461</v>
       </c>
       <c r="AG21" t="n">
-        <v>0.3931888544891641</v>
+        <v>0.434984520123839</v>
       </c>
       <c r="AH21" t="n">
-        <v>0.004665629860031105</v>
+        <v>0.23950233281493</v>
       </c>
       <c r="AI21" t="n">
-        <v>0.5566037735849056</v>
+        <v>0.4544025157232705</v>
       </c>
       <c r="AJ21" t="n">
-        <v>0.5433070866141733</v>
+        <v>0.4582677165354331</v>
       </c>
       <c r="AK21" t="n">
-        <v>0.5508607198748043</v>
+        <v>0.4303599374021909</v>
       </c>
       <c r="AL21" t="n">
-        <v>0.5624036979969184</v>
+        <v>0.7565485362095532</v>
       </c>
       <c r="AM21" t="n">
-        <v>0.5603576751117735</v>
+        <v>0.481371087928465</v>
       </c>
       <c r="AN21" t="n">
-        <v>0.5636645962732919</v>
+        <v>0.9829192546583851</v>
       </c>
       <c r="AO21" t="n">
-        <v>0.01062215477996965</v>
+        <v>0.2367223065250379</v>
       </c>
       <c r="AP21" t="n">
-        <v>0.4231974921630094</v>
+        <v>0.3150470219435736</v>
       </c>
       <c r="AQ21" t="n">
-        <v>0</v>
+        <v>0.0791476407914764</v>
       </c>
       <c r="AR21" t="n">
-        <v>0.4036697247706422</v>
+        <v>0.4296636085626911</v>
       </c>
       <c r="AS21" t="n">
-        <v>0.5071542130365659</v>
+        <v>0.6915739268680445</v>
       </c>
       <c r="AT21" t="n">
-        <v>0.5518867924528302</v>
+        <v>0.699685534591195</v>
       </c>
       <c r="AU21" t="n">
-        <v>0.006349206349206349</v>
+        <v>0.2952380952380952</v>
       </c>
       <c r="AV21" t="n">
-        <v>0.7987616099071208</v>
+        <v>0.5990712074303406</v>
       </c>
       <c r="AW21" t="n">
-        <v>0.5739268680445151</v>
+        <v>0.9682034976152624</v>
       </c>
       <c r="AX21" t="n">
-        <v>0.4018987341772152</v>
+        <v>0.4272151898734177</v>
       </c>
       <c r="AY21" t="n">
-        <v>0.5701078582434514</v>
+        <v>0.9815100154083205</v>
       </c>
     </row>
     <row r="22">
@@ -3844,7 +3844,7 @@
         <v>0</v>
       </c>
       <c r="F22" t="n">
-        <v>1</v>
+        <v>0.9355828220858896</v>
       </c>
       <c r="G22" t="n">
         <v>1</v>
@@ -3874,16 +3874,16 @@
         <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>1</v>
+        <v>0.9828926905132193</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>0.007633587786259542</v>
       </c>
       <c r="R22" t="n">
         <v>1</v>
       </c>
       <c r="S22" t="n">
-        <v>0.004784688995215311</v>
+        <v>0</v>
       </c>
       <c r="T22" t="n">
         <v>0</v>
@@ -3895,7 +3895,7 @@
         <v>1</v>
       </c>
       <c r="W22" t="n">
-        <v>0.1602465331278891</v>
+        <v>0.003081664098613251</v>
       </c>
       <c r="X22" t="n">
         <v>0</v>
@@ -3928,7 +3928,7 @@
         <v>0</v>
       </c>
       <c r="AH22" t="n">
-        <v>0.9875968992248062</v>
+        <v>0.2232558139534884</v>
       </c>
       <c r="AI22" t="n">
         <v>0</v>
@@ -3949,13 +3949,13 @@
         <v>0</v>
       </c>
       <c r="AO22" t="n">
-        <v>0.9878603945371776</v>
+        <v>0.2564491654021244</v>
       </c>
       <c r="AP22" t="n">
-        <v>0</v>
+        <v>0.004651162790697674</v>
       </c>
       <c r="AQ22" t="n">
-        <v>0.9955156950672646</v>
+        <v>0.4170403587443946</v>
       </c>
       <c r="AR22" t="n">
         <v>0</v>
@@ -3967,10 +3967,10 @@
         <v>0</v>
       </c>
       <c r="AU22" t="n">
-        <v>0.9921259842519685</v>
+        <v>0.2125984251968504</v>
       </c>
       <c r="AV22" t="n">
-        <v>0</v>
+        <v>0.00302571860816944</v>
       </c>
       <c r="AW22" t="n">
         <v>0</v>
@@ -3989,154 +3989,154 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.2782071097372488</v>
+        <v>0.5023183925811437</v>
       </c>
       <c r="C23" t="n">
-        <v>0.1650793650793651</v>
+        <v>0.003174603174603175</v>
       </c>
       <c r="D23" t="n">
-        <v>0.4427001569858713</v>
+        <v>0.554160125588697</v>
       </c>
       <c r="E23" t="n">
-        <v>0.8411949685534591</v>
+        <v>0.539308176100629</v>
       </c>
       <c r="F23" t="n">
-        <v>0.1546875</v>
+        <v>0.0515625</v>
       </c>
       <c r="G23" t="n">
-        <v>0.1576433121019108</v>
+        <v>0.003184713375796179</v>
       </c>
       <c r="H23" t="n">
-        <v>0.4</v>
+        <v>0.1181818181818182</v>
       </c>
       <c r="I23" t="n">
-        <v>0.1658914728682171</v>
+        <v>0.00310077519379845</v>
       </c>
       <c r="J23" t="n">
-        <v>0.3004694835680751</v>
+        <v>0.107981220657277</v>
       </c>
       <c r="K23" t="n">
-        <v>0.1624203821656051</v>
+        <v>0.003184713375796179</v>
       </c>
       <c r="L23" t="n">
-        <v>0.1578125</v>
+        <v>0.003125</v>
       </c>
       <c r="M23" t="n">
-        <v>0.321259842519685</v>
+        <v>0.4992125984251968</v>
       </c>
       <c r="N23" t="n">
-        <v>0.286833855799373</v>
+        <v>0.5658307210031348</v>
       </c>
       <c r="O23" t="n">
-        <v>0.3054263565891473</v>
+        <v>0.1069767441860465</v>
       </c>
       <c r="P23" t="n">
-        <v>0.1637519872813991</v>
+        <v>0.004769475357710651</v>
       </c>
       <c r="Q23" t="n">
-        <v>0.4968944099378882</v>
+        <v>0.04813664596273292</v>
       </c>
       <c r="R23" t="n">
-        <v>0.1669316375198728</v>
+        <v>0.003179650238473768</v>
       </c>
       <c r="S23" t="n">
-        <v>0.9427168576104746</v>
+        <v>1</v>
       </c>
       <c r="T23" t="n">
-        <v>0.7279874213836478</v>
+        <v>0.5833333333333334</v>
       </c>
       <c r="U23" t="n">
-        <v>0.7546875</v>
+        <v>0.5953125</v>
       </c>
       <c r="V23" t="n">
-        <v>0.1602465331278891</v>
+        <v>0.003081664098613251</v>
       </c>
       <c r="W23" t="n">
         <v>1</v>
       </c>
       <c r="X23" t="n">
-        <v>0.5207006369426752</v>
+        <v>0.1305732484076433</v>
       </c>
       <c r="Y23" t="n">
-        <v>0.3087774294670846</v>
+        <v>0.9028213166144201</v>
       </c>
       <c r="Z23" t="n">
-        <v>0.405320813771518</v>
+        <v>0.3427230046948357</v>
       </c>
       <c r="AA23" t="n">
-        <v>0.5559105431309904</v>
+        <v>0.1070287539936102</v>
       </c>
       <c r="AB23" t="n">
-        <v>0.5445859872611465</v>
+        <v>0.1130573248407643</v>
       </c>
       <c r="AC23" t="n">
-        <v>0.5016129032258064</v>
+        <v>0.1145161290322581</v>
       </c>
       <c r="AD23" t="n">
-        <v>0.3183925811437404</v>
+        <v>0.115919629057187</v>
       </c>
       <c r="AE23" t="n">
-        <v>0.546875</v>
+        <v>0.1203125</v>
       </c>
       <c r="AF23" t="n">
-        <v>0.5539906103286385</v>
+        <v>0.1158059467918623</v>
       </c>
       <c r="AG23" t="n">
-        <v>0.5123076923076924</v>
+        <v>0.1092307692307692</v>
       </c>
       <c r="AH23" t="n">
-        <v>0.1751592356687898</v>
+        <v>0.6528662420382165</v>
       </c>
       <c r="AI23" t="n">
-        <v>0.2924528301886792</v>
+        <v>0.119496855345912</v>
       </c>
       <c r="AJ23" t="n">
-        <v>0.3004846526655897</v>
+        <v>0.1227786752827141</v>
       </c>
       <c r="AK23" t="n">
-        <v>0.3160377358490566</v>
+        <v>0.1006289308176101</v>
       </c>
       <c r="AL23" t="n">
-        <v>0.3046153846153846</v>
+        <v>0.3184615384615385</v>
       </c>
       <c r="AM23" t="n">
-        <v>0.2870090634441088</v>
+        <v>0.1329305135951662</v>
       </c>
       <c r="AN23" t="n">
-        <v>0.6505460218408736</v>
+        <v>0.5288611544461779</v>
       </c>
       <c r="AO23" t="n">
-        <v>0.184331797235023</v>
+        <v>0.6374807987711214</v>
       </c>
       <c r="AP23" t="n">
-        <v>0.5229067930489731</v>
+        <v>0.0679304897314376</v>
       </c>
       <c r="AQ23" t="n">
-        <v>0.1509715994020927</v>
+        <v>0.4618834080717489</v>
       </c>
       <c r="AR23" t="n">
-        <v>0.5207373271889401</v>
+        <v>0.1029185867895545</v>
       </c>
       <c r="AS23" t="n">
-        <v>0.5964912280701754</v>
+        <v>1</v>
       </c>
       <c r="AT23" t="n">
-        <v>0.2945859872611465</v>
+        <v>0.9952229299363057</v>
       </c>
       <c r="AU23" t="n">
-        <v>0.1598101265822785</v>
+        <v>0.6977848101265823</v>
       </c>
       <c r="AV23" t="n">
-        <v>0.8268330733229329</v>
+        <v>0.9859594383775351</v>
       </c>
       <c r="AW23" t="n">
-        <v>0.303370786516854</v>
+        <v>0.463884430176565</v>
       </c>
       <c r="AX23" t="n">
-        <v>0.5182829888712241</v>
+        <v>0.08744038155802862</v>
       </c>
       <c r="AY23" t="n">
-        <v>0.3052959501557632</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="24">
@@ -4146,16 +4146,16 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0</v>
+        <v>0.5796875</v>
       </c>
       <c r="C24" t="n">
         <v>0</v>
       </c>
       <c r="D24" t="n">
-        <v>0.07740916271721959</v>
+        <v>0.5165876777251185</v>
       </c>
       <c r="E24" t="n">
-        <v>0.6130573248407644</v>
+        <v>0.5445859872611465</v>
       </c>
       <c r="F24" t="n">
         <v>0</v>
@@ -4164,13 +4164,13 @@
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>0.4226006191950464</v>
+        <v>0.9891640866873065</v>
       </c>
       <c r="I24" t="n">
         <v>0</v>
       </c>
       <c r="J24" t="n">
-        <v>0</v>
+        <v>0.9855769230769231</v>
       </c>
       <c r="K24" t="n">
         <v>0</v>
@@ -4179,121 +4179,121 @@
         <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>0.6129541864139021</v>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>0.5208333333333334</v>
       </c>
       <c r="O24" t="n">
-        <v>0.0126984126984127</v>
+        <v>0.9857142857142858</v>
       </c>
       <c r="P24" t="n">
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>1</v>
+        <v>0.875</v>
       </c>
       <c r="R24" t="n">
         <v>0</v>
       </c>
       <c r="S24" t="n">
-        <v>0.5264</v>
+        <v>0.1456</v>
       </c>
       <c r="T24" t="n">
-        <v>0.3513513513513514</v>
+        <v>0.4992050874403816</v>
       </c>
       <c r="U24" t="n">
-        <v>0.4065934065934066</v>
+        <v>0.478806907378336</v>
       </c>
       <c r="V24" t="n">
         <v>0</v>
       </c>
       <c r="W24" t="n">
-        <v>0.5207006369426752</v>
+        <v>0.1305732484076433</v>
       </c>
       <c r="X24" t="n">
         <v>1</v>
       </c>
       <c r="Y24" t="n">
-        <v>0</v>
+        <v>0.2750397456279809</v>
       </c>
       <c r="Z24" t="n">
-        <v>0.5908372827804107</v>
+        <v>0.7393364928909952</v>
       </c>
       <c r="AA24" t="n">
-        <v>0.9136807817589576</v>
+        <v>0.9869706840390879</v>
       </c>
       <c r="AB24" t="n">
+        <v>0.9853896103896104</v>
+      </c>
+      <c r="AC24" t="n">
         <v>0.913961038961039</v>
       </c>
-      <c r="AC24" t="n">
-        <v>1</v>
-      </c>
       <c r="AD24" t="n">
-        <v>0.009273570324574961</v>
+        <v>0.9845440494590417</v>
       </c>
       <c r="AE24" t="n">
-        <v>0.9388714733542319</v>
+        <v>0.9843260188087775</v>
       </c>
       <c r="AF24" t="n">
-        <v>0.9224683544303798</v>
+        <v>0.9889240506329114</v>
       </c>
       <c r="AG24" t="n">
-        <v>1</v>
+        <v>0.984472049689441</v>
       </c>
       <c r="AH24" t="n">
-        <v>0.01446945337620579</v>
+        <v>0.008038585209003215</v>
       </c>
       <c r="AI24" t="n">
-        <v>0</v>
+        <v>0.9821717990275527</v>
       </c>
       <c r="AJ24" t="n">
-        <v>0</v>
+        <v>0.9983498349834984</v>
       </c>
       <c r="AK24" t="n">
-        <v>0.02211690363349131</v>
+        <v>0.990521327014218</v>
       </c>
       <c r="AL24" t="n">
-        <v>0.009448818897637795</v>
+        <v>0.7637795275590551</v>
       </c>
       <c r="AM24" t="n">
-        <v>0</v>
+        <v>0.9602446483180428</v>
       </c>
       <c r="AN24" t="n">
-        <v>0.8641390205371248</v>
+        <v>0.5576619273301737</v>
       </c>
       <c r="AO24" t="n">
-        <v>0.01228878648233487</v>
+        <v>0.006144393241167435</v>
       </c>
       <c r="AP24" t="n">
-        <v>0.998422712933754</v>
+        <v>0.8422712933753943</v>
       </c>
       <c r="AQ24" t="n">
-        <v>0.004601226993865031</v>
+        <v>0.001533742331288344</v>
       </c>
       <c r="AR24" t="n">
-        <v>1</v>
+        <v>0.9858267716535433</v>
       </c>
       <c r="AS24" t="n">
-        <v>0.9419354838709677</v>
+        <v>0.1790322580645161</v>
       </c>
       <c r="AT24" t="n">
-        <v>0</v>
+        <v>0.1736334405144695</v>
       </c>
       <c r="AU24" t="n">
-        <v>0.009569377990430622</v>
+        <v>0.01116427432216906</v>
       </c>
       <c r="AV24" t="n">
-        <v>0.5361635220125787</v>
+        <v>0.08962264150943396</v>
       </c>
       <c r="AW24" t="n">
-        <v>0.001607717041800643</v>
+        <v>0.617363344051447</v>
       </c>
       <c r="AX24" t="n">
-        <v>1</v>
+        <v>0.9824000000000001</v>
       </c>
       <c r="AY24" t="n">
-        <v>0</v>
+        <v>0.5682888540031397</v>
       </c>
     </row>
     <row r="25">
@@ -4303,31 +4303,31 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>1</v>
+        <v>0.6835637480798771</v>
       </c>
       <c r="C25" t="n">
         <v>0</v>
       </c>
       <c r="D25" t="n">
-        <v>0.9183673469387755</v>
+        <v>0.7268445839874411</v>
       </c>
       <c r="E25" t="n">
-        <v>0.3694968553459119</v>
+        <v>0.7169811320754716</v>
       </c>
       <c r="F25" t="n">
-        <v>0</v>
+        <v>0.01713395638629283</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>0.5630630630630631</v>
+        <v>0.2597597597597597</v>
       </c>
       <c r="I25" t="n">
         <v>0</v>
       </c>
       <c r="J25" t="n">
-        <v>1</v>
+        <v>0.2413793103448276</v>
       </c>
       <c r="K25" t="n">
         <v>0</v>
@@ -4336,121 +4336,121 @@
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>1</v>
+        <v>0.7126984126984127</v>
       </c>
       <c r="N25" t="n">
-        <v>1</v>
+        <v>0.7507936507936508</v>
       </c>
       <c r="O25" t="n">
-        <v>0.9875776397515528</v>
+        <v>0.2453416149068323</v>
       </c>
       <c r="P25" t="n">
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>0.1411042944785276</v>
       </c>
       <c r="R25" t="n">
         <v>0</v>
       </c>
       <c r="S25" t="n">
-        <v>0.4374009508716323</v>
+        <v>0.9318541996830428</v>
       </c>
       <c r="T25" t="n">
-        <v>0.6118935837245696</v>
+        <v>0.7543035993740219</v>
       </c>
       <c r="U25" t="n">
-        <v>0.5683229813664596</v>
+        <v>0.7608695652173914</v>
       </c>
       <c r="V25" t="n">
         <v>0</v>
       </c>
       <c r="W25" t="n">
-        <v>0.3087774294670846</v>
+        <v>0.9028213166144201</v>
       </c>
       <c r="X25" t="n">
-        <v>0</v>
+        <v>0.2750397456279809</v>
       </c>
       <c r="Y25" t="n">
         <v>1</v>
       </c>
       <c r="Z25" t="n">
-        <v>0.4136858475894246</v>
+        <v>0.5396578538102644</v>
       </c>
       <c r="AA25" t="n">
-        <v>0.08972267536704731</v>
+        <v>0.2414355628058727</v>
       </c>
       <c r="AB25" t="n">
-        <v>0.08695652173913043</v>
+        <v>0.2592592592592592</v>
       </c>
       <c r="AC25" t="n">
-        <v>0</v>
+        <v>0.2173913043478261</v>
       </c>
       <c r="AD25" t="n">
-        <v>0.9922600619195047</v>
+        <v>0.260061919504644</v>
       </c>
       <c r="AE25" t="n">
-        <v>0.0565149136577708</v>
+        <v>0.2621664050235479</v>
       </c>
       <c r="AF25" t="n">
-        <v>0.07923930269413629</v>
+        <v>0.2662440570522979</v>
       </c>
       <c r="AG25" t="n">
-        <v>0</v>
+        <v>0.2553516819571865</v>
       </c>
       <c r="AH25" t="n">
-        <v>0.001569858712715856</v>
+        <v>0.4725274725274725</v>
       </c>
       <c r="AI25" t="n">
-        <v>1</v>
+        <v>0.2527301092043682</v>
       </c>
       <c r="AJ25" t="n">
-        <v>1</v>
+        <v>0.2588996763754045</v>
       </c>
       <c r="AK25" t="n">
-        <v>0.9779874213836478</v>
+        <v>0.2327044025157233</v>
       </c>
       <c r="AL25" t="n">
-        <v>0.9876543209876543</v>
+        <v>0.5077160493827161</v>
       </c>
       <c r="AM25" t="n">
-        <v>1</v>
+        <v>0.2762762762762763</v>
       </c>
       <c r="AN25" t="n">
-        <v>0.1230529595015576</v>
+        <v>0.7071651090342679</v>
       </c>
       <c r="AO25" t="n">
-        <v>0.003067484662576687</v>
+        <v>0.4355828220858896</v>
       </c>
       <c r="AP25" t="n">
-        <v>0</v>
+        <v>0.1518987341772152</v>
       </c>
       <c r="AQ25" t="n">
-        <v>0</v>
+        <v>0.275968992248062</v>
       </c>
       <c r="AR25" t="n">
-        <v>0</v>
+        <v>0.2384615384615385</v>
       </c>
       <c r="AS25" t="n">
-        <v>0.05573248407643312</v>
+        <v>0.945859872611465</v>
       </c>
       <c r="AT25" t="n">
-        <v>1</v>
+        <v>0.9352290679304898</v>
       </c>
       <c r="AU25" t="n">
-        <v>0</v>
+        <v>0.5192307692307693</v>
       </c>
       <c r="AV25" t="n">
-        <v>0.4522691705790297</v>
+        <v>0.8732394366197183</v>
       </c>
       <c r="AW25" t="n">
-        <v>1</v>
+        <v>0.6591639871382636</v>
       </c>
       <c r="AX25" t="n">
-        <v>0</v>
+        <v>0.2283464566929134</v>
       </c>
       <c r="AY25" t="n">
-        <v>1</v>
+        <v>0.6847826086956522</v>
       </c>
     </row>
     <row r="26">
@@ -4460,16 +4460,16 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.4155038759689922</v>
+        <v>0.8790697674418605</v>
       </c>
       <c r="C26" t="n">
         <v>0</v>
       </c>
       <c r="D26" t="n">
-        <v>0.5031446540880503</v>
+        <v>0.8522012578616353</v>
       </c>
       <c r="E26" t="n">
-        <v>0.5102040816326531</v>
+        <v>0.8665620094191523</v>
       </c>
       <c r="F26" t="n">
         <v>0</v>
@@ -4478,13 +4478,13 @@
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>1</v>
+        <v>0.7331288343558282</v>
       </c>
       <c r="I26" t="n">
         <v>0</v>
       </c>
       <c r="J26" t="n">
-        <v>0.3949843260188088</v>
+        <v>0.7241379310344828</v>
       </c>
       <c r="K26" t="n">
         <v>0</v>
@@ -4493,121 +4493,121 @@
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>0.4048</v>
+        <v>0.8</v>
       </c>
       <c r="N26" t="n">
-        <v>0.4124203821656051</v>
+        <v>0.7914012738853503</v>
       </c>
       <c r="O26" t="n">
-        <v>0.434375</v>
+        <v>0.7203125</v>
       </c>
       <c r="P26" t="n">
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.5780525502318392</v>
+        <v>0.5935085007727975</v>
       </c>
       <c r="R26" t="n">
         <v>0</v>
       </c>
       <c r="S26" t="n">
-        <v>0.4429967426710097</v>
+        <v>0.4283387622149837</v>
       </c>
       <c r="T26" t="n">
-        <v>0.4094488188976378</v>
+        <v>0.8362204724409449</v>
       </c>
       <c r="U26" t="n">
-        <v>0.4335443037974683</v>
+        <v>0.8306962025316456</v>
       </c>
       <c r="V26" t="n">
         <v>0</v>
       </c>
       <c r="W26" t="n">
-        <v>0.405320813771518</v>
+        <v>0.3427230046948357</v>
       </c>
       <c r="X26" t="n">
-        <v>0.5908372827804107</v>
+        <v>0.7393364928909952</v>
       </c>
       <c r="Y26" t="n">
-        <v>0.4136858475894246</v>
+        <v>0.5396578538102644</v>
       </c>
       <c r="Z26" t="n">
         <v>1</v>
       </c>
       <c r="AA26" t="n">
-        <v>0.6731391585760518</v>
+        <v>0.7346278317152104</v>
       </c>
       <c r="AB26" t="n">
-        <v>0.7435897435897436</v>
+        <v>0.7419871794871795</v>
       </c>
       <c r="AC26" t="n">
-        <v>0.5877616747181964</v>
+        <v>0.6344605475040258</v>
       </c>
       <c r="AD26" t="n">
-        <v>0.4158878504672897</v>
+        <v>0.735202492211838</v>
       </c>
       <c r="AE26" t="n">
-        <v>0.6120556414219475</v>
+        <v>0.7310664605873262</v>
       </c>
       <c r="AF26" t="n">
-        <v>0.6713836477987422</v>
+        <v>0.7531446540880503</v>
       </c>
       <c r="AG26" t="n">
-        <v>0.5855161787365177</v>
+        <v>0.7303543913713405</v>
       </c>
       <c r="AH26" t="n">
-        <v>0.007836990595611285</v>
+        <v>0.103448275862069</v>
       </c>
       <c r="AI26" t="n">
-        <v>0.3724247226624406</v>
+        <v>0.7321711568938193</v>
       </c>
       <c r="AJ26" t="n">
-        <v>0.4211382113821138</v>
+        <v>0.734959349593496</v>
       </c>
       <c r="AK26" t="n">
-        <v>0.5311004784688995</v>
+        <v>0.7208931419457735</v>
       </c>
       <c r="AL26" t="n">
-        <v>0.4403100775193798</v>
+        <v>0.9844961240310077</v>
       </c>
       <c r="AM26" t="n">
-        <v>0.4036144578313253</v>
+        <v>0.75</v>
       </c>
       <c r="AN26" t="n">
-        <v>0.5416666666666666</v>
+        <v>0.8503086419753086</v>
       </c>
       <c r="AO26" t="n">
-        <v>0.01225114854517611</v>
+        <v>0.09494640122511486</v>
       </c>
       <c r="AP26" t="n">
-        <v>0.5828025477707006</v>
+        <v>0.5764331210191083</v>
       </c>
       <c r="AQ26" t="n">
-        <v>0.001508295625942685</v>
+        <v>0.02111613876319759</v>
       </c>
       <c r="AR26" t="n">
-        <v>0.5934579439252337</v>
+        <v>0.7071651090342679</v>
       </c>
       <c r="AS26" t="n">
-        <v>0.6773675762439807</v>
+        <v>0.4382022471910113</v>
       </c>
       <c r="AT26" t="n">
-        <v>0.4545454545454545</v>
+        <v>0.4529505582137161</v>
       </c>
       <c r="AU26" t="n">
-        <v>0.006462035541195477</v>
+        <v>0.1211631663974152</v>
       </c>
       <c r="AV26" t="n">
-        <v>0.5565891472868217</v>
+        <v>0.3426356589147287</v>
       </c>
       <c r="AW26" t="n">
-        <v>0.4116693679092382</v>
+        <v>1</v>
       </c>
       <c r="AX26" t="n">
-        <v>0.5949367088607594</v>
+        <v>0.7151898734177216</v>
       </c>
       <c r="AY26" t="n">
-        <v>0.4327666151468315</v>
+        <v>0.8732612055641422</v>
       </c>
     </row>
     <row r="27">
@@ -4617,16 +4617,16 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.08333333333333333</v>
+        <v>0.5496794871794872</v>
       </c>
       <c r="C27" t="n">
         <v>0</v>
       </c>
       <c r="D27" t="n">
-        <v>0.1645367412140575</v>
+        <v>0.4840255591054313</v>
       </c>
       <c r="E27" t="n">
-        <v>0.6937086092715232</v>
+        <v>0.5149006622516556</v>
       </c>
       <c r="F27" t="n">
         <v>0</v>
@@ -4635,13 +4635,13 @@
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="I27" t="n">
         <v>0</v>
       </c>
       <c r="J27" t="n">
-        <v>0.07479674796747968</v>
+        <v>1</v>
       </c>
       <c r="K27" t="n">
         <v>0</v>
@@ -4650,46 +4650,46 @@
         <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>0.08852459016393442</v>
+        <v>0.5737704918032787</v>
       </c>
       <c r="N27" t="n">
-        <v>0.07843137254901961</v>
+        <v>0.4901960784313725</v>
       </c>
       <c r="O27" t="n">
-        <v>0.1021069692058347</v>
+        <v>1</v>
       </c>
       <c r="P27" t="n">
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>0.9012738853503185</v>
+        <v>0.89171974522293</v>
       </c>
       <c r="R27" t="n">
         <v>0</v>
       </c>
       <c r="S27" t="n">
-        <v>0.5779967159277504</v>
+        <v>0.1247947454844007</v>
       </c>
       <c r="T27" t="n">
-        <v>0.4498381877022654</v>
+        <v>0.4724919093851133</v>
       </c>
       <c r="U27" t="n">
-        <v>0.4855305466237942</v>
+        <v>0.4453376205787781</v>
       </c>
       <c r="V27" t="n">
         <v>0</v>
       </c>
       <c r="W27" t="n">
-        <v>0.5559105431309904</v>
+        <v>0.1070287539936102</v>
       </c>
       <c r="X27" t="n">
-        <v>0.9136807817589576</v>
+        <v>0.9869706840390879</v>
       </c>
       <c r="Y27" t="n">
-        <v>0.08972267536704731</v>
+        <v>0.2414355628058727</v>
       </c>
       <c r="Z27" t="n">
-        <v>0.6731391585760518</v>
+        <v>0.7346278317152104</v>
       </c>
       <c r="AA27" t="n">
         <v>1</v>
@@ -4698,10 +4698,10 @@
         <v>1</v>
       </c>
       <c r="AC27" t="n">
-        <v>0.8991596638655462</v>
+        <v>0.9294117647058824</v>
       </c>
       <c r="AD27" t="n">
-        <v>0.09134615384615384</v>
+        <v>1</v>
       </c>
       <c r="AE27" t="n">
         <v>1</v>
@@ -4710,61 +4710,61 @@
         <v>1</v>
       </c>
       <c r="AG27" t="n">
-        <v>0.9193037974683544</v>
+        <v>1</v>
       </c>
       <c r="AH27" t="n">
-        <v>0.01477832512315271</v>
+        <v>0.008210180623973728</v>
       </c>
       <c r="AI27" t="n">
-        <v>0.06393442622950819</v>
+        <v>1</v>
       </c>
       <c r="AJ27" t="n">
-        <v>0.07717569786535304</v>
+        <v>1</v>
       </c>
       <c r="AK27" t="n">
-        <v>0.1192368839427663</v>
+        <v>1</v>
       </c>
       <c r="AL27" t="n">
-        <v>0.09279999999999999</v>
+        <v>0.7552</v>
       </c>
       <c r="AM27" t="n">
-        <v>0.08422664624808576</v>
+        <v>0.9770290964777948</v>
       </c>
       <c r="AN27" t="n">
-        <v>0.8096774193548387</v>
+        <v>0.5225806451612903</v>
       </c>
       <c r="AO27" t="n">
-        <v>0.01277955271565495</v>
+        <v>0.003194888178913738</v>
       </c>
       <c r="AP27" t="n">
-        <v>0.9056</v>
+        <v>0.8592</v>
       </c>
       <c r="AQ27" t="n">
-        <v>0.0062402496099844</v>
+        <v>0.0046801872074883</v>
       </c>
       <c r="AR27" t="n">
-        <v>0.910828025477707</v>
+        <v>1</v>
       </c>
       <c r="AS27" t="n">
-        <v>1</v>
+        <v>0.1454849498327759</v>
       </c>
       <c r="AT27" t="n">
-        <v>0.07504078303425775</v>
+        <v>0.1517128874388254</v>
       </c>
       <c r="AU27" t="n">
-        <v>0.008223684210526315</v>
+        <v>0.001644736842105263</v>
       </c>
       <c r="AV27" t="n">
-        <v>0.6260032102728732</v>
+        <v>0.08025682182985554</v>
       </c>
       <c r="AW27" t="n">
-        <v>0.07603305785123966</v>
+        <v>0.5917355371900826</v>
       </c>
       <c r="AX27" t="n">
-        <v>0.9170731707317074</v>
+        <v>1</v>
       </c>
       <c r="AY27" t="n">
-        <v>0.07890499194847021</v>
+        <v>0.5475040257648953</v>
       </c>
     </row>
     <row r="28">
@@ -4774,16 +4774,16 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.08571428571428572</v>
+        <v>0.5507936507936508</v>
       </c>
       <c r="C28" t="n">
         <v>0</v>
       </c>
       <c r="D28" t="n">
-        <v>0.1777777777777778</v>
+        <v>0.5</v>
       </c>
       <c r="E28" t="n">
-        <v>0.6954397394136808</v>
+        <v>0.5211726384364821</v>
       </c>
       <c r="F28" t="n">
         <v>0</v>
@@ -4792,13 +4792,13 @@
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>0.5581395348837209</v>
+        <v>1</v>
       </c>
       <c r="I28" t="n">
         <v>0</v>
       </c>
       <c r="J28" t="n">
-        <v>0.07592891760904685</v>
+        <v>1</v>
       </c>
       <c r="K28" t="n">
         <v>0</v>
@@ -4807,46 +4807,46 @@
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>0.08412698412698413</v>
+        <v>0.5888888888888889</v>
       </c>
       <c r="N28" t="n">
-        <v>0.07928802588996764</v>
+        <v>0.5048543689320388</v>
       </c>
       <c r="O28" t="n">
-        <v>0.09651898734177215</v>
+        <v>1</v>
       </c>
       <c r="P28" t="n">
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>0.9017713365539453</v>
+        <v>0.8808373590982287</v>
       </c>
       <c r="R28" t="n">
         <v>0</v>
       </c>
       <c r="S28" t="n">
-        <v>0.5721311475409836</v>
+        <v>0.140983606557377</v>
       </c>
       <c r="T28" t="n">
-        <v>0.4315286624203822</v>
+        <v>0.4856687898089172</v>
       </c>
       <c r="U28" t="n">
-        <v>0.4729299363057325</v>
+        <v>0.4601910828025478</v>
       </c>
       <c r="V28" t="n">
         <v>0</v>
       </c>
       <c r="W28" t="n">
-        <v>0.5445859872611465</v>
+        <v>0.1130573248407643</v>
       </c>
       <c r="X28" t="n">
-        <v>0.913961038961039</v>
+        <v>0.9853896103896104</v>
       </c>
       <c r="Y28" t="n">
-        <v>0.08695652173913043</v>
+        <v>0.2592592592592592</v>
       </c>
       <c r="Z28" t="n">
-        <v>0.7435897435897436</v>
+        <v>0.7419871794871795</v>
       </c>
       <c r="AA28" t="n">
         <v>1</v>
@@ -4855,73 +4855,73 @@
         <v>1</v>
       </c>
       <c r="AC28" t="n">
-        <v>0.9050736497545008</v>
+        <v>0.9279869067103109</v>
       </c>
       <c r="AD28" t="n">
-        <v>0.09233176838810642</v>
+        <v>1</v>
       </c>
       <c r="AE28" t="n">
-        <v>0.9984051036682615</v>
+        <v>1</v>
       </c>
       <c r="AF28" t="n">
         <v>1</v>
       </c>
       <c r="AG28" t="n">
-        <v>0.9227129337539433</v>
+        <v>1</v>
       </c>
       <c r="AH28" t="n">
-        <v>0.01149425287356322</v>
+        <v>0.008210180623973728</v>
       </c>
       <c r="AI28" t="n">
-        <v>0.06219312602291326</v>
+        <v>1</v>
       </c>
       <c r="AJ28" t="n">
-        <v>0.07855973813420622</v>
+        <v>1</v>
       </c>
       <c r="AK28" t="n">
-        <v>0.1195476575121163</v>
+        <v>1</v>
       </c>
       <c r="AL28" t="n">
-        <v>0.09345794392523364</v>
+        <v>0.7601246105919003</v>
       </c>
       <c r="AM28" t="n">
-        <v>0.08487654320987655</v>
+        <v>0.9722222222222222</v>
       </c>
       <c r="AN28" t="n">
-        <v>0.8157051282051282</v>
+        <v>0.5464743589743589</v>
       </c>
       <c r="AO28" t="n">
-        <v>0.01253918495297806</v>
+        <v>0.003134796238244514</v>
       </c>
       <c r="AP28" t="n">
-        <v>0.9113924050632911</v>
+        <v>0.8481012658227848</v>
       </c>
       <c r="AQ28" t="n">
         <v>0.004658385093167702</v>
       </c>
       <c r="AR28" t="n">
-        <v>0.9156050955414012</v>
+        <v>1</v>
       </c>
       <c r="AS28" t="n">
-        <v>0.9983525535420099</v>
+        <v>0.1581548599670511</v>
       </c>
       <c r="AT28" t="n">
-        <v>0.07790143084260731</v>
+        <v>0.1494435612082671</v>
       </c>
       <c r="AU28" t="n">
-        <v>0.00974025974025974</v>
+        <v>0.003246753246753247</v>
       </c>
       <c r="AV28" t="n">
-        <v>0.6192733017377567</v>
+        <v>0.07740916271721959</v>
       </c>
       <c r="AW28" t="n">
-        <v>0.07119205298013245</v>
+        <v>0.5927152317880795</v>
       </c>
       <c r="AX28" t="n">
-        <v>0.9207119741100324</v>
+        <v>1</v>
       </c>
       <c r="AY28" t="n">
-        <v>0.08214849921011058</v>
+        <v>0.5497630331753555</v>
       </c>
     </row>
     <row r="29">
@@ -4931,31 +4931,31 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0</v>
+        <v>0.4621578099838969</v>
       </c>
       <c r="C29" t="n">
         <v>0</v>
       </c>
       <c r="D29" t="n">
-        <v>0.06677265500794913</v>
+        <v>0.4085850556438791</v>
       </c>
       <c r="E29" t="n">
-        <v>0.5928338762214984</v>
+        <v>0.4267100977198697</v>
       </c>
       <c r="F29" t="n">
-        <v>0</v>
+        <v>0.001592356687898089</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>0.419811320754717</v>
+        <v>0.9229559748427673</v>
       </c>
       <c r="I29" t="n">
         <v>0</v>
       </c>
       <c r="J29" t="n">
-        <v>0</v>
+        <v>0.9189627228525121</v>
       </c>
       <c r="K29" t="n">
         <v>0</v>
@@ -4964,121 +4964,121 @@
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>0</v>
+        <v>0.4838709677419355</v>
       </c>
       <c r="N29" t="n">
-        <v>0</v>
+        <v>0.4059900166389351</v>
       </c>
       <c r="O29" t="n">
-        <v>0.0127591706539075</v>
+        <v>0.9234449760765551</v>
       </c>
       <c r="P29" t="n">
-        <v>0</v>
+        <v>0.003294892915980231</v>
       </c>
       <c r="Q29" t="n">
-        <v>1</v>
+        <v>0.9278846153846154</v>
       </c>
       <c r="R29" t="n">
         <v>0</v>
       </c>
       <c r="S29" t="n">
-        <v>0.5091819699499165</v>
+        <v>0.1185308848080134</v>
       </c>
       <c r="T29" t="n">
-        <v>0.3440514469453376</v>
+        <v>0.3938906752411576</v>
       </c>
       <c r="U29" t="n">
-        <v>0.3754045307443366</v>
+        <v>0.3608414239482201</v>
       </c>
       <c r="V29" t="n">
         <v>0</v>
       </c>
       <c r="W29" t="n">
-        <v>0.5016129032258064</v>
+        <v>0.1145161290322581</v>
       </c>
       <c r="X29" t="n">
-        <v>1</v>
+        <v>0.913961038961039</v>
       </c>
       <c r="Y29" t="n">
-        <v>0</v>
+        <v>0.2173913043478261</v>
       </c>
       <c r="Z29" t="n">
-        <v>0.5877616747181964</v>
+        <v>0.6344605475040258</v>
       </c>
       <c r="AA29" t="n">
-        <v>0.8991596638655462</v>
+        <v>0.9294117647058824</v>
       </c>
       <c r="AB29" t="n">
-        <v>0.9050736497545008</v>
+        <v>0.9279869067103109</v>
       </c>
       <c r="AC29" t="n">
         <v>1</v>
       </c>
       <c r="AD29" t="n">
-        <v>0.009375</v>
+        <v>0.921875</v>
       </c>
       <c r="AE29" t="n">
-        <v>0.9292604501607717</v>
+        <v>0.9212218649517685</v>
       </c>
       <c r="AF29" t="n">
-        <v>0.910828025477707</v>
+        <v>0.9235668789808917</v>
       </c>
       <c r="AG29" t="n">
-        <v>1</v>
+        <v>0.9511811023622048</v>
       </c>
       <c r="AH29" t="n">
-        <v>0.0113452188006483</v>
+        <v>0.09238249594813615</v>
       </c>
       <c r="AI29" t="n">
-        <v>0</v>
+        <v>0.9146141215106732</v>
       </c>
       <c r="AJ29" t="n">
-        <v>0</v>
+        <v>0.9201331114808652</v>
       </c>
       <c r="AK29" t="n">
-        <v>0.022508038585209</v>
+        <v>0.9356913183279743</v>
       </c>
       <c r="AL29" t="n">
-        <v>0.01426307448494453</v>
+        <v>0.6719492868462758</v>
       </c>
       <c r="AM29" t="n">
-        <v>0</v>
+        <v>0.9116279069767442</v>
       </c>
       <c r="AN29" t="n">
-        <v>0.8612903225806452</v>
+        <v>0.4387096774193548</v>
       </c>
       <c r="AO29" t="n">
-        <v>0.01114649681528662</v>
+        <v>0.0589171974522293</v>
       </c>
       <c r="AP29" t="n">
-        <v>1</v>
+        <v>0.9297385620915033</v>
       </c>
       <c r="AQ29" t="n">
-        <v>0.004665629860031105</v>
+        <v>0.08398133748055987</v>
       </c>
       <c r="AR29" t="n">
-        <v>1</v>
+        <v>0.9403453689167975</v>
       </c>
       <c r="AS29" t="n">
-        <v>0.9320066334991708</v>
+        <v>0.1393034825870647</v>
       </c>
       <c r="AT29" t="n">
-        <v>0</v>
+        <v>0.1352657004830918</v>
       </c>
       <c r="AU29" t="n">
-        <v>0.006611570247933884</v>
+        <v>0.04462809917355372</v>
       </c>
       <c r="AV29" t="n">
-        <v>0.5255591054313099</v>
+        <v>0.08945686900958466</v>
       </c>
       <c r="AW29" t="n">
-        <v>0</v>
+        <v>0.5008183306055647</v>
       </c>
       <c r="AX29" t="n">
-        <v>1</v>
+        <v>0.9341021416803954</v>
       </c>
       <c r="AY29" t="n">
-        <v>0</v>
+        <v>0.456140350877193</v>
       </c>
     </row>
     <row r="30">
@@ -5088,16 +5088,16 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.9891640866873065</v>
+        <v>0.5541795665634675</v>
       </c>
       <c r="C30" t="n">
         <v>0</v>
       </c>
       <c r="D30" t="n">
-        <v>0.9088098918083463</v>
+        <v>0.4930448222565688</v>
       </c>
       <c r="E30" t="n">
-        <v>0.3886255924170616</v>
+        <v>0.5197472353870458</v>
       </c>
       <c r="F30" t="n">
         <v>0</v>
@@ -5106,13 +5106,13 @@
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>0.5960365853658537</v>
+        <v>1</v>
       </c>
       <c r="I30" t="n">
         <v>0</v>
       </c>
       <c r="J30" t="n">
-        <v>0.9889415481832543</v>
+        <v>1</v>
       </c>
       <c r="K30" t="n">
         <v>0</v>
@@ -5121,10 +5121,10 @@
         <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>0.9889937106918238</v>
+        <v>0.5849056603773585</v>
       </c>
       <c r="N30" t="n">
-        <v>0.9905511811023622</v>
+        <v>0.5023622047244094</v>
       </c>
       <c r="O30" t="n">
         <v>1</v>
@@ -5133,109 +5133,109 @@
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>0.009216589861751152</v>
+        <v>0.8755760368663594</v>
       </c>
       <c r="R30" t="n">
         <v>0</v>
       </c>
       <c r="S30" t="n">
-        <v>0.4465709728867623</v>
+        <v>0.1291866028708134</v>
       </c>
       <c r="T30" t="n">
-        <v>0.6105100463678517</v>
+        <v>0.4744976816074188</v>
       </c>
       <c r="U30" t="n">
-        <v>0.576271186440678</v>
+        <v>0.4468412942989214</v>
       </c>
       <c r="V30" t="n">
         <v>0</v>
       </c>
       <c r="W30" t="n">
-        <v>0.3183925811437404</v>
+        <v>0.115919629057187</v>
       </c>
       <c r="X30" t="n">
-        <v>0.009273570324574961</v>
+        <v>0.9845440494590417</v>
       </c>
       <c r="Y30" t="n">
-        <v>0.9922600619195047</v>
+        <v>0.260061919504644</v>
       </c>
       <c r="Z30" t="n">
-        <v>0.4158878504672897</v>
+        <v>0.735202492211838</v>
       </c>
       <c r="AA30" t="n">
-        <v>0.09134615384615384</v>
+        <v>1</v>
       </c>
       <c r="AB30" t="n">
-        <v>0.09233176838810642</v>
+        <v>1</v>
       </c>
       <c r="AC30" t="n">
-        <v>0.009375</v>
+        <v>0.921875</v>
       </c>
       <c r="AD30" t="n">
         <v>1</v>
       </c>
       <c r="AE30" t="n">
-        <v>0.07033639143730887</v>
+        <v>1</v>
       </c>
       <c r="AF30" t="n">
-        <v>0.08409785932721713</v>
+        <v>1</v>
       </c>
       <c r="AG30" t="n">
-        <v>0.006106870229007634</v>
+        <v>1</v>
       </c>
       <c r="AH30" t="n">
-        <v>0.001569858712715856</v>
+        <v>0.006279434850863423</v>
       </c>
       <c r="AI30" t="n">
         <v>1</v>
       </c>
       <c r="AJ30" t="n">
-        <v>0.9919224555735057</v>
+        <v>1</v>
       </c>
       <c r="AK30" t="n">
         <v>1</v>
       </c>
       <c r="AL30" t="n">
-        <v>1</v>
+        <v>0.7674772036474165</v>
       </c>
       <c r="AM30" t="n">
-        <v>0.9895833333333334</v>
+        <v>0.9761904761904762</v>
       </c>
       <c r="AN30" t="n">
-        <v>0.1306376360808709</v>
+        <v>0.5349922239502333</v>
       </c>
       <c r="AO30" t="n">
         <v>0.003048780487804878</v>
       </c>
       <c r="AP30" t="n">
-        <v>0.003115264797507788</v>
+        <v>0.8395638629283489</v>
       </c>
       <c r="AQ30" t="n">
-        <v>0</v>
+        <v>0.004545454545454545</v>
       </c>
       <c r="AR30" t="n">
-        <v>0.009216589861751152</v>
+        <v>1</v>
       </c>
       <c r="AS30" t="n">
-        <v>0.06782334384858044</v>
+        <v>0.1561514195583596</v>
       </c>
       <c r="AT30" t="n">
-        <v>0.9905511811023622</v>
+        <v>0.1559055118110236</v>
       </c>
       <c r="AU30" t="n">
-        <v>0</v>
+        <v>0.001582278481012658</v>
       </c>
       <c r="AV30" t="n">
-        <v>0.4696734059097978</v>
+        <v>0.08087091757387248</v>
       </c>
       <c r="AW30" t="n">
-        <v>0.9952229299363057</v>
+        <v>0.5987261146496815</v>
       </c>
       <c r="AX30" t="n">
-        <v>0.009345794392523364</v>
+        <v>1</v>
       </c>
       <c r="AY30" t="n">
-        <v>0.9908256880733946</v>
+        <v>0.5504587155963303</v>
       </c>
     </row>
     <row r="31">
@@ -5245,16 +5245,16 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.06220839813374806</v>
+        <v>0.5536547433903577</v>
       </c>
       <c r="C31" t="n">
         <v>0</v>
       </c>
       <c r="D31" t="n">
-        <v>0.1269592476489028</v>
+        <v>0.4921630094043887</v>
       </c>
       <c r="E31" t="n">
-        <v>0.7018927444794952</v>
+        <v>0.5173501577287066</v>
       </c>
       <c r="F31" t="n">
         <v>0</v>
@@ -5263,13 +5263,13 @@
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>0.4349157733537519</v>
+        <v>1</v>
       </c>
       <c r="I31" t="n">
         <v>0</v>
       </c>
       <c r="J31" t="n">
-        <v>0.05727554179566564</v>
+        <v>1</v>
       </c>
       <c r="K31" t="n">
         <v>0</v>
@@ -5278,58 +5278,58 @@
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>0.06190476190476191</v>
+        <v>0.5841269841269842</v>
       </c>
       <c r="N31" t="n">
-        <v>0.06151419558359621</v>
+        <v>0.5047318611987381</v>
       </c>
       <c r="O31" t="n">
-        <v>0.07266982622432859</v>
+        <v>1</v>
       </c>
       <c r="P31" t="n">
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>0.9287925696594427</v>
+        <v>0.8761609907120743</v>
       </c>
       <c r="R31" t="n">
         <v>0</v>
       </c>
       <c r="S31" t="n">
-        <v>0.5702746365105008</v>
+        <v>0.1405492730210016</v>
       </c>
       <c r="T31" t="n">
-        <v>0.4207221350078493</v>
+        <v>0.478806907378336</v>
       </c>
       <c r="U31" t="n">
-        <v>0.4758942457231726</v>
+        <v>0.4494556765163297</v>
       </c>
       <c r="V31" t="n">
         <v>0</v>
       </c>
       <c r="W31" t="n">
-        <v>0.546875</v>
+        <v>0.1203125</v>
       </c>
       <c r="X31" t="n">
-        <v>0.9388714733542319</v>
+        <v>0.9843260188087775</v>
       </c>
       <c r="Y31" t="n">
-        <v>0.0565149136577708</v>
+        <v>0.2621664050235479</v>
       </c>
       <c r="Z31" t="n">
-        <v>0.6120556414219475</v>
+        <v>0.7310664605873262</v>
       </c>
       <c r="AA31" t="n">
         <v>1</v>
       </c>
       <c r="AB31" t="n">
-        <v>0.9984051036682615</v>
+        <v>1</v>
       </c>
       <c r="AC31" t="n">
-        <v>0.9292604501607717</v>
+        <v>0.9212218649517685</v>
       </c>
       <c r="AD31" t="n">
-        <v>0.07033639143730887</v>
+        <v>1</v>
       </c>
       <c r="AE31" t="n">
         <v>1</v>
@@ -5338,61 +5338,61 @@
         <v>1</v>
       </c>
       <c r="AG31" t="n">
-        <v>0.9491525423728814</v>
+        <v>1</v>
       </c>
       <c r="AH31" t="n">
-        <v>0.01408450704225352</v>
+        <v>0.00782472613458529</v>
       </c>
       <c r="AI31" t="n">
-        <v>0.03815580286168521</v>
+        <v>1</v>
       </c>
       <c r="AJ31" t="n">
-        <v>0.05825242718446602</v>
+        <v>1</v>
       </c>
       <c r="AK31" t="n">
-        <v>0.09276729559748427</v>
+        <v>1</v>
       </c>
       <c r="AL31" t="n">
-        <v>0.07373271889400922</v>
+        <v>0.7634408602150538</v>
       </c>
       <c r="AM31" t="n">
-        <v>0.06042296072507553</v>
+        <v>0.9758308157099698</v>
       </c>
       <c r="AN31" t="n">
-        <v>0.8330733229329174</v>
+        <v>0.5397815912636506</v>
       </c>
       <c r="AO31" t="n">
-        <v>0.0107197549770291</v>
+        <v>0.003062787136294028</v>
       </c>
       <c r="AP31" t="n">
-        <v>0.9385826771653544</v>
+        <v>0.8393700787401575</v>
       </c>
       <c r="AQ31" t="n">
         <v>0.004511278195488722</v>
       </c>
       <c r="AR31" t="n">
-        <v>0.9411764705882353</v>
+        <v>1</v>
       </c>
       <c r="AS31" t="n">
-        <v>0.9984126984126984</v>
+        <v>0.1650793650793651</v>
       </c>
       <c r="AT31" t="n">
-        <v>0.05188679245283019</v>
+        <v>0.1619496855345912</v>
       </c>
       <c r="AU31" t="n">
-        <v>0.009478672985781991</v>
+        <v>0.00315955766192733</v>
       </c>
       <c r="AV31" t="n">
-        <v>0.6052631578947368</v>
+        <v>0.08668730650154799</v>
       </c>
       <c r="AW31" t="n">
-        <v>0.05379746835443038</v>
+        <v>0.5901898734177216</v>
       </c>
       <c r="AX31" t="n">
-        <v>0.9416403785488959</v>
+        <v>1</v>
       </c>
       <c r="AY31" t="n">
-        <v>0.0514018691588785</v>
+        <v>0.5560747663551402</v>
       </c>
     </row>
     <row r="32">
@@ -5402,16 +5402,16 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.07894736842105263</v>
+        <v>0.5634674922600619</v>
       </c>
       <c r="C32" t="n">
         <v>0</v>
       </c>
       <c r="D32" t="n">
-        <v>0.15600624024961</v>
+        <v>0.5101404056162246</v>
       </c>
       <c r="E32" t="n">
-        <v>0.6769706336939721</v>
+        <v>0.5347758887171561</v>
       </c>
       <c r="F32" t="n">
         <v>0</v>
@@ -5420,13 +5420,13 @@
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>0.4977307110438729</v>
+        <v>1</v>
       </c>
       <c r="I32" t="n">
         <v>0</v>
       </c>
       <c r="J32" t="n">
-        <v>0.07210031347962383</v>
+        <v>1</v>
       </c>
       <c r="K32" t="n">
         <v>0</v>
@@ -5435,46 +5435,46 @@
         <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>0.0828125</v>
+        <v>0.5984375</v>
       </c>
       <c r="N32" t="n">
-        <v>0.07355242566510173</v>
+        <v>0.5164319248826291</v>
       </c>
       <c r="O32" t="n">
-        <v>0.09782608695652174</v>
+        <v>1</v>
       </c>
       <c r="P32" t="n">
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>0.9069767441860465</v>
+        <v>0.8728682170542635</v>
       </c>
       <c r="R32" t="n">
         <v>0</v>
       </c>
       <c r="S32" t="n">
-        <v>0.5696</v>
+        <v>0.1376</v>
       </c>
       <c r="T32" t="n">
-        <v>0.425</v>
+        <v>0.490625</v>
       </c>
       <c r="U32" t="n">
-        <v>0.4738461538461539</v>
+        <v>0.4661538461538461</v>
       </c>
       <c r="V32" t="n">
         <v>0</v>
       </c>
       <c r="W32" t="n">
-        <v>0.5539906103286385</v>
+        <v>0.1158059467918623</v>
       </c>
       <c r="X32" t="n">
-        <v>0.9224683544303798</v>
+        <v>0.9889240506329114</v>
       </c>
       <c r="Y32" t="n">
-        <v>0.07923930269413629</v>
+        <v>0.2662440570522979</v>
       </c>
       <c r="Z32" t="n">
-        <v>0.6713836477987422</v>
+        <v>0.7531446540880503</v>
       </c>
       <c r="AA32" t="n">
         <v>1</v>
@@ -5483,10 +5483,10 @@
         <v>1</v>
       </c>
       <c r="AC32" t="n">
-        <v>0.910828025477707</v>
+        <v>0.9235668789808917</v>
       </c>
       <c r="AD32" t="n">
-        <v>0.08409785932721713</v>
+        <v>1</v>
       </c>
       <c r="AE32" t="n">
         <v>1</v>
@@ -5495,61 +5495,61 @@
         <v>1</v>
       </c>
       <c r="AG32" t="n">
-        <v>0.9251908396946565</v>
+        <v>1</v>
       </c>
       <c r="AH32" t="n">
-        <v>0.0110410094637224</v>
+        <v>0.007886435331230283</v>
       </c>
       <c r="AI32" t="n">
-        <v>0.05371248025276461</v>
+        <v>1</v>
       </c>
       <c r="AJ32" t="n">
-        <v>0.07348242811501597</v>
+        <v>1</v>
       </c>
       <c r="AK32" t="n">
-        <v>0.1114599686028257</v>
+        <v>1</v>
       </c>
       <c r="AL32" t="n">
-        <v>0.08755760368663594</v>
+        <v>0.7880184331797235</v>
       </c>
       <c r="AM32" t="n">
-        <v>0.07749627421758569</v>
+        <v>0.9806259314456036</v>
       </c>
       <c r="AN32" t="n">
-        <v>0.8152173913043478</v>
+        <v>0.5403726708074534</v>
       </c>
       <c r="AO32" t="n">
-        <v>0.01234567901234568</v>
+        <v>0.00308641975308642</v>
       </c>
       <c r="AP32" t="n">
-        <v>0.917981072555205</v>
+        <v>0.8391167192429022</v>
       </c>
       <c r="AQ32" t="n">
         <v>0.0045662100456621</v>
       </c>
       <c r="AR32" t="n">
-        <v>0.9228395061728395</v>
+        <v>1</v>
       </c>
       <c r="AS32" t="n">
-        <v>1</v>
+        <v>0.1603174603174603</v>
       </c>
       <c r="AT32" t="n">
-        <v>0.0679304897314376</v>
+        <v>0.1611374407582938</v>
       </c>
       <c r="AU32" t="n">
-        <v>0.006339144215530904</v>
+        <v>0.003169572107765452</v>
       </c>
       <c r="AV32" t="n">
-        <v>0.6141975308641975</v>
+        <v>0.07561728395061729</v>
       </c>
       <c r="AW32" t="n">
-        <v>0.064</v>
+        <v>0.6112</v>
       </c>
       <c r="AX32" t="n">
-        <v>0.9233176838810642</v>
+        <v>1</v>
       </c>
       <c r="AY32" t="n">
-        <v>0.0700152207001522</v>
+        <v>0.5601217656012176</v>
       </c>
     </row>
     <row r="33">
@@ -5559,16 +5559,16 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0</v>
+        <v>0.546969696969697</v>
       </c>
       <c r="C33" t="n">
         <v>0</v>
       </c>
       <c r="D33" t="n">
-        <v>0.07272727272727272</v>
+        <v>0.4818181818181818</v>
       </c>
       <c r="E33" t="n">
-        <v>0.6018662519440124</v>
+        <v>0.5054432348367029</v>
       </c>
       <c r="F33" t="n">
         <v>0</v>
@@ -5577,13 +5577,13 @@
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>0.4152923538230884</v>
+        <v>1</v>
       </c>
       <c r="I33" t="n">
         <v>0</v>
       </c>
       <c r="J33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K33" t="n">
         <v>0</v>
@@ -5592,94 +5592,94 @@
         <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>0</v>
+        <v>0.577639751552795</v>
       </c>
       <c r="N33" t="n">
-        <v>0</v>
+        <v>0.4984177215189873</v>
       </c>
       <c r="O33" t="n">
-        <v>0.01057401812688822</v>
+        <v>1</v>
       </c>
       <c r="P33" t="n">
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>1</v>
+        <v>0.8931297709923665</v>
       </c>
       <c r="R33" t="n">
         <v>0</v>
       </c>
       <c r="S33" t="n">
-        <v>0.5285714285714286</v>
+        <v>0.126984126984127</v>
       </c>
       <c r="T33" t="n">
-        <v>0.3543913713405239</v>
+        <v>0.4668721109399075</v>
       </c>
       <c r="U33" t="n">
-        <v>0.3931888544891641</v>
+        <v>0.434984520123839</v>
       </c>
       <c r="V33" t="n">
         <v>0</v>
       </c>
       <c r="W33" t="n">
-        <v>0.5123076923076924</v>
+        <v>0.1092307692307692</v>
       </c>
       <c r="X33" t="n">
-        <v>1</v>
+        <v>0.984472049689441</v>
       </c>
       <c r="Y33" t="n">
-        <v>0</v>
+        <v>0.2553516819571865</v>
       </c>
       <c r="Z33" t="n">
-        <v>0.5855161787365177</v>
+        <v>0.7303543913713405</v>
       </c>
       <c r="AA33" t="n">
-        <v>0.9193037974683544</v>
+        <v>1</v>
       </c>
       <c r="AB33" t="n">
-        <v>0.9227129337539433</v>
+        <v>1</v>
       </c>
       <c r="AC33" t="n">
-        <v>1</v>
+        <v>0.9511811023622048</v>
       </c>
       <c r="AD33" t="n">
-        <v>0.006106870229007634</v>
+        <v>1</v>
       </c>
       <c r="AE33" t="n">
-        <v>0.9491525423728814</v>
+        <v>1</v>
       </c>
       <c r="AF33" t="n">
-        <v>0.9251908396946565</v>
+        <v>1</v>
       </c>
       <c r="AG33" t="n">
         <v>1</v>
       </c>
       <c r="AH33" t="n">
-        <v>0.01393188854489164</v>
+        <v>0.007739938080495356</v>
       </c>
       <c r="AI33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK33" t="n">
-        <v>0.01681957186544342</v>
+        <v>1</v>
       </c>
       <c r="AL33" t="n">
-        <v>0.007692307692307693</v>
+        <v>0.7630769230769231</v>
       </c>
       <c r="AM33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN33" t="n">
-        <v>0.8659476117103235</v>
+        <v>0.5254237288135594</v>
       </c>
       <c r="AO33" t="n">
-        <v>0.007530120481927711</v>
+        <v>0.003012048192771084</v>
       </c>
       <c r="AP33" t="n">
-        <v>0.9984496124031008</v>
+        <v>0.8682170542635659</v>
       </c>
       <c r="AQ33" t="n">
         <v>0.004484304932735426</v>
@@ -5688,25 +5688,25 @@
         <v>1</v>
       </c>
       <c r="AS33" t="n">
-        <v>0.9480314960629921</v>
+        <v>0.1511811023622047</v>
       </c>
       <c r="AT33" t="n">
-        <v>0</v>
+        <v>0.1470588235294118</v>
       </c>
       <c r="AU33" t="n">
-        <v>0.004739336492890996</v>
+        <v>0.00315955766192733</v>
       </c>
       <c r="AV33" t="n">
-        <v>0.5286144578313253</v>
+        <v>0.0783132530120482</v>
       </c>
       <c r="AW33" t="n">
-        <v>0.001582278481012658</v>
+        <v>0.5854430379746836</v>
       </c>
       <c r="AX33" t="n">
         <v>1</v>
       </c>
       <c r="AY33" t="n">
-        <v>0</v>
+        <v>0.5444947209653092</v>
       </c>
     </row>
     <row r="34">
@@ -5716,154 +5716,154 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.001555209953343701</v>
+        <v>0.1959564541213064</v>
       </c>
       <c r="C34" t="n">
-        <v>0.9825949367088608</v>
+        <v>0.2088607594936709</v>
       </c>
       <c r="D34" t="n">
-        <v>0.00310077519379845</v>
+        <v>0.2294573643410853</v>
       </c>
       <c r="E34" t="n">
-        <v>0.007874015748031496</v>
+        <v>0.2110236220472441</v>
       </c>
       <c r="F34" t="n">
-        <v>0.9843014128728415</v>
+        <v>0.3092621664050236</v>
       </c>
       <c r="G34" t="n">
-        <v>0.9838187702265372</v>
+        <v>0.226537216828479</v>
       </c>
       <c r="H34" t="n">
         <v>0.0060790273556231</v>
       </c>
       <c r="I34" t="n">
-        <v>0.984251968503937</v>
+        <v>0.2062992125984252</v>
       </c>
       <c r="J34" t="n">
-        <v>0.001579778830963665</v>
+        <v>0.007898894154818325</v>
       </c>
       <c r="K34" t="n">
-        <v>0.9853896103896104</v>
+        <v>0.2256493506493507</v>
       </c>
       <c r="L34" t="n">
-        <v>0.9826771653543307</v>
+        <v>0.1984251968503937</v>
       </c>
       <c r="M34" t="n">
-        <v>0.001607717041800643</v>
+        <v>0.1752411575562701</v>
       </c>
       <c r="N34" t="n">
-        <v>0</v>
+        <v>0.22508038585209</v>
       </c>
       <c r="O34" t="n">
-        <v>0.003129890453834116</v>
+        <v>0.004694835680751174</v>
       </c>
       <c r="P34" t="n">
-        <v>0.9890453834115805</v>
+        <v>0.2676056338028169</v>
       </c>
       <c r="Q34" t="n">
-        <v>0.01417322834645669</v>
+        <v>0.1133858267716535</v>
       </c>
       <c r="R34" t="n">
-        <v>0.9823151125401929</v>
+        <v>0.2122186495176849</v>
       </c>
       <c r="S34" t="n">
-        <v>0.01623376623376623</v>
+        <v>0.5957792207792207</v>
       </c>
       <c r="T34" t="n">
-        <v>0.01114649681528662</v>
+        <v>0.2340764331210191</v>
       </c>
       <c r="U34" t="n">
-        <v>0.004665629860031105</v>
+        <v>0.23950233281493</v>
       </c>
       <c r="V34" t="n">
-        <v>0.9875968992248062</v>
+        <v>0.2232558139534884</v>
       </c>
       <c r="W34" t="n">
-        <v>0.1751592356687898</v>
+        <v>0.6528662420382165</v>
       </c>
       <c r="X34" t="n">
-        <v>0.01446945337620579</v>
+        <v>0.008038585209003215</v>
       </c>
       <c r="Y34" t="n">
-        <v>0.001569858712715856</v>
+        <v>0.4725274725274725</v>
       </c>
       <c r="Z34" t="n">
-        <v>0.007836990595611285</v>
+        <v>0.103448275862069</v>
       </c>
       <c r="AA34" t="n">
-        <v>0.01477832512315271</v>
+        <v>0.008210180623973728</v>
       </c>
       <c r="AB34" t="n">
-        <v>0.01149425287356322</v>
+        <v>0.008210180623973728</v>
       </c>
       <c r="AC34" t="n">
-        <v>0.0113452188006483</v>
+        <v>0.09238249594813615</v>
       </c>
       <c r="AD34" t="n">
-        <v>0.001569858712715856</v>
+        <v>0.006279434850863423</v>
       </c>
       <c r="AE34" t="n">
-        <v>0.01408450704225352</v>
+        <v>0.00782472613458529</v>
       </c>
       <c r="AF34" t="n">
-        <v>0.0110410094637224</v>
+        <v>0.007886435331230283</v>
       </c>
       <c r="AG34" t="n">
-        <v>0.01393188854489164</v>
+        <v>0.007739938080495356</v>
       </c>
       <c r="AH34" t="n">
         <v>1</v>
       </c>
       <c r="AI34" t="n">
-        <v>0.001572327044025157</v>
+        <v>0.006289308176100629</v>
       </c>
       <c r="AJ34" t="n">
-        <v>0.001633986928104575</v>
+        <v>0.006535947712418301</v>
       </c>
       <c r="AK34" t="n">
-        <v>0.003154574132492113</v>
+        <v>0.006309148264984227</v>
       </c>
       <c r="AL34" t="n">
-        <v>0.003129890453834116</v>
+        <v>0.09233176838810642</v>
       </c>
       <c r="AM34" t="n">
-        <v>0</v>
+        <v>0.01060606060606061</v>
       </c>
       <c r="AN34" t="n">
-        <v>0.01540832049306626</v>
+        <v>0.2234206471494607</v>
       </c>
       <c r="AO34" t="n">
         <v>1</v>
       </c>
       <c r="AP34" t="n">
-        <v>0.01129032258064516</v>
+        <v>0.1596774193548387</v>
       </c>
       <c r="AQ34" t="n">
-        <v>1</v>
+        <v>0.8923076923076924</v>
       </c>
       <c r="AR34" t="n">
-        <v>0.01085271317829457</v>
+        <v>0.006201550387596899</v>
       </c>
       <c r="AS34" t="n">
-        <v>0.01612903225806452</v>
+        <v>0.5919354838709677</v>
       </c>
       <c r="AT34" t="n">
-        <v>0.001587301587301587</v>
+        <v>0.5476190476190477</v>
       </c>
       <c r="AU34" t="n">
         <v>1</v>
       </c>
       <c r="AV34" t="n">
-        <v>0.00778816199376947</v>
+        <v>0.7071651090342679</v>
       </c>
       <c r="AW34" t="n">
-        <v>0.001594896331738437</v>
+        <v>0.1658692185007974</v>
       </c>
       <c r="AX34" t="n">
-        <v>0.01449275362318841</v>
+        <v>0.00644122383252818</v>
       </c>
       <c r="AY34" t="n">
-        <v>0.001567398119122257</v>
+        <v>0.2006269592476489</v>
       </c>
     </row>
     <row r="35">
@@ -5873,16 +5873,16 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>1</v>
+        <v>0.5461658841940532</v>
       </c>
       <c r="C35" t="n">
         <v>0</v>
       </c>
       <c r="D35" t="n">
-        <v>0.9022082018927445</v>
+        <v>0.4889589905362776</v>
       </c>
       <c r="E35" t="n">
-        <v>0.3591772151898734</v>
+        <v>0.5205696202531646</v>
       </c>
       <c r="F35" t="n">
         <v>0</v>
@@ -5891,7 +5891,7 @@
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>0.5390505359877489</v>
+        <v>1</v>
       </c>
       <c r="I35" t="n">
         <v>0</v>
@@ -5906,10 +5906,10 @@
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>1</v>
+        <v>0.5945945945945946</v>
       </c>
       <c r="N35" t="n">
-        <v>1</v>
+        <v>0.5087719298245614</v>
       </c>
       <c r="O35" t="n">
         <v>1</v>
@@ -5918,58 +5918,58 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>0</v>
+        <v>0.8757861635220126</v>
       </c>
       <c r="R35" t="n">
         <v>0</v>
       </c>
       <c r="S35" t="n">
-        <v>0.4204545454545455</v>
+        <v>0.1314935064935065</v>
       </c>
       <c r="T35" t="n">
-        <v>0.5921259842519685</v>
+        <v>0.4755905511811024</v>
       </c>
       <c r="U35" t="n">
-        <v>0.5566037735849056</v>
+        <v>0.4544025157232705</v>
       </c>
       <c r="V35" t="n">
         <v>0</v>
       </c>
       <c r="W35" t="n">
-        <v>0.2924528301886792</v>
+        <v>0.119496855345912</v>
       </c>
       <c r="X35" t="n">
-        <v>0</v>
+        <v>0.9821717990275527</v>
       </c>
       <c r="Y35" t="n">
-        <v>1</v>
+        <v>0.2527301092043682</v>
       </c>
       <c r="Z35" t="n">
-        <v>0.3724247226624406</v>
+        <v>0.7321711568938193</v>
       </c>
       <c r="AA35" t="n">
-        <v>0.06393442622950819</v>
+        <v>1</v>
       </c>
       <c r="AB35" t="n">
-        <v>0.06219312602291326</v>
+        <v>1</v>
       </c>
       <c r="AC35" t="n">
-        <v>0</v>
+        <v>0.9146141215106732</v>
       </c>
       <c r="AD35" t="n">
         <v>1</v>
       </c>
       <c r="AE35" t="n">
-        <v>0.03815580286168521</v>
+        <v>1</v>
       </c>
       <c r="AF35" t="n">
-        <v>0.05371248025276461</v>
+        <v>1</v>
       </c>
       <c r="AG35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH35" t="n">
-        <v>0.001572327044025157</v>
+        <v>0.006289308176100629</v>
       </c>
       <c r="AI35" t="n">
         <v>1</v>
@@ -5978,49 +5978,49 @@
         <v>1</v>
       </c>
       <c r="AK35" t="n">
-        <v>0.9952</v>
+        <v>1</v>
       </c>
       <c r="AL35" t="n">
-        <v>1</v>
+        <v>0.7597503900156006</v>
       </c>
       <c r="AM35" t="n">
-        <v>1</v>
+        <v>0.9801223241590215</v>
       </c>
       <c r="AN35" t="n">
-        <v>0.1150855365474339</v>
+        <v>0.5381026438569206</v>
       </c>
       <c r="AO35" t="n">
-        <v>0.0031201248049922</v>
+        <v>0.0015600624024961</v>
       </c>
       <c r="AP35" t="n">
-        <v>0</v>
+        <v>0.8343848580441641</v>
       </c>
       <c r="AQ35" t="n">
-        <v>0</v>
+        <v>0.004622496147919877</v>
       </c>
       <c r="AR35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AS35" t="n">
-        <v>0.04207119741100324</v>
+        <v>0.1553398058252427</v>
       </c>
       <c r="AT35" t="n">
-        <v>1</v>
+        <v>0.1590551181102362</v>
       </c>
       <c r="AU35" t="n">
-        <v>0</v>
+        <v>0.003236245954692557</v>
       </c>
       <c r="AV35" t="n">
-        <v>0.4341692789968652</v>
+        <v>0.08463949843260188</v>
       </c>
       <c r="AW35" t="n">
-        <v>1</v>
+        <v>0.5891980360065466</v>
       </c>
       <c r="AX35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AY35" t="n">
-        <v>1</v>
+        <v>0.5484375</v>
       </c>
     </row>
     <row r="36">
@@ -6030,16 +6030,16 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>1</v>
+        <v>0.5632911392405063</v>
       </c>
       <c r="C36" t="n">
         <v>0</v>
       </c>
       <c r="D36" t="n">
-        <v>0.9079365079365079</v>
+        <v>0.4952380952380953</v>
       </c>
       <c r="E36" t="n">
-        <v>0.3745980707395498</v>
+        <v>0.522508038585209</v>
       </c>
       <c r="F36" t="n">
         <v>0</v>
@@ -6048,7 +6048,7 @@
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>0.5801526717557252</v>
+        <v>1</v>
       </c>
       <c r="I36" t="n">
         <v>0</v>
@@ -6063,70 +6063,70 @@
         <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>1</v>
+        <v>0.593192868719611</v>
       </c>
       <c r="N36" t="n">
-        <v>1</v>
+        <v>0.5111464968152867</v>
       </c>
       <c r="O36" t="n">
-        <v>0.9841269841269841</v>
+        <v>1</v>
       </c>
       <c r="P36" t="n">
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>0</v>
+        <v>0.8770226537216829</v>
       </c>
       <c r="R36" t="n">
         <v>0</v>
       </c>
       <c r="S36" t="n">
-        <v>0.4223300970873786</v>
+        <v>0.1407766990291262</v>
       </c>
       <c r="T36" t="n">
-        <v>0.5906902086677368</v>
+        <v>0.4895666131621188</v>
       </c>
       <c r="U36" t="n">
-        <v>0.5433070866141733</v>
+        <v>0.4582677165354331</v>
       </c>
       <c r="V36" t="n">
         <v>0</v>
       </c>
       <c r="W36" t="n">
-        <v>0.3004846526655897</v>
+        <v>0.1227786752827141</v>
       </c>
       <c r="X36" t="n">
-        <v>0</v>
+        <v>0.9983498349834984</v>
       </c>
       <c r="Y36" t="n">
-        <v>1</v>
+        <v>0.2588996763754045</v>
       </c>
       <c r="Z36" t="n">
-        <v>0.4211382113821138</v>
+        <v>0.734959349593496</v>
       </c>
       <c r="AA36" t="n">
-        <v>0.07717569786535304</v>
+        <v>1</v>
       </c>
       <c r="AB36" t="n">
-        <v>0.07855973813420622</v>
+        <v>1</v>
       </c>
       <c r="AC36" t="n">
-        <v>0</v>
+        <v>0.9201331114808652</v>
       </c>
       <c r="AD36" t="n">
-        <v>0.9919224555735057</v>
+        <v>1</v>
       </c>
       <c r="AE36" t="n">
-        <v>0.05825242718446602</v>
+        <v>1</v>
       </c>
       <c r="AF36" t="n">
-        <v>0.07348242811501597</v>
+        <v>1</v>
       </c>
       <c r="AG36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH36" t="n">
-        <v>0.001633986928104575</v>
+        <v>0.006535947712418301</v>
       </c>
       <c r="AI36" t="n">
         <v>1</v>
@@ -6135,49 +6135,49 @@
         <v>1</v>
       </c>
       <c r="AK36" t="n">
-        <v>0.9763406940063092</v>
+        <v>1</v>
       </c>
       <c r="AL36" t="n">
-        <v>0.988835725677831</v>
+        <v>0.7719298245614035</v>
       </c>
       <c r="AM36" t="n">
-        <v>1</v>
+        <v>0.9797191887675507</v>
       </c>
       <c r="AN36" t="n">
-        <v>0.1253968253968254</v>
+        <v>0.5396825396825397</v>
       </c>
       <c r="AO36" t="n">
         <v>0.003144654088050315</v>
       </c>
       <c r="AP36" t="n">
-        <v>0.001612903225806452</v>
+        <v>0.8338709677419355</v>
       </c>
       <c r="AQ36" t="n">
-        <v>0</v>
+        <v>0.003110419906687403</v>
       </c>
       <c r="AR36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AS36" t="n">
-        <v>0.05392156862745098</v>
+        <v>0.1584967320261438</v>
       </c>
       <c r="AT36" t="n">
-        <v>1</v>
+        <v>0.1558441558441558</v>
       </c>
       <c r="AU36" t="n">
-        <v>0</v>
+        <v>0.001639344262295082</v>
       </c>
       <c r="AV36" t="n">
-        <v>0.4565916398713826</v>
+        <v>0.07717041800643087</v>
       </c>
       <c r="AW36" t="n">
-        <v>0.9983579638752053</v>
+        <v>0.5944170771756979</v>
       </c>
       <c r="AX36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AY36" t="n">
-        <v>1</v>
+        <v>0.5584</v>
       </c>
     </row>
     <row r="37">
@@ -6187,16 +6187,16 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.9734789391575663</v>
+        <v>0.5273010920436817</v>
       </c>
       <c r="C37" t="n">
         <v>0</v>
       </c>
       <c r="D37" t="n">
-        <v>0.8961832061068702</v>
+        <v>0.482442748091603</v>
       </c>
       <c r="E37" t="n">
-        <v>0.3913713405238829</v>
+        <v>0.5038520801232665</v>
       </c>
       <c r="F37" t="n">
         <v>0</v>
@@ -6205,13 +6205,13 @@
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>0.687218045112782</v>
+        <v>1</v>
       </c>
       <c r="I37" t="n">
         <v>0</v>
       </c>
       <c r="J37" t="n">
-        <v>0.9728</v>
+        <v>1</v>
       </c>
       <c r="K37" t="n">
         <v>0</v>
@@ -6220,10 +6220,10 @@
         <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>0.9745627980922098</v>
+        <v>0.5739268680445151</v>
       </c>
       <c r="N37" t="n">
-        <v>0.9750390015600624</v>
+        <v>0.4960998439937597</v>
       </c>
       <c r="O37" t="n">
         <v>1</v>
@@ -6232,109 +6232,109 @@
         <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>0.02180685358255452</v>
+        <v>0.9003115264797508</v>
       </c>
       <c r="R37" t="n">
         <v>0</v>
       </c>
       <c r="S37" t="n">
-        <v>0.4317817014446228</v>
+        <v>0.1171749598715891</v>
       </c>
       <c r="T37" t="n">
-        <v>0.5863708399366085</v>
+        <v>0.4564183835182251</v>
       </c>
       <c r="U37" t="n">
-        <v>0.5508607198748043</v>
+        <v>0.4303599374021909</v>
       </c>
       <c r="V37" t="n">
         <v>0</v>
       </c>
       <c r="W37" t="n">
-        <v>0.3160377358490566</v>
+        <v>0.1006289308176101</v>
       </c>
       <c r="X37" t="n">
-        <v>0.02211690363349131</v>
+        <v>0.990521327014218</v>
       </c>
       <c r="Y37" t="n">
-        <v>0.9779874213836478</v>
+        <v>0.2327044025157233</v>
       </c>
       <c r="Z37" t="n">
-        <v>0.5311004784688995</v>
+        <v>0.7208931419457735</v>
       </c>
       <c r="AA37" t="n">
-        <v>0.1192368839427663</v>
+        <v>1</v>
       </c>
       <c r="AB37" t="n">
-        <v>0.1195476575121163</v>
+        <v>1</v>
       </c>
       <c r="AC37" t="n">
-        <v>0.022508038585209</v>
+        <v>0.9356913183279743</v>
       </c>
       <c r="AD37" t="n">
         <v>1</v>
       </c>
       <c r="AE37" t="n">
-        <v>0.09276729559748427</v>
+        <v>1</v>
       </c>
       <c r="AF37" t="n">
-        <v>0.1114599686028257</v>
+        <v>1</v>
       </c>
       <c r="AG37" t="n">
-        <v>0.01681957186544342</v>
+        <v>1</v>
       </c>
       <c r="AH37" t="n">
-        <v>0.003154574132492113</v>
+        <v>0.006309148264984227</v>
       </c>
       <c r="AI37" t="n">
-        <v>0.9952</v>
+        <v>1</v>
       </c>
       <c r="AJ37" t="n">
-        <v>0.9763406940063092</v>
+        <v>1</v>
       </c>
       <c r="AK37" t="n">
         <v>1</v>
       </c>
       <c r="AL37" t="n">
-        <v>1</v>
+        <v>0.7511591962905718</v>
       </c>
       <c r="AM37" t="n">
-        <v>0.975867269984917</v>
+        <v>0.9728506787330317</v>
       </c>
       <c r="AN37" t="n">
-        <v>0.1363636363636364</v>
+        <v>0.5156739811912225</v>
       </c>
       <c r="AO37" t="n">
-        <v>0.004580152671755725</v>
+        <v>0.003053435114503817</v>
       </c>
       <c r="AP37" t="n">
-        <v>0.0143312101910828</v>
+        <v>0.8630573248407644</v>
       </c>
       <c r="AQ37" t="n">
-        <v>0</v>
+        <v>0.003048780487804878</v>
       </c>
       <c r="AR37" t="n">
-        <v>0.02469135802469136</v>
+        <v>1</v>
       </c>
       <c r="AS37" t="n">
-        <v>0.09162717219589257</v>
+        <v>0.1374407582938389</v>
       </c>
       <c r="AT37" t="n">
-        <v>0.9759229534510433</v>
+        <v>0.1364365971107544</v>
       </c>
       <c r="AU37" t="n">
-        <v>0</v>
+        <v>0.001577287066246057</v>
       </c>
       <c r="AV37" t="n">
-        <v>0.4751552795031056</v>
+        <v>0.06832298136645963</v>
       </c>
       <c r="AW37" t="n">
-        <v>0.9820846905537459</v>
+        <v>0.5651465798045603</v>
       </c>
       <c r="AX37" t="n">
-        <v>0.02070063694267516</v>
+        <v>1</v>
       </c>
       <c r="AY37" t="n">
-        <v>0.9844236760124611</v>
+        <v>0.5295950155763239</v>
       </c>
     </row>
     <row r="38">
@@ -6344,16 +6344,16 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.9862174578866769</v>
+        <v>0.8208269525267994</v>
       </c>
       <c r="C38" t="n">
         <v>0</v>
       </c>
       <c r="D38" t="n">
-        <v>0.9015625</v>
+        <v>0.7921875</v>
       </c>
       <c r="E38" t="n">
-        <v>0.3713405238828968</v>
+        <v>0.785824345146379</v>
       </c>
       <c r="F38" t="n">
         <v>0</v>
@@ -6362,13 +6362,13 @@
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>0.600896860986547</v>
+        <v>0.7937219730941704</v>
       </c>
       <c r="I38" t="n">
         <v>0</v>
       </c>
       <c r="J38" t="n">
-        <v>0.9859375</v>
+        <v>0.7515625</v>
       </c>
       <c r="K38" t="n">
         <v>0</v>
@@ -6377,121 +6377,121 @@
         <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>0.9874411302982732</v>
+        <v>0.7456828885400314</v>
       </c>
       <c r="N38" t="n">
-        <v>0.9875968992248062</v>
+        <v>0.7364341085271318</v>
       </c>
       <c r="O38" t="n">
-        <v>1</v>
+        <v>0.7538940809968847</v>
       </c>
       <c r="P38" t="n">
         <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>0.0108359133126935</v>
+        <v>0.6191950464396285</v>
       </c>
       <c r="R38" t="n">
         <v>0</v>
       </c>
       <c r="S38" t="n">
-        <v>0.4281098546042003</v>
+        <v>0.3909531502423264</v>
       </c>
       <c r="T38" t="n">
-        <v>0.5987460815047022</v>
+        <v>0.7695924764890282</v>
       </c>
       <c r="U38" t="n">
-        <v>0.5624036979969184</v>
+        <v>0.7565485362095532</v>
       </c>
       <c r="V38" t="n">
         <v>0</v>
       </c>
       <c r="W38" t="n">
-        <v>0.3046153846153846</v>
+        <v>0.3184615384615385</v>
       </c>
       <c r="X38" t="n">
-        <v>0.009448818897637795</v>
+        <v>0.7637795275590551</v>
       </c>
       <c r="Y38" t="n">
-        <v>0.9876543209876543</v>
+        <v>0.5077160493827161</v>
       </c>
       <c r="Z38" t="n">
-        <v>0.4403100775193798</v>
+        <v>0.9844961240310077</v>
       </c>
       <c r="AA38" t="n">
-        <v>0.09279999999999999</v>
+        <v>0.7552</v>
       </c>
       <c r="AB38" t="n">
-        <v>0.09345794392523364</v>
+        <v>0.7601246105919003</v>
       </c>
       <c r="AC38" t="n">
-        <v>0.01426307448494453</v>
+        <v>0.6719492868462758</v>
       </c>
       <c r="AD38" t="n">
-        <v>1</v>
+        <v>0.7674772036474165</v>
       </c>
       <c r="AE38" t="n">
-        <v>0.07373271889400922</v>
+        <v>0.7634408602150538</v>
       </c>
       <c r="AF38" t="n">
-        <v>0.08755760368663594</v>
+        <v>0.7880184331797235</v>
       </c>
       <c r="AG38" t="n">
-        <v>0.007692307692307693</v>
+        <v>0.7630769230769231</v>
       </c>
       <c r="AH38" t="n">
-        <v>0.003129890453834116</v>
+        <v>0.09233176838810642</v>
       </c>
       <c r="AI38" t="n">
-        <v>1</v>
+        <v>0.7597503900156006</v>
       </c>
       <c r="AJ38" t="n">
-        <v>0.988835725677831</v>
+        <v>0.7719298245614035</v>
       </c>
       <c r="AK38" t="n">
-        <v>1</v>
+        <v>0.7511591962905718</v>
       </c>
       <c r="AL38" t="n">
         <v>1</v>
       </c>
       <c r="AM38" t="n">
-        <v>0.9880952380952381</v>
+        <v>0.7782738095238095</v>
       </c>
       <c r="AN38" t="n">
-        <v>0.1294851794071763</v>
+        <v>0.7987519500780031</v>
       </c>
       <c r="AO38" t="n">
-        <v>0.004531722054380665</v>
+        <v>0.09063444108761329</v>
       </c>
       <c r="AP38" t="n">
-        <v>0.007716049382716049</v>
+        <v>0.6033950617283951</v>
       </c>
       <c r="AQ38" t="n">
-        <v>0</v>
+        <v>0.02252252252252252</v>
       </c>
       <c r="AR38" t="n">
-        <v>0.01374045801526718</v>
+        <v>0.7343511450381679</v>
       </c>
       <c r="AS38" t="n">
-        <v>0.06624605678233439</v>
+        <v>0.3990536277602524</v>
       </c>
       <c r="AT38" t="n">
-        <v>0.9861538461538462</v>
+        <v>0.4169230769230769</v>
       </c>
       <c r="AU38" t="n">
-        <v>0</v>
+        <v>0.1121642969984202</v>
       </c>
       <c r="AV38" t="n">
-        <v>0.445468509984639</v>
+        <v>0.3164362519201229</v>
       </c>
       <c r="AW38" t="n">
-        <v>0.9936608557844691</v>
+        <v>0.9112519809825673</v>
       </c>
       <c r="AX38" t="n">
-        <v>0.009360374414976599</v>
+        <v>0.7410296411856474</v>
       </c>
       <c r="AY38" t="n">
-        <v>0.9861963190184049</v>
+        <v>0.8113496932515337</v>
       </c>
     </row>
     <row r="39">
@@ -6501,16 +6501,16 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>1</v>
+        <v>0.5799701046337817</v>
       </c>
       <c r="C39" t="n">
         <v>0</v>
       </c>
       <c r="D39" t="n">
-        <v>0.911144578313253</v>
+        <v>0.5030120481927711</v>
       </c>
       <c r="E39" t="n">
-        <v>0.362406015037594</v>
+        <v>0.5398496240601504</v>
       </c>
       <c r="F39" t="n">
         <v>0</v>
@@ -6519,13 +6519,13 @@
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>0.5647058823529412</v>
+        <v>0.9779411764705882</v>
       </c>
       <c r="I39" t="n">
         <v>0</v>
       </c>
       <c r="J39" t="n">
-        <v>1</v>
+        <v>0.9758308157099698</v>
       </c>
       <c r="K39" t="n">
         <v>0</v>
@@ -6534,121 +6534,121 @@
         <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>1</v>
+        <v>0.6018376722817764</v>
       </c>
       <c r="N39" t="n">
-        <v>1</v>
+        <v>0.5251141552511416</v>
       </c>
       <c r="O39" t="n">
-        <v>0.9834586466165414</v>
+        <v>0.9759398496240601</v>
       </c>
       <c r="P39" t="n">
         <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>0</v>
+        <v>0.8649468892261002</v>
       </c>
       <c r="R39" t="n">
         <v>0</v>
       </c>
       <c r="S39" t="n">
-        <v>0.4134165366614664</v>
+        <v>0.15600624024961</v>
       </c>
       <c r="T39" t="n">
-        <v>0.5987933634992458</v>
+        <v>0.5037707390648567</v>
       </c>
       <c r="U39" t="n">
-        <v>0.5603576751117735</v>
+        <v>0.481371087928465</v>
       </c>
       <c r="V39" t="n">
         <v>0</v>
       </c>
       <c r="W39" t="n">
-        <v>0.2870090634441088</v>
+        <v>0.1329305135951662</v>
       </c>
       <c r="X39" t="n">
-        <v>0</v>
+        <v>0.9602446483180428</v>
       </c>
       <c r="Y39" t="n">
-        <v>1</v>
+        <v>0.2762762762762763</v>
       </c>
       <c r="Z39" t="n">
-        <v>0.4036144578313253</v>
+        <v>0.75</v>
       </c>
       <c r="AA39" t="n">
-        <v>0.08422664624808576</v>
+        <v>0.9770290964777948</v>
       </c>
       <c r="AB39" t="n">
-        <v>0.08487654320987655</v>
+        <v>0.9722222222222222</v>
       </c>
       <c r="AC39" t="n">
-        <v>0</v>
+        <v>0.9116279069767442</v>
       </c>
       <c r="AD39" t="n">
-        <v>0.9895833333333334</v>
+        <v>0.9761904761904762</v>
       </c>
       <c r="AE39" t="n">
-        <v>0.06042296072507553</v>
+        <v>0.9758308157099698</v>
       </c>
       <c r="AF39" t="n">
-        <v>0.07749627421758569</v>
+        <v>0.9806259314456036</v>
       </c>
       <c r="AG39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH39" t="n">
-        <v>0</v>
+        <v>0.01060606060606061</v>
       </c>
       <c r="AI39" t="n">
-        <v>1</v>
+        <v>0.9801223241590215</v>
       </c>
       <c r="AJ39" t="n">
-        <v>1</v>
+        <v>0.9797191887675507</v>
       </c>
       <c r="AK39" t="n">
-        <v>0.975867269984917</v>
+        <v>0.9728506787330317</v>
       </c>
       <c r="AL39" t="n">
-        <v>0.9880952380952381</v>
+        <v>0.7782738095238095</v>
       </c>
       <c r="AM39" t="n">
         <v>1</v>
       </c>
       <c r="AN39" t="n">
-        <v>0.1218424962852897</v>
+        <v>0.5572065378900446</v>
       </c>
       <c r="AO39" t="n">
-        <v>0.002967359050445104</v>
+        <v>0.00741839762611276</v>
       </c>
       <c r="AP39" t="n">
-        <v>0.001519756838905775</v>
+        <v>0.8252279635258358</v>
       </c>
       <c r="AQ39" t="n">
-        <v>0</v>
+        <v>0.005865102639296188</v>
       </c>
       <c r="AR39" t="n">
-        <v>0</v>
+        <v>0.973568281938326</v>
       </c>
       <c r="AS39" t="n">
-        <v>0.05546995377503852</v>
+        <v>0.1818181818181818</v>
       </c>
       <c r="AT39" t="n">
-        <v>1</v>
+        <v>0.1803030303030303</v>
       </c>
       <c r="AU39" t="n">
-        <v>0</v>
+        <v>0.009287925696594427</v>
       </c>
       <c r="AV39" t="n">
-        <v>0.4369369369369369</v>
+        <v>0.09759759759759759</v>
       </c>
       <c r="AW39" t="n">
-        <v>0.9984709480122325</v>
+        <v>0.6207951070336392</v>
       </c>
       <c r="AX39" t="n">
-        <v>0</v>
+        <v>0.9725609756097561</v>
       </c>
       <c r="AY39" t="n">
-        <v>1</v>
+        <v>0.5729166666666666</v>
       </c>
     </row>
     <row r="40">
@@ -6658,16 +6658,16 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.1037151702786378</v>
+        <v>0.9721362229102167</v>
       </c>
       <c r="C40" t="n">
         <v>0</v>
       </c>
       <c r="D40" t="n">
-        <v>0.2390625</v>
+        <v>0.9875</v>
       </c>
       <c r="E40" t="n">
-        <v>0.7429906542056075</v>
+        <v>0.9813084112149533</v>
       </c>
       <c r="F40" t="n">
         <v>0</v>
@@ -6676,13 +6676,13 @@
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>0.4486404833836858</v>
+        <v>0.5468277945619335</v>
       </c>
       <c r="I40" t="n">
         <v>0</v>
       </c>
       <c r="J40" t="n">
-        <v>0.1316614420062696</v>
+        <v>0.5203761755485894</v>
       </c>
       <c r="K40" t="n">
         <v>0</v>
@@ -6691,121 +6691,121 @@
         <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>0.1293375394321767</v>
+        <v>0.8785488958990536</v>
       </c>
       <c r="N40" t="n">
-        <v>0.1271860095389507</v>
+        <v>0.931637519872814</v>
       </c>
       <c r="O40" t="n">
-        <v>0.125193199381762</v>
+        <v>0.5162287480680062</v>
       </c>
       <c r="P40" t="n">
         <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>0.8627145085803433</v>
+        <v>0.3946957878315133</v>
       </c>
       <c r="R40" t="n">
         <v>0</v>
       </c>
       <c r="S40" t="n">
-        <v>0.717741935483871</v>
+        <v>0.617741935483871</v>
       </c>
       <c r="T40" t="n">
-        <v>0.5458860759493671</v>
+        <v>0.9857594936708861</v>
       </c>
       <c r="U40" t="n">
-        <v>0.5636645962732919</v>
+        <v>0.9829192546583851</v>
       </c>
       <c r="V40" t="n">
         <v>0</v>
       </c>
       <c r="W40" t="n">
-        <v>0.6505460218408736</v>
+        <v>0.5288611544461779</v>
       </c>
       <c r="X40" t="n">
-        <v>0.8641390205371248</v>
+        <v>0.5576619273301737</v>
       </c>
       <c r="Y40" t="n">
-        <v>0.1230529595015576</v>
+        <v>0.7071651090342679</v>
       </c>
       <c r="Z40" t="n">
-        <v>0.5416666666666666</v>
+        <v>0.8503086419753086</v>
       </c>
       <c r="AA40" t="n">
-        <v>0.8096774193548387</v>
+        <v>0.5225806451612903</v>
       </c>
       <c r="AB40" t="n">
-        <v>0.8157051282051282</v>
+        <v>0.5464743589743589</v>
       </c>
       <c r="AC40" t="n">
-        <v>0.8612903225806452</v>
+        <v>0.4387096774193548</v>
       </c>
       <c r="AD40" t="n">
-        <v>0.1306376360808709</v>
+        <v>0.5349922239502333</v>
       </c>
       <c r="AE40" t="n">
-        <v>0.8330733229329174</v>
+        <v>0.5397815912636506</v>
       </c>
       <c r="AF40" t="n">
-        <v>0.8152173913043478</v>
+        <v>0.5403726708074534</v>
       </c>
       <c r="AG40" t="n">
-        <v>0.8659476117103235</v>
+        <v>0.5254237288135594</v>
       </c>
       <c r="AH40" t="n">
-        <v>0.01540832049306626</v>
+        <v>0.2234206471494607</v>
       </c>
       <c r="AI40" t="n">
-        <v>0.1150855365474339</v>
+        <v>0.5381026438569206</v>
       </c>
       <c r="AJ40" t="n">
-        <v>0.1253968253968254</v>
+        <v>0.5396825396825397</v>
       </c>
       <c r="AK40" t="n">
-        <v>0.1363636363636364</v>
+        <v>0.5156739811912225</v>
       </c>
       <c r="AL40" t="n">
-        <v>0.1294851794071763</v>
+        <v>0.7987519500780031</v>
       </c>
       <c r="AM40" t="n">
-        <v>0.1218424962852897</v>
+        <v>0.5572065378900446</v>
       </c>
       <c r="AN40" t="n">
         <v>1</v>
       </c>
       <c r="AO40" t="n">
-        <v>0.01225114854517611</v>
+        <v>0.1914241960183767</v>
       </c>
       <c r="AP40" t="n">
-        <v>0.9289099526066351</v>
+        <v>0.3649289099526066</v>
       </c>
       <c r="AQ40" t="n">
-        <v>0.006033182503770739</v>
+        <v>0.06636500754147813</v>
       </c>
       <c r="AR40" t="n">
-        <v>0.8687022900763359</v>
+        <v>0.5129770992366413</v>
       </c>
       <c r="AS40" t="n">
-        <v>0.8576</v>
+        <v>0.6368</v>
       </c>
       <c r="AT40" t="n">
-        <v>0.1182965299684543</v>
+        <v>0.6451104100946372</v>
       </c>
       <c r="AU40" t="n">
-        <v>0.006472491909385114</v>
+        <v>0.2734627831715211</v>
       </c>
       <c r="AV40" t="n">
-        <v>0.6578538102643857</v>
+        <v>0.5412130637636081</v>
       </c>
       <c r="AW40" t="n">
-        <v>0.1244094488188976</v>
+        <v>0.9606299212598425</v>
       </c>
       <c r="AX40" t="n">
-        <v>0.8578199052132701</v>
+        <v>0.5197472353870458</v>
       </c>
       <c r="AY40" t="n">
-        <v>0.1138845553822153</v>
+        <v>0.9719188767550702</v>
       </c>
     </row>
     <row r="41">
@@ -6815,154 +6815,154 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.003021148036253776</v>
+        <v>0.1812688821752266</v>
       </c>
       <c r="C41" t="n">
-        <v>0.9831546707503829</v>
+        <v>0.2419601837672282</v>
       </c>
       <c r="D41" t="n">
-        <v>0.006163328197226503</v>
+        <v>0.2187981510015408</v>
       </c>
       <c r="E41" t="n">
-        <v>0.01080246913580247</v>
+        <v>0.2067901234567901</v>
       </c>
       <c r="F41" t="n">
-        <v>0.9892966360856269</v>
+        <v>0.3440366972477064</v>
       </c>
       <c r="G41" t="n">
-        <v>0.984375</v>
+        <v>0.271875</v>
       </c>
       <c r="H41" t="n">
-        <v>0.01037037037037037</v>
+        <v>0.002962962962962963</v>
       </c>
       <c r="I41" t="n">
-        <v>0.9847560975609756</v>
+        <v>0.2469512195121951</v>
       </c>
       <c r="J41" t="n">
-        <v>0.001555209953343701</v>
+        <v>0.003110419906687403</v>
       </c>
       <c r="K41" t="n">
-        <v>0.9829192546583851</v>
+        <v>0.2531055900621118</v>
       </c>
       <c r="L41" t="n">
-        <v>0.9848024316109423</v>
+        <v>0.2386018237082067</v>
       </c>
       <c r="M41" t="n">
-        <v>0.001540832049306626</v>
+        <v>0.1679506933744222</v>
       </c>
       <c r="N41" t="n">
-        <v>0</v>
+        <v>0.2186046511627907</v>
       </c>
       <c r="O41" t="n">
         <v>0.00303030303030303</v>
       </c>
       <c r="P41" t="n">
-        <v>0.9891975308641975</v>
+        <v>0.2993827160493827</v>
       </c>
       <c r="Q41" t="n">
-        <v>0.01070336391437309</v>
+        <v>0.09021406727828746</v>
       </c>
       <c r="R41" t="n">
-        <v>0.984472049689441</v>
+        <v>0.2453416149068323</v>
       </c>
       <c r="S41" t="n">
-        <v>0.01901743264659271</v>
+        <v>0.5625990491283677</v>
       </c>
       <c r="T41" t="n">
-        <v>0.01393188854489164</v>
+        <v>0.2321981424148607</v>
       </c>
       <c r="U41" t="n">
-        <v>0.01062215477996965</v>
+        <v>0.2367223065250379</v>
       </c>
       <c r="V41" t="n">
-        <v>0.9878603945371776</v>
+        <v>0.2564491654021244</v>
       </c>
       <c r="W41" t="n">
-        <v>0.184331797235023</v>
+        <v>0.6374807987711214</v>
       </c>
       <c r="X41" t="n">
-        <v>0.01228878648233487</v>
+        <v>0.006144393241167435</v>
       </c>
       <c r="Y41" t="n">
-        <v>0.003067484662576687</v>
+        <v>0.4355828220858896</v>
       </c>
       <c r="Z41" t="n">
-        <v>0.01225114854517611</v>
+        <v>0.09494640122511486</v>
       </c>
       <c r="AA41" t="n">
-        <v>0.01277955271565495</v>
+        <v>0.003194888178913738</v>
       </c>
       <c r="AB41" t="n">
-        <v>0.01253918495297806</v>
+        <v>0.003134796238244514</v>
       </c>
       <c r="AC41" t="n">
-        <v>0.01114649681528662</v>
+        <v>0.0589171974522293</v>
       </c>
       <c r="AD41" t="n">
         <v>0.003048780487804878</v>
       </c>
       <c r="AE41" t="n">
-        <v>0.0107197549770291</v>
+        <v>0.003062787136294028</v>
       </c>
       <c r="AF41" t="n">
-        <v>0.01234567901234568</v>
+        <v>0.00308641975308642</v>
       </c>
       <c r="AG41" t="n">
-        <v>0.007530120481927711</v>
+        <v>0.003012048192771084</v>
       </c>
       <c r="AH41" t="n">
         <v>1</v>
       </c>
       <c r="AI41" t="n">
-        <v>0.0031201248049922</v>
+        <v>0.0015600624024961</v>
       </c>
       <c r="AJ41" t="n">
         <v>0.003144654088050315</v>
       </c>
       <c r="AK41" t="n">
-        <v>0.004580152671755725</v>
+        <v>0.003053435114503817</v>
       </c>
       <c r="AL41" t="n">
-        <v>0.004531722054380665</v>
+        <v>0.09063444108761329</v>
       </c>
       <c r="AM41" t="n">
-        <v>0.002967359050445104</v>
+        <v>0.00741839762611276</v>
       </c>
       <c r="AN41" t="n">
-        <v>0.01225114854517611</v>
+        <v>0.1914241960183767</v>
       </c>
       <c r="AO41" t="n">
         <v>1</v>
       </c>
       <c r="AP41" t="n">
-        <v>0.007716049382716049</v>
+        <v>0.1265432098765432</v>
       </c>
       <c r="AQ41" t="n">
-        <v>1</v>
+        <v>0.922272047832586</v>
       </c>
       <c r="AR41" t="n">
-        <v>0.01339285714285714</v>
+        <v>0.002976190476190476</v>
       </c>
       <c r="AS41" t="n">
-        <v>0.0140625</v>
+        <v>0.56875</v>
       </c>
       <c r="AT41" t="n">
-        <v>0.003095975232198143</v>
+        <v>0.5185758513931888</v>
       </c>
       <c r="AU41" t="n">
         <v>1</v>
       </c>
       <c r="AV41" t="n">
-        <v>0.01234567901234568</v>
+        <v>0.6759259259259259</v>
       </c>
       <c r="AW41" t="n">
-        <v>0.00310077519379845</v>
+        <v>0.1581395348837209</v>
       </c>
       <c r="AX41" t="n">
-        <v>0.01246105919003115</v>
+        <v>0.001557632398753894</v>
       </c>
       <c r="AY41" t="n">
-        <v>0.00310077519379845</v>
+        <v>0.1937984496124031</v>
       </c>
     </row>
     <row r="42">
@@ -6972,154 +6972,154 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.0015600624024961</v>
+        <v>0.4024960998439938</v>
       </c>
       <c r="C42" t="n">
-        <v>0</v>
+        <v>0.009433962264150943</v>
       </c>
       <c r="D42" t="n">
-        <v>0.07740916271721959</v>
+        <v>0.344391785150079</v>
       </c>
       <c r="E42" t="n">
-        <v>0.6156299840510366</v>
+        <v>0.3700159489633174</v>
       </c>
       <c r="F42" t="n">
-        <v>0</v>
+        <v>0.01095461658841941</v>
       </c>
       <c r="G42" t="n">
-        <v>0</v>
+        <v>0.0046875</v>
       </c>
       <c r="H42" t="n">
-        <v>0.4224924012158054</v>
+        <v>0.8495440729483282</v>
       </c>
       <c r="I42" t="n">
-        <v>0</v>
+        <v>0.004724409448818898</v>
       </c>
       <c r="J42" t="n">
-        <v>0.001610305958132045</v>
+        <v>0.8486312399355878</v>
       </c>
       <c r="K42" t="n">
-        <v>0</v>
+        <v>0.008</v>
       </c>
       <c r="L42" t="n">
-        <v>0</v>
+        <v>0.00782472613458529</v>
       </c>
       <c r="M42" t="n">
-        <v>0.001587301587301587</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="N42" t="n">
-        <v>0.001574803149606299</v>
+        <v>0.3574803149606299</v>
       </c>
       <c r="O42" t="n">
-        <v>0.00778816199376947</v>
+        <v>0.8520249221183801</v>
       </c>
       <c r="P42" t="n">
-        <v>0</v>
+        <v>0.0208</v>
       </c>
       <c r="Q42" t="n">
-        <v>0.9984375</v>
+        <v>1</v>
       </c>
       <c r="R42" t="n">
-        <v>0</v>
+        <v>0.003231017770597738</v>
       </c>
       <c r="S42" t="n">
-        <v>0.5418006430868167</v>
+        <v>0.0707395498392283</v>
       </c>
       <c r="T42" t="n">
-        <v>0.3789308176100629</v>
+        <v>0.3191823899371069</v>
       </c>
       <c r="U42" t="n">
-        <v>0.4231974921630094</v>
+        <v>0.3150470219435736</v>
       </c>
       <c r="V42" t="n">
-        <v>0</v>
+        <v>0.004651162790697674</v>
       </c>
       <c r="W42" t="n">
-        <v>0.5229067930489731</v>
+        <v>0.0679304897314376</v>
       </c>
       <c r="X42" t="n">
-        <v>0.998422712933754</v>
+        <v>0.8422712933753943</v>
       </c>
       <c r="Y42" t="n">
-        <v>0</v>
+        <v>0.1518987341772152</v>
       </c>
       <c r="Z42" t="n">
-        <v>0.5828025477707006</v>
+        <v>0.5764331210191083</v>
       </c>
       <c r="AA42" t="n">
-        <v>0.9056</v>
+        <v>0.8592</v>
       </c>
       <c r="AB42" t="n">
-        <v>0.9113924050632911</v>
+        <v>0.8481012658227848</v>
       </c>
       <c r="AC42" t="n">
-        <v>1</v>
+        <v>0.9297385620915033</v>
       </c>
       <c r="AD42" t="n">
-        <v>0.003115264797507788</v>
+        <v>0.8395638629283489</v>
       </c>
       <c r="AE42" t="n">
-        <v>0.9385826771653544</v>
+        <v>0.8393700787401575</v>
       </c>
       <c r="AF42" t="n">
-        <v>0.917981072555205</v>
+        <v>0.8391167192429022</v>
       </c>
       <c r="AG42" t="n">
-        <v>0.9984496124031008</v>
+        <v>0.8682170542635659</v>
       </c>
       <c r="AH42" t="n">
-        <v>0.01129032258064516</v>
+        <v>0.1596774193548387</v>
       </c>
       <c r="AI42" t="n">
-        <v>0</v>
+        <v>0.8343848580441641</v>
       </c>
       <c r="AJ42" t="n">
-        <v>0.001612903225806452</v>
+        <v>0.8338709677419355</v>
       </c>
       <c r="AK42" t="n">
-        <v>0.0143312101910828</v>
+        <v>0.8630573248407644</v>
       </c>
       <c r="AL42" t="n">
-        <v>0.007716049382716049</v>
+        <v>0.6033950617283951</v>
       </c>
       <c r="AM42" t="n">
-        <v>0.001519756838905775</v>
+        <v>0.8252279635258358</v>
       </c>
       <c r="AN42" t="n">
-        <v>0.9289099526066351</v>
+        <v>0.3649289099526066</v>
       </c>
       <c r="AO42" t="n">
-        <v>0.007716049382716049</v>
+        <v>0.1265432098765432</v>
       </c>
       <c r="AP42" t="n">
         <v>1</v>
       </c>
       <c r="AQ42" t="n">
-        <v>0.006116207951070336</v>
+        <v>0.1743119266055046</v>
       </c>
       <c r="AR42" t="n">
-        <v>0.9984472049689441</v>
+        <v>0.8680124223602484</v>
       </c>
       <c r="AS42" t="n">
-        <v>0.9314194577352473</v>
+        <v>0.07336523125996811</v>
       </c>
       <c r="AT42" t="n">
-        <v>0.001574803149606299</v>
+        <v>0.06929133858267716</v>
       </c>
       <c r="AU42" t="n">
-        <v>0.007974481658692184</v>
+        <v>0.08771929824561403</v>
       </c>
       <c r="AV42" t="n">
-        <v>0.5388198757763976</v>
+        <v>0.06055900621118013</v>
       </c>
       <c r="AW42" t="n">
-        <v>0.003241491085899514</v>
+        <v>0.4408427876823339</v>
       </c>
       <c r="AX42" t="n">
-        <v>0.9983896940418679</v>
+        <v>0.8679549114331723</v>
       </c>
       <c r="AY42" t="n">
-        <v>0</v>
+        <v>0.3987635239567233</v>
       </c>
     </row>
     <row r="43">
@@ -7129,91 +7129,91 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0</v>
+        <v>0.05405405405405406</v>
       </c>
       <c r="C43" t="n">
-        <v>0.9953198127925117</v>
+        <v>0.4040561622464899</v>
       </c>
       <c r="D43" t="n">
-        <v>0</v>
+        <v>0.07121212121212121</v>
       </c>
       <c r="E43" t="n">
-        <v>0.001529051987767584</v>
+        <v>0.06727828746177369</v>
       </c>
       <c r="F43" t="n">
-        <v>0.9954819277108434</v>
+        <v>0.5225903614457831</v>
       </c>
       <c r="G43" t="n">
-        <v>0.9938176197836167</v>
+        <v>0.4234930448222566</v>
       </c>
       <c r="H43" t="n">
-        <v>0.001464128843338214</v>
+        <v>0.002928257686676428</v>
       </c>
       <c r="I43" t="n">
-        <v>0.9939024390243902</v>
+        <v>0.4009146341463415</v>
       </c>
       <c r="J43" t="n">
-        <v>0</v>
+        <v>0.0045662100456621</v>
       </c>
       <c r="K43" t="n">
-        <v>0.9937694704049844</v>
+        <v>0.3800623052959501</v>
       </c>
       <c r="L43" t="n">
-        <v>0.9938931297709923</v>
+        <v>0.3816793893129771</v>
       </c>
       <c r="M43" t="n">
-        <v>0</v>
+        <v>0.05513016845329249</v>
       </c>
       <c r="N43" t="n">
-        <v>0</v>
+        <v>0.06955177743431221</v>
       </c>
       <c r="O43" t="n">
-        <v>0</v>
+        <v>0.004497751124437781</v>
       </c>
       <c r="P43" t="n">
-        <v>0.9953488372093023</v>
+        <v>0.4837209302325581</v>
       </c>
       <c r="Q43" t="n">
-        <v>0.0060790273556231</v>
+        <v>0.1291793313069909</v>
       </c>
       <c r="R43" t="n">
-        <v>0.9938271604938271</v>
+        <v>0.4104938271604938</v>
       </c>
       <c r="S43" t="n">
-        <v>0.006211180124223602</v>
+        <v>0.391304347826087</v>
       </c>
       <c r="T43" t="n">
-        <v>0.0045662100456621</v>
+        <v>0.0776255707762557</v>
       </c>
       <c r="U43" t="n">
-        <v>0</v>
+        <v>0.0791476407914764</v>
       </c>
       <c r="V43" t="n">
-        <v>0.9955156950672646</v>
+        <v>0.4170403587443946</v>
       </c>
       <c r="W43" t="n">
-        <v>0.1509715994020927</v>
+        <v>0.4618834080717489</v>
       </c>
       <c r="X43" t="n">
-        <v>0.004601226993865031</v>
+        <v>0.001533742331288344</v>
       </c>
       <c r="Y43" t="n">
-        <v>0</v>
+        <v>0.275968992248062</v>
       </c>
       <c r="Z43" t="n">
-        <v>0.001508295625942685</v>
+        <v>0.02111613876319759</v>
       </c>
       <c r="AA43" t="n">
-        <v>0.0062402496099844</v>
+        <v>0.0046801872074883</v>
       </c>
       <c r="AB43" t="n">
         <v>0.004658385093167702</v>
       </c>
       <c r="AC43" t="n">
-        <v>0.004665629860031105</v>
+        <v>0.08398133748055987</v>
       </c>
       <c r="AD43" t="n">
-        <v>0</v>
+        <v>0.004545454545454545</v>
       </c>
       <c r="AE43" t="n">
         <v>0.004511278195488722</v>
@@ -7225,31 +7225,31 @@
         <v>0.004484304932735426</v>
       </c>
       <c r="AH43" t="n">
-        <v>1</v>
+        <v>0.8923076923076924</v>
       </c>
       <c r="AI43" t="n">
-        <v>0</v>
+        <v>0.004622496147919877</v>
       </c>
       <c r="AJ43" t="n">
-        <v>0</v>
+        <v>0.003110419906687403</v>
       </c>
       <c r="AK43" t="n">
-        <v>0</v>
+        <v>0.003048780487804878</v>
       </c>
       <c r="AL43" t="n">
-        <v>0</v>
+        <v>0.02252252252252252</v>
       </c>
       <c r="AM43" t="n">
-        <v>0</v>
+        <v>0.005865102639296188</v>
       </c>
       <c r="AN43" t="n">
-        <v>0.006033182503770739</v>
+        <v>0.06636500754147813</v>
       </c>
       <c r="AO43" t="n">
-        <v>1</v>
+        <v>0.922272047832586</v>
       </c>
       <c r="AP43" t="n">
-        <v>0.006116207951070336</v>
+        <v>0.1743119266055046</v>
       </c>
       <c r="AQ43" t="n">
         <v>1</v>
@@ -7258,25 +7258,25 @@
         <v>0.004457652303120356</v>
       </c>
       <c r="AS43" t="n">
-        <v>0.00631911532385466</v>
+        <v>0.3775671406003159</v>
       </c>
       <c r="AT43" t="n">
-        <v>0</v>
+        <v>0.367283950617284</v>
       </c>
       <c r="AU43" t="n">
-        <v>1</v>
+        <v>0.8502340093603744</v>
       </c>
       <c r="AV43" t="n">
-        <v>0</v>
+        <v>0.4764079147640791</v>
       </c>
       <c r="AW43" t="n">
-        <v>0</v>
+        <v>0.04107424960505529</v>
       </c>
       <c r="AX43" t="n">
-        <v>0.006182380216383307</v>
+        <v>0.00463678516228748</v>
       </c>
       <c r="AY43" t="n">
-        <v>0</v>
+        <v>0.05038167938931298</v>
       </c>
     </row>
     <row r="44">
@@ -7286,16 +7286,16 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0</v>
+        <v>0.5276073619631901</v>
       </c>
       <c r="C44" t="n">
         <v>0</v>
       </c>
       <c r="D44" t="n">
-        <v>0.07339449541284404</v>
+        <v>0.463302752293578</v>
       </c>
       <c r="E44" t="n">
-        <v>0.6213740458015267</v>
+        <v>0.4916030534351145</v>
       </c>
       <c r="F44" t="n">
         <v>0</v>
@@ -7304,13 +7304,13 @@
         <v>0</v>
       </c>
       <c r="H44" t="n">
-        <v>0.4296407185628742</v>
+        <v>1</v>
       </c>
       <c r="I44" t="n">
         <v>0</v>
       </c>
       <c r="J44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K44" t="n">
         <v>0</v>
@@ -7319,94 +7319,94 @@
         <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>0</v>
+        <v>0.5595054095826894</v>
       </c>
       <c r="N44" t="n">
-        <v>0</v>
+        <v>0.4721362229102167</v>
       </c>
       <c r="O44" t="n">
-        <v>0.01536098310291859</v>
+        <v>1</v>
       </c>
       <c r="P44" t="n">
         <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>1</v>
+        <v>0.9041731066460588</v>
       </c>
       <c r="R44" t="n">
         <v>0</v>
       </c>
       <c r="S44" t="n">
-        <v>0.534621578099839</v>
+        <v>0.1175523349436393</v>
       </c>
       <c r="T44" t="n">
-        <v>0.3580246913580247</v>
+        <v>0.4567901234567901</v>
       </c>
       <c r="U44" t="n">
-        <v>0.4036697247706422</v>
+        <v>0.4296636085626911</v>
       </c>
       <c r="V44" t="n">
         <v>0</v>
       </c>
       <c r="W44" t="n">
-        <v>0.5207373271889401</v>
+        <v>0.1029185867895545</v>
       </c>
       <c r="X44" t="n">
-        <v>1</v>
+        <v>0.9858267716535433</v>
       </c>
       <c r="Y44" t="n">
-        <v>0</v>
+        <v>0.2384615384615385</v>
       </c>
       <c r="Z44" t="n">
-        <v>0.5934579439252337</v>
+        <v>0.7071651090342679</v>
       </c>
       <c r="AA44" t="n">
-        <v>0.910828025477707</v>
+        <v>1</v>
       </c>
       <c r="AB44" t="n">
-        <v>0.9156050955414012</v>
+        <v>1</v>
       </c>
       <c r="AC44" t="n">
-        <v>1</v>
+        <v>0.9403453689167975</v>
       </c>
       <c r="AD44" t="n">
-        <v>0.009216589861751152</v>
+        <v>1</v>
       </c>
       <c r="AE44" t="n">
-        <v>0.9411764705882353</v>
+        <v>1</v>
       </c>
       <c r="AF44" t="n">
-        <v>0.9228395061728395</v>
+        <v>1</v>
       </c>
       <c r="AG44" t="n">
         <v>1</v>
       </c>
       <c r="AH44" t="n">
-        <v>0.01085271317829457</v>
+        <v>0.006201550387596899</v>
       </c>
       <c r="AI44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK44" t="n">
-        <v>0.02469135802469136</v>
+        <v>1</v>
       </c>
       <c r="AL44" t="n">
-        <v>0.01374045801526718</v>
+        <v>0.7343511450381679</v>
       </c>
       <c r="AM44" t="n">
-        <v>0</v>
+        <v>0.973568281938326</v>
       </c>
       <c r="AN44" t="n">
-        <v>0.8687022900763359</v>
+        <v>0.5129770992366413</v>
       </c>
       <c r="AO44" t="n">
-        <v>0.01339285714285714</v>
+        <v>0.002976190476190476</v>
       </c>
       <c r="AP44" t="n">
-        <v>0.9984472049689441</v>
+        <v>0.8680124223602484</v>
       </c>
       <c r="AQ44" t="n">
         <v>0.004457652303120356</v>
@@ -7415,25 +7415,25 @@
         <v>1</v>
       </c>
       <c r="AS44" t="n">
-        <v>0.9415481832543444</v>
+        <v>0.1453396524486572</v>
       </c>
       <c r="AT44" t="n">
-        <v>0</v>
+        <v>0.1430793157076205</v>
       </c>
       <c r="AU44" t="n">
-        <v>0.007776049766718507</v>
+        <v>0.003110419906687403</v>
       </c>
       <c r="AV44" t="n">
-        <v>0.5475460122699386</v>
+        <v>0.0736196319018405</v>
       </c>
       <c r="AW44" t="n">
-        <v>0.001582278481012658</v>
+        <v>0.560126582278481</v>
       </c>
       <c r="AX44" t="n">
         <v>1</v>
       </c>
       <c r="AY44" t="n">
-        <v>0</v>
+        <v>0.5209302325581395</v>
       </c>
     </row>
     <row r="45">
@@ -7443,31 +7443,31 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.0577223088923557</v>
+        <v>0.6037441497659907</v>
       </c>
       <c r="C45" t="n">
         <v>0</v>
       </c>
       <c r="D45" t="n">
-        <v>0.1605723370429253</v>
+        <v>0.6565977742448331</v>
       </c>
       <c r="E45" t="n">
-        <v>0.7435483870967742</v>
+        <v>0.6483870967741936</v>
       </c>
       <c r="F45" t="n">
-        <v>0</v>
+        <v>0.04081632653061224</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
       </c>
       <c r="H45" t="n">
-        <v>0.503125</v>
+        <v>0.1640625</v>
       </c>
       <c r="I45" t="n">
         <v>0</v>
       </c>
       <c r="J45" t="n">
-        <v>0.04830917874396135</v>
+        <v>0.14170692431562</v>
       </c>
       <c r="K45" t="n">
         <v>0</v>
@@ -7476,121 +7476,121 @@
         <v>0</v>
       </c>
       <c r="M45" t="n">
-        <v>0.06180665610142631</v>
+        <v>0.5784469096671949</v>
       </c>
       <c r="N45" t="n">
-        <v>0.05144694533762058</v>
+        <v>0.6495176848874598</v>
       </c>
       <c r="O45" t="n">
-        <v>0.07606973058637084</v>
+        <v>0.1489698890649762</v>
       </c>
       <c r="P45" t="n">
-        <v>0</v>
+        <v>0.001610305958132045</v>
       </c>
       <c r="Q45" t="n">
-        <v>0.9300476947535771</v>
+        <v>0.05405405405405406</v>
       </c>
       <c r="R45" t="n">
         <v>0</v>
       </c>
       <c r="S45" t="n">
-        <v>0.6183574879227053</v>
+        <v>1</v>
       </c>
       <c r="T45" t="n">
-        <v>0.4647435897435898</v>
+        <v>0.6714743589743589</v>
       </c>
       <c r="U45" t="n">
-        <v>0.5071542130365659</v>
+        <v>0.6915739268680445</v>
       </c>
       <c r="V45" t="n">
         <v>0</v>
       </c>
       <c r="W45" t="n">
-        <v>0.5964912280701754</v>
+        <v>1</v>
       </c>
       <c r="X45" t="n">
-        <v>0.9419354838709677</v>
+        <v>0.1790322580645161</v>
       </c>
       <c r="Y45" t="n">
-        <v>0.05573248407643312</v>
+        <v>0.945859872611465</v>
       </c>
       <c r="Z45" t="n">
-        <v>0.6773675762439807</v>
+        <v>0.4382022471910113</v>
       </c>
       <c r="AA45" t="n">
-        <v>1</v>
+        <v>0.1454849498327759</v>
       </c>
       <c r="AB45" t="n">
-        <v>0.9983525535420099</v>
+        <v>0.1581548599670511</v>
       </c>
       <c r="AC45" t="n">
-        <v>0.9320066334991708</v>
+        <v>0.1393034825870647</v>
       </c>
       <c r="AD45" t="n">
-        <v>0.06782334384858044</v>
+        <v>0.1561514195583596</v>
       </c>
       <c r="AE45" t="n">
-        <v>0.9984126984126984</v>
+        <v>0.1650793650793651</v>
       </c>
       <c r="AF45" t="n">
-        <v>1</v>
+        <v>0.1603174603174603</v>
       </c>
       <c r="AG45" t="n">
-        <v>0.9480314960629921</v>
+        <v>0.1511811023622047</v>
       </c>
       <c r="AH45" t="n">
-        <v>0.01612903225806452</v>
+        <v>0.5919354838709677</v>
       </c>
       <c r="AI45" t="n">
-        <v>0.04207119741100324</v>
+        <v>0.1553398058252427</v>
       </c>
       <c r="AJ45" t="n">
-        <v>0.05392156862745098</v>
+        <v>0.1584967320261438</v>
       </c>
       <c r="AK45" t="n">
-        <v>0.09162717219589257</v>
+        <v>0.1374407582938389</v>
       </c>
       <c r="AL45" t="n">
-        <v>0.06624605678233439</v>
+        <v>0.3990536277602524</v>
       </c>
       <c r="AM45" t="n">
-        <v>0.05546995377503852</v>
+        <v>0.1818181818181818</v>
       </c>
       <c r="AN45" t="n">
-        <v>0.8576</v>
+        <v>0.6368</v>
       </c>
       <c r="AO45" t="n">
-        <v>0.0140625</v>
+        <v>0.56875</v>
       </c>
       <c r="AP45" t="n">
-        <v>0.9314194577352473</v>
+        <v>0.07336523125996811</v>
       </c>
       <c r="AQ45" t="n">
-        <v>0.00631911532385466</v>
+        <v>0.3775671406003159</v>
       </c>
       <c r="AR45" t="n">
-        <v>0.9415481832543444</v>
+        <v>0.1453396524486572</v>
       </c>
       <c r="AS45" t="n">
         <v>1</v>
       </c>
       <c r="AT45" t="n">
-        <v>0.05967741935483871</v>
+        <v>1</v>
       </c>
       <c r="AU45" t="n">
-        <v>0.009724473257698542</v>
+        <v>0.6434359805510534</v>
       </c>
       <c r="AV45" t="n">
-        <v>0.6661417322834645</v>
+        <v>0.9669291338582677</v>
       </c>
       <c r="AW45" t="n">
-        <v>0.05254515599343185</v>
+        <v>0.5763546798029556</v>
       </c>
       <c r="AX45" t="n">
-        <v>0.9448051948051948</v>
+        <v>0.1347402597402597</v>
       </c>
       <c r="AY45" t="n">
-        <v>0.05431309904153354</v>
+        <v>0.6070287539936102</v>
       </c>
     </row>
     <row r="46">
@@ -7600,31 +7600,31 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>1</v>
+        <v>0.6213292117465224</v>
       </c>
       <c r="C46" t="n">
         <v>0</v>
       </c>
       <c r="D46" t="n">
-        <v>0.9254658385093167</v>
+        <v>0.6537267080745341</v>
       </c>
       <c r="E46" t="n">
-        <v>0.3528481012658228</v>
+        <v>0.6392405063291139</v>
       </c>
       <c r="F46" t="n">
-        <v>0</v>
+        <v>0.02773497688751926</v>
       </c>
       <c r="G46" t="n">
         <v>0</v>
       </c>
       <c r="H46" t="n">
-        <v>0.6198473282442748</v>
+        <v>0.1603053435114504</v>
       </c>
       <c r="I46" t="n">
         <v>0</v>
       </c>
       <c r="J46" t="n">
-        <v>1</v>
+        <v>0.1403508771929824</v>
       </c>
       <c r="K46" t="n">
         <v>0</v>
@@ -7633,121 +7633,121 @@
         <v>0</v>
       </c>
       <c r="M46" t="n">
-        <v>1</v>
+        <v>0.5921259842519685</v>
       </c>
       <c r="N46" t="n">
-        <v>1</v>
+        <v>0.6687797147385103</v>
       </c>
       <c r="O46" t="n">
-        <v>0.984399375975039</v>
+        <v>0.1419656786271451</v>
       </c>
       <c r="P46" t="n">
-        <v>0</v>
+        <v>0.0016</v>
       </c>
       <c r="Q46" t="n">
-        <v>0</v>
+        <v>0.05817610062893082</v>
       </c>
       <c r="R46" t="n">
         <v>0</v>
       </c>
       <c r="S46" t="n">
-        <v>0.417741935483871</v>
+        <v>0.9983870967741936</v>
       </c>
       <c r="T46" t="n">
-        <v>0.5915492957746479</v>
+        <v>0.6807511737089202</v>
       </c>
       <c r="U46" t="n">
-        <v>0.5518867924528302</v>
+        <v>0.699685534591195</v>
       </c>
       <c r="V46" t="n">
         <v>0</v>
       </c>
       <c r="W46" t="n">
-        <v>0.2945859872611465</v>
+        <v>0.9952229299363057</v>
       </c>
       <c r="X46" t="n">
-        <v>0</v>
+        <v>0.1736334405144695</v>
       </c>
       <c r="Y46" t="n">
-        <v>1</v>
+        <v>0.9352290679304898</v>
       </c>
       <c r="Z46" t="n">
-        <v>0.4545454545454545</v>
+        <v>0.4529505582137161</v>
       </c>
       <c r="AA46" t="n">
-        <v>0.07504078303425775</v>
+        <v>0.1517128874388254</v>
       </c>
       <c r="AB46" t="n">
-        <v>0.07790143084260731</v>
+        <v>0.1494435612082671</v>
       </c>
       <c r="AC46" t="n">
-        <v>0</v>
+        <v>0.1352657004830918</v>
       </c>
       <c r="AD46" t="n">
-        <v>0.9905511811023622</v>
+        <v>0.1559055118110236</v>
       </c>
       <c r="AE46" t="n">
-        <v>0.05188679245283019</v>
+        <v>0.1619496855345912</v>
       </c>
       <c r="AF46" t="n">
-        <v>0.0679304897314376</v>
+        <v>0.1611374407582938</v>
       </c>
       <c r="AG46" t="n">
-        <v>0</v>
+        <v>0.1470588235294118</v>
       </c>
       <c r="AH46" t="n">
-        <v>0.001587301587301587</v>
+        <v>0.5476190476190477</v>
       </c>
       <c r="AI46" t="n">
-        <v>1</v>
+        <v>0.1590551181102362</v>
       </c>
       <c r="AJ46" t="n">
-        <v>1</v>
+        <v>0.1558441558441558</v>
       </c>
       <c r="AK46" t="n">
-        <v>0.9759229534510433</v>
+        <v>0.1364365971107544</v>
       </c>
       <c r="AL46" t="n">
-        <v>0.9861538461538462</v>
+        <v>0.4169230769230769</v>
       </c>
       <c r="AM46" t="n">
-        <v>1</v>
+        <v>0.1803030303030303</v>
       </c>
       <c r="AN46" t="n">
-        <v>0.1182965299684543</v>
+        <v>0.6451104100946372</v>
       </c>
       <c r="AO46" t="n">
-        <v>0.003095975232198143</v>
+        <v>0.5185758513931888</v>
       </c>
       <c r="AP46" t="n">
-        <v>0.001574803149606299</v>
+        <v>0.06929133858267716</v>
       </c>
       <c r="AQ46" t="n">
-        <v>0</v>
+        <v>0.367283950617284</v>
       </c>
       <c r="AR46" t="n">
-        <v>0</v>
+        <v>0.1430793157076205</v>
       </c>
       <c r="AS46" t="n">
-        <v>0.05967741935483871</v>
+        <v>1</v>
       </c>
       <c r="AT46" t="n">
         <v>1</v>
       </c>
       <c r="AU46" t="n">
-        <v>0</v>
+        <v>0.6009538950715422</v>
       </c>
       <c r="AV46" t="n">
-        <v>0.4470404984423676</v>
+        <v>0.9875389408099688</v>
       </c>
       <c r="AW46" t="n">
-        <v>1</v>
+        <v>0.5823817292006526</v>
       </c>
       <c r="AX46" t="n">
-        <v>0</v>
+        <v>0.1358609794628752</v>
       </c>
       <c r="AY46" t="n">
-        <v>1</v>
+        <v>0.6095679012345679</v>
       </c>
     </row>
     <row r="47">
@@ -7757,154 +7757,154 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0</v>
+        <v>0.2339089481946625</v>
       </c>
       <c r="C47" t="n">
-        <v>0.9919614147909968</v>
+        <v>0.2057877813504823</v>
       </c>
       <c r="D47" t="n">
-        <v>0.003194888178913738</v>
+        <v>0.2795527156549521</v>
       </c>
       <c r="E47" t="n">
-        <v>0.00644122383252818</v>
+        <v>0.2576489533011272</v>
       </c>
       <c r="F47" t="n">
-        <v>0.9921259842519685</v>
+        <v>0.3023622047244094</v>
       </c>
       <c r="G47" t="n">
-        <v>0.9903999999999999</v>
+        <v>0.2256</v>
       </c>
       <c r="H47" t="n">
         <v>0.003076923076923077</v>
       </c>
       <c r="I47" t="n">
-        <v>0.9905808477237049</v>
+        <v>0.2135007849293564</v>
       </c>
       <c r="J47" t="n">
-        <v>0</v>
+        <v>0.003225806451612903</v>
       </c>
       <c r="K47" t="n">
-        <v>0.9901315789473685</v>
+        <v>0.2171052631578947</v>
       </c>
       <c r="L47" t="n">
-        <v>0.9904761904761905</v>
+        <v>0.2</v>
       </c>
       <c r="M47" t="n">
-        <v>0</v>
+        <v>0.2188498402555911</v>
       </c>
       <c r="N47" t="n">
-        <v>0</v>
+        <v>0.2688</v>
       </c>
       <c r="O47" t="n">
-        <v>0</v>
+        <v>0.001584786053882726</v>
       </c>
       <c r="P47" t="n">
-        <v>0.9936204146730463</v>
+        <v>0.2599681020733652</v>
       </c>
       <c r="Q47" t="n">
-        <v>0.007961783439490446</v>
+        <v>0.06847133757961783</v>
       </c>
       <c r="R47" t="n">
-        <v>0.9902120717781403</v>
+        <v>0.2088091353996737</v>
       </c>
       <c r="S47" t="n">
-        <v>0.01140065146579805</v>
+        <v>0.6351791530944625</v>
       </c>
       <c r="T47" t="n">
-        <v>0.008025682182985553</v>
+        <v>0.2921348314606741</v>
       </c>
       <c r="U47" t="n">
-        <v>0.006349206349206349</v>
+        <v>0.2952380952380952</v>
       </c>
       <c r="V47" t="n">
-        <v>0.9921259842519685</v>
+        <v>0.2125984251968504</v>
       </c>
       <c r="W47" t="n">
-        <v>0.1598101265822785</v>
+        <v>0.6977848101265823</v>
       </c>
       <c r="X47" t="n">
-        <v>0.009569377990430622</v>
+        <v>0.01116427432216906</v>
       </c>
       <c r="Y47" t="n">
-        <v>0</v>
+        <v>0.5192307692307693</v>
       </c>
       <c r="Z47" t="n">
-        <v>0.006462035541195477</v>
+        <v>0.1211631663974152</v>
       </c>
       <c r="AA47" t="n">
-        <v>0.008223684210526315</v>
+        <v>0.001644736842105263</v>
       </c>
       <c r="AB47" t="n">
-        <v>0.00974025974025974</v>
+        <v>0.003246753246753247</v>
       </c>
       <c r="AC47" t="n">
-        <v>0.006611570247933884</v>
+        <v>0.04462809917355372</v>
       </c>
       <c r="AD47" t="n">
-        <v>0</v>
+        <v>0.001582278481012658</v>
       </c>
       <c r="AE47" t="n">
-        <v>0.009478672985781991</v>
+        <v>0.00315955766192733</v>
       </c>
       <c r="AF47" t="n">
-        <v>0.006339144215530904</v>
+        <v>0.003169572107765452</v>
       </c>
       <c r="AG47" t="n">
-        <v>0.004739336492890996</v>
+        <v>0.00315955766192733</v>
       </c>
       <c r="AH47" t="n">
         <v>1</v>
       </c>
       <c r="AI47" t="n">
-        <v>0</v>
+        <v>0.003236245954692557</v>
       </c>
       <c r="AJ47" t="n">
-        <v>0</v>
+        <v>0.001639344262295082</v>
       </c>
       <c r="AK47" t="n">
-        <v>0</v>
+        <v>0.001577287066246057</v>
       </c>
       <c r="AL47" t="n">
-        <v>0</v>
+        <v>0.1121642969984202</v>
       </c>
       <c r="AM47" t="n">
-        <v>0</v>
+        <v>0.009287925696594427</v>
       </c>
       <c r="AN47" t="n">
-        <v>0.006472491909385114</v>
+        <v>0.2734627831715211</v>
       </c>
       <c r="AO47" t="n">
         <v>1</v>
       </c>
       <c r="AP47" t="n">
-        <v>0.007974481658692184</v>
+        <v>0.08771929824561403</v>
       </c>
       <c r="AQ47" t="n">
-        <v>1</v>
+        <v>0.8502340093603744</v>
       </c>
       <c r="AR47" t="n">
-        <v>0.007776049766718507</v>
+        <v>0.003110419906687403</v>
       </c>
       <c r="AS47" t="n">
-        <v>0.009724473257698542</v>
+        <v>0.6434359805510534</v>
       </c>
       <c r="AT47" t="n">
-        <v>0</v>
+        <v>0.6009538950715422</v>
       </c>
       <c r="AU47" t="n">
         <v>1</v>
       </c>
       <c r="AV47" t="n">
-        <v>0.0046875</v>
+        <v>0.7546875</v>
       </c>
       <c r="AW47" t="n">
-        <v>0</v>
+        <v>0.1986863711001642</v>
       </c>
       <c r="AX47" t="n">
-        <v>0.00966183574879227</v>
+        <v>0.001610305958132045</v>
       </c>
       <c r="AY47" t="n">
-        <v>0</v>
+        <v>0.2348242811501597</v>
       </c>
     </row>
     <row r="48">
@@ -7914,154 +7914,154 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.4094368340943683</v>
+        <v>0.512937595129376</v>
       </c>
       <c r="C48" t="n">
-        <v>0</v>
+        <v>0.003144654088050315</v>
       </c>
       <c r="D48" t="n">
-        <v>0.6172839506172839</v>
+        <v>0.5632716049382716</v>
       </c>
       <c r="E48" t="n">
-        <v>1</v>
+        <v>0.5383411580594679</v>
       </c>
       <c r="F48" t="n">
-        <v>0</v>
+        <v>0.04923076923076923</v>
       </c>
       <c r="G48" t="n">
-        <v>0</v>
+        <v>0.0032</v>
       </c>
       <c r="H48" t="n">
-        <v>0.5639097744360902</v>
+        <v>0.081203007518797</v>
       </c>
       <c r="I48" t="n">
-        <v>0</v>
+        <v>0.003091190108191654</v>
       </c>
       <c r="J48" t="n">
-        <v>0.4430379746835443</v>
+        <v>0.06487341772151899</v>
       </c>
       <c r="K48" t="n">
-        <v>0</v>
+        <v>0.004777070063694267</v>
       </c>
       <c r="L48" t="n">
-        <v>0</v>
+        <v>0.001524390243902439</v>
       </c>
       <c r="M48" t="n">
-        <v>0.4836702954898912</v>
+        <v>0.4758942457231726</v>
       </c>
       <c r="N48" t="n">
-        <v>0.4314641744548287</v>
+        <v>0.5467289719626168</v>
       </c>
       <c r="O48" t="n">
-        <v>0.4608294930875576</v>
+        <v>0.07526881720430108</v>
       </c>
       <c r="P48" t="n">
-        <v>0</v>
+        <v>0.01257861635220126</v>
       </c>
       <c r="Q48" t="n">
-        <v>0.5301391035548686</v>
+        <v>0.04482225656877898</v>
       </c>
       <c r="R48" t="n">
-        <v>0</v>
+        <v>0.003149606299212598</v>
       </c>
       <c r="S48" t="n">
-        <v>0.8763693270735524</v>
+        <v>0.9765258215962441</v>
       </c>
       <c r="T48" t="n">
-        <v>0.7897196261682243</v>
+        <v>0.5887850467289719</v>
       </c>
       <c r="U48" t="n">
-        <v>0.7987616099071208</v>
+        <v>0.5990712074303406</v>
       </c>
       <c r="V48" t="n">
-        <v>0</v>
+        <v>0.00302571860816944</v>
       </c>
       <c r="W48" t="n">
-        <v>0.8268330733229329</v>
+        <v>0.9859594383775351</v>
       </c>
       <c r="X48" t="n">
-        <v>0.5361635220125787</v>
+        <v>0.08962264150943396</v>
       </c>
       <c r="Y48" t="n">
-        <v>0.4522691705790297</v>
+        <v>0.8732394366197183</v>
       </c>
       <c r="Z48" t="n">
-        <v>0.5565891472868217</v>
+        <v>0.3426356589147287</v>
       </c>
       <c r="AA48" t="n">
-        <v>0.6260032102728732</v>
+        <v>0.08025682182985554</v>
       </c>
       <c r="AB48" t="n">
-        <v>0.6192733017377567</v>
+        <v>0.07740916271721959</v>
       </c>
       <c r="AC48" t="n">
-        <v>0.5255591054313099</v>
+        <v>0.08945686900958466</v>
       </c>
       <c r="AD48" t="n">
-        <v>0.4696734059097978</v>
+        <v>0.08087091757387248</v>
       </c>
       <c r="AE48" t="n">
-        <v>0.6052631578947368</v>
+        <v>0.08668730650154799</v>
       </c>
       <c r="AF48" t="n">
-        <v>0.6141975308641975</v>
+        <v>0.07561728395061729</v>
       </c>
       <c r="AG48" t="n">
-        <v>0.5286144578313253</v>
+        <v>0.0783132530120482</v>
       </c>
       <c r="AH48" t="n">
-        <v>0.00778816199376947</v>
+        <v>0.7071651090342679</v>
       </c>
       <c r="AI48" t="n">
-        <v>0.4341692789968652</v>
+        <v>0.08463949843260188</v>
       </c>
       <c r="AJ48" t="n">
-        <v>0.4565916398713826</v>
+        <v>0.07717041800643087</v>
       </c>
       <c r="AK48" t="n">
-        <v>0.4751552795031056</v>
+        <v>0.06832298136645963</v>
       </c>
       <c r="AL48" t="n">
-        <v>0.445468509984639</v>
+        <v>0.3164362519201229</v>
       </c>
       <c r="AM48" t="n">
-        <v>0.4369369369369369</v>
+        <v>0.09759759759759759</v>
       </c>
       <c r="AN48" t="n">
-        <v>0.6578538102643857</v>
+        <v>0.5412130637636081</v>
       </c>
       <c r="AO48" t="n">
-        <v>0.01234567901234568</v>
+        <v>0.6759259259259259</v>
       </c>
       <c r="AP48" t="n">
-        <v>0.5388198757763976</v>
+        <v>0.06055900621118013</v>
       </c>
       <c r="AQ48" t="n">
-        <v>0</v>
+        <v>0.4764079147640791</v>
       </c>
       <c r="AR48" t="n">
-        <v>0.5475460122699386</v>
+        <v>0.0736196319018405</v>
       </c>
       <c r="AS48" t="n">
-        <v>0.6661417322834645</v>
+        <v>0.9669291338582677</v>
       </c>
       <c r="AT48" t="n">
-        <v>0.4470404984423676</v>
+        <v>0.9875389408099688</v>
       </c>
       <c r="AU48" t="n">
-        <v>0.0046875</v>
+        <v>0.7546875</v>
       </c>
       <c r="AV48" t="n">
         <v>1</v>
       </c>
       <c r="AW48" t="n">
-        <v>0.4541139240506329</v>
+        <v>0.4731012658227848</v>
       </c>
       <c r="AX48" t="n">
-        <v>0.5377358490566038</v>
+        <v>0.07075471698113207</v>
       </c>
       <c r="AY48" t="n">
-        <v>0.4362519201228879</v>
+        <v>0.5038402457757296</v>
       </c>
     </row>
     <row r="49">
@@ -8071,16 +8071,16 @@
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.9984076433121019</v>
+        <v>1</v>
       </c>
       <c r="C49" t="n">
         <v>0</v>
       </c>
       <c r="D49" t="n">
-        <v>0.9149606299212598</v>
+        <v>0.9779527559055118</v>
       </c>
       <c r="E49" t="n">
-        <v>0.3695299837925446</v>
+        <v>1</v>
       </c>
       <c r="F49" t="n">
         <v>0</v>
@@ -8089,13 +8089,13 @@
         <v>0</v>
       </c>
       <c r="H49" t="n">
-        <v>0.5754276827371695</v>
+        <v>0.5987558320373251</v>
       </c>
       <c r="I49" t="n">
         <v>0</v>
       </c>
       <c r="J49" t="n">
-        <v>0.9983948635634029</v>
+        <v>0.579454253611557</v>
       </c>
       <c r="K49" t="n">
         <v>0</v>
@@ -8104,118 +8104,118 @@
         <v>0</v>
       </c>
       <c r="M49" t="n">
-        <v>0.9983766233766234</v>
+        <v>0.8944805194805194</v>
       </c>
       <c r="N49" t="n">
-        <v>0.99836867862969</v>
+        <v>0.9216965742251223</v>
       </c>
       <c r="O49" t="n">
-        <v>0.9889937106918238</v>
+        <v>0.5707547169811321</v>
       </c>
       <c r="P49" t="n">
         <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>0.0016</v>
+        <v>0.4528</v>
       </c>
       <c r="R49" t="n">
         <v>0</v>
       </c>
       <c r="S49" t="n">
-        <v>0.4444444444444444</v>
+        <v>0.5555555555555556</v>
       </c>
       <c r="T49" t="n">
-        <v>0.6236044657097288</v>
+        <v>0.9712918660287081</v>
       </c>
       <c r="U49" t="n">
-        <v>0.5739268680445151</v>
+        <v>0.9682034976152624</v>
       </c>
       <c r="V49" t="n">
         <v>0</v>
       </c>
       <c r="W49" t="n">
-        <v>0.303370786516854</v>
+        <v>0.463884430176565</v>
       </c>
       <c r="X49" t="n">
-        <v>0.001607717041800643</v>
+        <v>0.617363344051447</v>
       </c>
       <c r="Y49" t="n">
-        <v>1</v>
+        <v>0.6591639871382636</v>
       </c>
       <c r="Z49" t="n">
-        <v>0.4116693679092382</v>
+        <v>1</v>
       </c>
       <c r="AA49" t="n">
-        <v>0.07603305785123966</v>
+        <v>0.5917355371900826</v>
       </c>
       <c r="AB49" t="n">
-        <v>0.07119205298013245</v>
+        <v>0.5927152317880795</v>
       </c>
       <c r="AC49" t="n">
-        <v>0</v>
+        <v>0.5008183306055647</v>
       </c>
       <c r="AD49" t="n">
-        <v>0.9952229299363057</v>
+        <v>0.5987261146496815</v>
       </c>
       <c r="AE49" t="n">
-        <v>0.05379746835443038</v>
+        <v>0.5901898734177216</v>
       </c>
       <c r="AF49" t="n">
-        <v>0.064</v>
+        <v>0.6112</v>
       </c>
       <c r="AG49" t="n">
-        <v>0.001582278481012658</v>
+        <v>0.5854430379746836</v>
       </c>
       <c r="AH49" t="n">
-        <v>0.001594896331738437</v>
+        <v>0.1658692185007974</v>
       </c>
       <c r="AI49" t="n">
-        <v>1</v>
+        <v>0.5891980360065466</v>
       </c>
       <c r="AJ49" t="n">
-        <v>0.9983579638752053</v>
+        <v>0.5944170771756979</v>
       </c>
       <c r="AK49" t="n">
-        <v>0.9820846905537459</v>
+        <v>0.5651465798045603</v>
       </c>
       <c r="AL49" t="n">
-        <v>0.9936608557844691</v>
+        <v>0.9112519809825673</v>
       </c>
       <c r="AM49" t="n">
-        <v>0.9984709480122325</v>
+        <v>0.6207951070336392</v>
       </c>
       <c r="AN49" t="n">
-        <v>0.1244094488188976</v>
+        <v>0.9606299212598425</v>
       </c>
       <c r="AO49" t="n">
-        <v>0.00310077519379845</v>
+        <v>0.1581395348837209</v>
       </c>
       <c r="AP49" t="n">
-        <v>0.003241491085899514</v>
+        <v>0.4408427876823339</v>
       </c>
       <c r="AQ49" t="n">
-        <v>0</v>
+        <v>0.04107424960505529</v>
       </c>
       <c r="AR49" t="n">
-        <v>0.001582278481012658</v>
+        <v>0.560126582278481</v>
       </c>
       <c r="AS49" t="n">
-        <v>0.05254515599343185</v>
+        <v>0.5763546798029556</v>
       </c>
       <c r="AT49" t="n">
-        <v>1</v>
+        <v>0.5823817292006526</v>
       </c>
       <c r="AU49" t="n">
-        <v>0</v>
+        <v>0.1986863711001642</v>
       </c>
       <c r="AV49" t="n">
-        <v>0.4541139240506329</v>
+        <v>0.4731012658227848</v>
       </c>
       <c r="AW49" t="n">
         <v>1</v>
       </c>
       <c r="AX49" t="n">
-        <v>0.001626016260162602</v>
+        <v>0.5739837398373984</v>
       </c>
       <c r="AY49" t="n">
         <v>1</v>
@@ -8228,16 +8228,16 @@
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0</v>
+        <v>0.5300632911392406</v>
       </c>
       <c r="C50" t="n">
         <v>0</v>
       </c>
       <c r="D50" t="n">
-        <v>0.06698564593301436</v>
+        <v>0.4673046251993621</v>
       </c>
       <c r="E50" t="n">
-        <v>0.6075353218210361</v>
+        <v>0.5007849293563579</v>
       </c>
       <c r="F50" t="n">
         <v>0</v>
@@ -8246,13 +8246,13 @@
         <v>0</v>
       </c>
       <c r="H50" t="n">
-        <v>0.4230769230769231</v>
+        <v>1</v>
       </c>
       <c r="I50" t="n">
         <v>0</v>
       </c>
       <c r="J50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K50" t="n">
         <v>0</v>
@@ -8261,121 +8261,121 @@
         <v>0</v>
       </c>
       <c r="M50" t="n">
-        <v>0</v>
+        <v>0.5629032258064516</v>
       </c>
       <c r="N50" t="n">
-        <v>0</v>
+        <v>0.4719101123595505</v>
       </c>
       <c r="O50" t="n">
-        <v>0.01572327044025157</v>
+        <v>1</v>
       </c>
       <c r="P50" t="n">
         <v>0</v>
       </c>
       <c r="Q50" t="n">
-        <v>1</v>
+        <v>0.903125</v>
       </c>
       <c r="R50" t="n">
         <v>0</v>
       </c>
       <c r="S50" t="n">
-        <v>0.532051282051282</v>
+        <v>0.1201923076923077</v>
       </c>
       <c r="T50" t="n">
-        <v>0.3672496025437202</v>
+        <v>0.4578696343402226</v>
       </c>
       <c r="U50" t="n">
-        <v>0.4018987341772152</v>
+        <v>0.4272151898734177</v>
       </c>
       <c r="V50" t="n">
         <v>0</v>
       </c>
       <c r="W50" t="n">
-        <v>0.5182829888712241</v>
+        <v>0.08744038155802862</v>
       </c>
       <c r="X50" t="n">
-        <v>1</v>
+        <v>0.9824000000000001</v>
       </c>
       <c r="Y50" t="n">
-        <v>0</v>
+        <v>0.2283464566929134</v>
       </c>
       <c r="Z50" t="n">
-        <v>0.5949367088607594</v>
+        <v>0.7151898734177216</v>
       </c>
       <c r="AA50" t="n">
-        <v>0.9170731707317074</v>
+        <v>1</v>
       </c>
       <c r="AB50" t="n">
-        <v>0.9207119741100324</v>
+        <v>1</v>
       </c>
       <c r="AC50" t="n">
-        <v>1</v>
+        <v>0.9341021416803954</v>
       </c>
       <c r="AD50" t="n">
-        <v>0.009345794392523364</v>
+        <v>1</v>
       </c>
       <c r="AE50" t="n">
-        <v>0.9416403785488959</v>
+        <v>1</v>
       </c>
       <c r="AF50" t="n">
-        <v>0.9233176838810642</v>
+        <v>1</v>
       </c>
       <c r="AG50" t="n">
         <v>1</v>
       </c>
       <c r="AH50" t="n">
-        <v>0.01449275362318841</v>
+        <v>0.00644122383252818</v>
       </c>
       <c r="AI50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK50" t="n">
-        <v>0.02070063694267516</v>
+        <v>1</v>
       </c>
       <c r="AL50" t="n">
-        <v>0.009360374414976599</v>
+        <v>0.7410296411856474</v>
       </c>
       <c r="AM50" t="n">
-        <v>0</v>
+        <v>0.9725609756097561</v>
       </c>
       <c r="AN50" t="n">
-        <v>0.8578199052132701</v>
+        <v>0.5197472353870458</v>
       </c>
       <c r="AO50" t="n">
-        <v>0.01246105919003115</v>
+        <v>0.001557632398753894</v>
       </c>
       <c r="AP50" t="n">
-        <v>0.9983896940418679</v>
+        <v>0.8679549114331723</v>
       </c>
       <c r="AQ50" t="n">
-        <v>0.006182380216383307</v>
+        <v>0.00463678516228748</v>
       </c>
       <c r="AR50" t="n">
         <v>1</v>
       </c>
       <c r="AS50" t="n">
-        <v>0.9448051948051948</v>
+        <v>0.1347402597402597</v>
       </c>
       <c r="AT50" t="n">
-        <v>0</v>
+        <v>0.1358609794628752</v>
       </c>
       <c r="AU50" t="n">
-        <v>0.00966183574879227</v>
+        <v>0.001610305958132045</v>
       </c>
       <c r="AV50" t="n">
-        <v>0.5377358490566038</v>
+        <v>0.07075471698113207</v>
       </c>
       <c r="AW50" t="n">
-        <v>0.001626016260162602</v>
+        <v>0.5739837398373984</v>
       </c>
       <c r="AX50" t="n">
         <v>1</v>
       </c>
       <c r="AY50" t="n">
-        <v>0</v>
+        <v>0.5266457680250783</v>
       </c>
     </row>
     <row r="51">
@@ -8391,10 +8391,10 @@
         <v>0</v>
       </c>
       <c r="D51" t="n">
-        <v>0.9231950844854071</v>
+        <v>0.9907834101382489</v>
       </c>
       <c r="E51" t="n">
-        <v>0.3674418604651163</v>
+        <v>1</v>
       </c>
       <c r="F51" t="n">
         <v>0</v>
@@ -8403,13 +8403,13 @@
         <v>0</v>
       </c>
       <c r="H51" t="n">
-        <v>0.5969696969696969</v>
+        <v>0.546969696969697</v>
       </c>
       <c r="I51" t="n">
         <v>0</v>
       </c>
       <c r="J51" t="n">
-        <v>1</v>
+        <v>0.5337519623233909</v>
       </c>
       <c r="K51" t="n">
         <v>0</v>
@@ -8418,118 +8418,118 @@
         <v>0</v>
       </c>
       <c r="M51" t="n">
-        <v>1</v>
+        <v>0.8918495297805643</v>
       </c>
       <c r="N51" t="n">
-        <v>1</v>
+        <v>0.9365079365079365</v>
       </c>
       <c r="O51" t="n">
-        <v>0.9891135303265941</v>
+        <v>0.5349922239502333</v>
       </c>
       <c r="P51" t="n">
         <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>0</v>
+        <v>0.4101382488479263</v>
       </c>
       <c r="R51" t="n">
         <v>0</v>
       </c>
       <c r="S51" t="n">
-        <v>0.4391025641025641</v>
+        <v>0.592948717948718</v>
       </c>
       <c r="T51" t="n">
-        <v>0.6111111111111112</v>
+        <v>0.9861111111111112</v>
       </c>
       <c r="U51" t="n">
-        <v>0.5701078582434514</v>
+        <v>0.9815100154083205</v>
       </c>
       <c r="V51" t="n">
         <v>0</v>
       </c>
       <c r="W51" t="n">
-        <v>0.3052959501557632</v>
+        <v>0.5</v>
       </c>
       <c r="X51" t="n">
-        <v>0</v>
+        <v>0.5682888540031397</v>
       </c>
       <c r="Y51" t="n">
-        <v>1</v>
+        <v>0.6847826086956522</v>
       </c>
       <c r="Z51" t="n">
-        <v>0.4327666151468315</v>
+        <v>0.8732612055641422</v>
       </c>
       <c r="AA51" t="n">
-        <v>0.07890499194847021</v>
+        <v>0.5475040257648953</v>
       </c>
       <c r="AB51" t="n">
-        <v>0.08214849921011058</v>
+        <v>0.5497630331753555</v>
       </c>
       <c r="AC51" t="n">
-        <v>0</v>
+        <v>0.456140350877193</v>
       </c>
       <c r="AD51" t="n">
-        <v>0.9908256880733946</v>
+        <v>0.5504587155963303</v>
       </c>
       <c r="AE51" t="n">
-        <v>0.0514018691588785</v>
+        <v>0.5560747663551402</v>
       </c>
       <c r="AF51" t="n">
-        <v>0.0700152207001522</v>
+        <v>0.5601217656012176</v>
       </c>
       <c r="AG51" t="n">
-        <v>0</v>
+        <v>0.5444947209653092</v>
       </c>
       <c r="AH51" t="n">
-        <v>0.001567398119122257</v>
+        <v>0.2006269592476489</v>
       </c>
       <c r="AI51" t="n">
-        <v>1</v>
+        <v>0.5484375</v>
       </c>
       <c r="AJ51" t="n">
-        <v>1</v>
+        <v>0.5584</v>
       </c>
       <c r="AK51" t="n">
-        <v>0.9844236760124611</v>
+        <v>0.5295950155763239</v>
       </c>
       <c r="AL51" t="n">
-        <v>0.9861963190184049</v>
+        <v>0.8113496932515337</v>
       </c>
       <c r="AM51" t="n">
-        <v>1</v>
+        <v>0.5729166666666666</v>
       </c>
       <c r="AN51" t="n">
-        <v>0.1138845553822153</v>
+        <v>0.9719188767550702</v>
       </c>
       <c r="AO51" t="n">
-        <v>0.00310077519379845</v>
+        <v>0.1937984496124031</v>
       </c>
       <c r="AP51" t="n">
-        <v>0</v>
+        <v>0.3987635239567233</v>
       </c>
       <c r="AQ51" t="n">
-        <v>0</v>
+        <v>0.05038167938931298</v>
       </c>
       <c r="AR51" t="n">
-        <v>0</v>
+        <v>0.5209302325581395</v>
       </c>
       <c r="AS51" t="n">
-        <v>0.05431309904153354</v>
+        <v>0.6070287539936102</v>
       </c>
       <c r="AT51" t="n">
-        <v>1</v>
+        <v>0.6095679012345679</v>
       </c>
       <c r="AU51" t="n">
-        <v>0</v>
+        <v>0.2348242811501597</v>
       </c>
       <c r="AV51" t="n">
-        <v>0.4362519201228879</v>
+        <v>0.5038402457757296</v>
       </c>
       <c r="AW51" t="n">
         <v>1</v>
       </c>
       <c r="AX51" t="n">
-        <v>0</v>
+        <v>0.5266457680250783</v>
       </c>
       <c r="AY51" t="n">
         <v>1</v>
